--- a/financials/TCX/TCX_financials.xlsx
+++ b/financials/TCX/TCX_financials.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_sheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="income_statement" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cash_flow" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="balance_sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="income_statement" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="cash_flow" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,13 +19,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -36,7 +39,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -44,12 +47,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -419,27 +431,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
@@ -756,16 +768,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>15472433711</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>53177959656</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>34102287159</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>18621853899</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -4404,27 +4416,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
@@ -5946,27 +5958,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
@@ -6856,7 +6868,7 @@
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>35000000000</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -7290,16 +7302,16 @@
         </is>
       </c>
       <c r="B71" t="n">
+        <v>6447211380125</v>
+      </c>
+      <c r="C71" t="n">
         <v>8245482244688</v>
       </c>
-      <c r="C71" t="n">
+      <c r="D71" t="n">
         <v>2945784273957</v>
       </c>
-      <c r="D71" t="n">
-        <v>855886234155</v>
-      </c>
       <c r="E71" t="n">
-        <v>4575045031535</v>
+        <v>2278125882711</v>
       </c>
     </row>
     <row r="72">
@@ -7347,13 +7359,13 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0</v>
+        <v>4206007929509</v>
       </c>
       <c r="C74" t="n">
-        <v>0</v>
+        <v>1734150405730</v>
       </c>
       <c r="D74" t="n">
-        <v>0</v>
+        <v>1797451176015</v>
       </c>
       <c r="E74" t="n">
         <v>0</v>
@@ -7366,16 +7378,16 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1734150405730</v>
+        <v>49373986618</v>
       </c>
       <c r="C75" t="n">
-        <v>1797451176015</v>
+        <v>44613698630</v>
       </c>
       <c r="D75" t="n">
-        <v>1422239648556</v>
+        <v>1031489346567</v>
       </c>
       <c r="E75" t="n">
-        <v>0</v>
+        <v>51919186748</v>
       </c>
     </row>
     <row r="76">
@@ -7404,16 +7416,16 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>44613698630</v>
+        <v>0</v>
       </c>
       <c r="C77" t="n">
-        <v>1031489346567</v>
+        <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>51919186748</v>
+        <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>2052242343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">

--- a/financials/TCX/TCX_financials.xlsx
+++ b/financials/TCX/TCX_financials.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="balance_sheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="income_statement" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="cash_flow" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="chi_so_tai_chinh" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="income_statement" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cash_flow" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chi_so_tai_chinh" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -555,11 +555,11 @@
   <dimension ref="A1:E209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="88" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -570,22 +570,22 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>2025</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>2022</t>
         </is>
       </c>
     </row>
@@ -596,16 +596,16 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
+        <v>25948479990644</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>40628257426641</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>49394749963613</v>
+      </c>
+      <c r="E2" s="4" t="n">
         <v>76612765855403</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>49394749963613</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>40628257426641</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>25948479990644</v>
       </c>
     </row>
     <row r="3">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
+        <v>2404813202406</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>4582180994188</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>2864601041636</v>
+      </c>
+      <c r="E3" s="4" t="n">
         <v>3108078221717</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>2864601041636</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>4582180994188</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>2404813202406</v>
       </c>
     </row>
     <row r="4">
@@ -634,16 +634,16 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
+        <v>2404813202406</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>4547180994188</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>2864601041636</v>
+      </c>
+      <c r="E4" s="4" t="n">
         <v>3108078221717</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>2864601041636</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>4547180994188</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>2404813202406</v>
       </c>
     </row>
     <row r="5">
@@ -656,10 +656,10 @@
         <v>0</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>0</v>
+        <v>35000000000</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>35000000000</v>
+        <v>0</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>0</v>
@@ -672,16 +672,16 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>17278163500</v>
+      </c>
+      <c r="E6" s="4" t="n">
         <v>38923020900</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>17278163500</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
+        <v>-3599620</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>-4774603364</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>-10806072274</v>
+      </c>
+      <c r="E7" s="4" t="n">
         <v>-12757948678</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>-10806072274</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>-4774603364</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>-3599620</v>
       </c>
     </row>
     <row r="8">
@@ -710,16 +710,16 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
+        <v>3658318396519</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>3064760726090</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>656597329458</v>
+      </c>
+      <c r="E8" s="4" t="n">
         <v>727456098295</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>656597329458</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>3064760726090</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>3658318396519</v>
       </c>
     </row>
     <row r="9">
@@ -748,16 +748,16 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
+        <v>1512267704</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>1707458921</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>1949853033</v>
+      </c>
+      <c r="E10" s="4" t="n">
         <v>5729878954</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>1949853033</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>1707458921</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>1512267704</v>
       </c>
     </row>
     <row r="11">
@@ -805,16 +805,16 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
+        <v>3450110238837</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>2709273571142</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>22076558945</v>
+      </c>
+      <c r="E13" s="4" t="n">
         <v>2271195630</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>22076558945</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>2709273571142</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>3450110238837</v>
       </c>
     </row>
     <row r="14">
@@ -919,16 +919,16 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
+        <v>7373703649</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>33780597159</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>52699169656</v>
+      </c>
+      <c r="E19" s="4" t="n">
         <v>13408458353</v>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>52699169656</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>33780597159</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>7373703649</v>
       </c>
     </row>
     <row r="20">
@@ -995,16 +995,16 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
+        <v>143067748219</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>3160172027968</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>3849383856581</v>
+      </c>
+      <c r="E23" s="4" t="n">
         <v>4019491143606</v>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>3849383856581</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>3160172027968</v>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>143067748219</v>
       </c>
     </row>
     <row r="24">
@@ -1109,16 +1109,16 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
+        <v>84726784106</v>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>64589748067</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>50740739690</v>
+      </c>
+      <c r="E29" s="4" t="n">
         <v>107181206706</v>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>50740739690</v>
-      </c>
-      <c r="D29" s="4" t="n">
-        <v>64589748067</v>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>84726784106</v>
       </c>
     </row>
     <row r="30">
@@ -1128,16 +1128,16 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
+        <v>68067359617</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>50134678668</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>39993555777</v>
+      </c>
+      <c r="E30" s="4" t="n">
         <v>33220423249</v>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>39993555777</v>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>50134678668</v>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>68067359617</v>
       </c>
     </row>
     <row r="31">
@@ -1147,16 +1147,16 @@
         </is>
       </c>
       <c r="B31" s="4" t="n">
+        <v>110681859040</v>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>109934766200</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>117475687200</v>
+      </c>
+      <c r="E31" s="4" t="n">
         <v>126797126020</v>
-      </c>
-      <c r="C31" s="4" t="n">
-        <v>117475687200</v>
-      </c>
-      <c r="D31" s="4" t="n">
-        <v>109934766200</v>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>110681859040</v>
       </c>
     </row>
     <row r="32">
@@ -1166,16 +1166,16 @@
         </is>
       </c>
       <c r="B32" s="4" t="n">
+        <v>-42614499423</v>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>-59800087532</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>-77482131423</v>
+      </c>
+      <c r="E32" s="4" t="n">
         <v>-93576702771</v>
-      </c>
-      <c r="C32" s="4" t="n">
-        <v>-77482131423</v>
-      </c>
-      <c r="D32" s="4" t="n">
-        <v>-59800087532</v>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>-42614499423</v>
       </c>
     </row>
     <row r="33">
@@ -1242,16 +1242,16 @@
         </is>
       </c>
       <c r="B36" s="4" t="n">
+        <v>16659424489</v>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>14455069399</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>10747183913</v>
+      </c>
+      <c r="E36" s="4" t="n">
         <v>73960783457</v>
-      </c>
-      <c r="C36" s="4" t="n">
-        <v>10747183913</v>
-      </c>
-      <c r="D36" s="4" t="n">
-        <v>14455069399</v>
-      </c>
-      <c r="E36" s="4" t="n">
-        <v>16659424489</v>
       </c>
     </row>
     <row r="37">
@@ -1261,16 +1261,16 @@
         </is>
       </c>
       <c r="B37" s="4" t="n">
+        <v>61426279490</v>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>64600335490</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>66775606490</v>
+      </c>
+      <c r="E37" s="4" t="n">
         <v>138768470729</v>
-      </c>
-      <c r="C37" s="4" t="n">
-        <v>66775606490</v>
-      </c>
-      <c r="D37" s="4" t="n">
-        <v>64600335490</v>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>61426279490</v>
       </c>
     </row>
     <row r="38">
@@ -1280,16 +1280,16 @@
         </is>
       </c>
       <c r="B38" s="4" t="n">
+        <v>-44766855001</v>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>-50145266091</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>-56028422577</v>
+      </c>
+      <c r="E38" s="4" t="n">
         <v>-64807687272</v>
-      </c>
-      <c r="C38" s="4" t="n">
-        <v>-56028422577</v>
-      </c>
-      <c r="D38" s="4" t="n">
-        <v>-50145266091</v>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>-44766855001</v>
       </c>
     </row>
     <row r="39">
@@ -1375,16 +1375,16 @@
         </is>
       </c>
       <c r="B43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>3033431775000</v>
+      </c>
+      <c r="D43" s="4" t="n">
+        <v>3533431775000</v>
+      </c>
+      <c r="E43" s="4" t="n">
         <v>3610268431824</v>
-      </c>
-      <c r="C43" s="4" t="n">
-        <v>3533431775000</v>
-      </c>
-      <c r="D43" s="4" t="n">
-        <v>3033431775000</v>
-      </c>
-      <c r="E43" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1432,16 +1432,16 @@
         </is>
       </c>
       <c r="B46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>3033431775000</v>
+      </c>
+      <c r="E46" s="4" t="n">
         <v>3200268431824</v>
-      </c>
-      <c r="C46" s="4" t="n">
-        <v>3033431775000</v>
-      </c>
-      <c r="D46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1470,16 +1470,16 @@
         </is>
       </c>
       <c r="B48" s="4" t="n">
+        <v>58340964113</v>
+      </c>
+      <c r="C48" s="4" t="n">
+        <v>59493017350</v>
+      </c>
+      <c r="D48" s="4" t="n">
+        <v>256740022659</v>
+      </c>
+      <c r="E48" s="4" t="n">
         <v>248276291750</v>
-      </c>
-      <c r="C48" s="4" t="n">
-        <v>256740022659</v>
-      </c>
-      <c r="D48" s="4" t="n">
-        <v>59493017350</v>
-      </c>
-      <c r="E48" s="4" t="n">
-        <v>58340964113</v>
       </c>
     </row>
     <row r="49">
@@ -1489,16 +1489,16 @@
         </is>
       </c>
       <c r="B49" s="4" t="n">
+        <v>14257812698</v>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>8860645504</v>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>8909838294</v>
+      </c>
+      <c r="E49" s="4" t="n">
         <v>16980000795</v>
-      </c>
-      <c r="C49" s="4" t="n">
-        <v>8909838294</v>
-      </c>
-      <c r="D49" s="4" t="n">
-        <v>8860645504</v>
-      </c>
-      <c r="E49" s="4" t="n">
-        <v>14257812698</v>
       </c>
     </row>
     <row r="50">
@@ -1508,16 +1508,16 @@
         </is>
       </c>
       <c r="B50" s="4" t="n">
+        <v>20791943497</v>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>24188580704</v>
+      </c>
+      <c r="D50" s="4" t="n">
+        <v>23846393223</v>
+      </c>
+      <c r="E50" s="4" t="n">
         <v>17804201744</v>
-      </c>
-      <c r="C50" s="4" t="n">
-        <v>23846393223</v>
-      </c>
-      <c r="D50" s="4" t="n">
-        <v>24188580704</v>
-      </c>
-      <c r="E50" s="4" t="n">
-        <v>20791943497</v>
       </c>
     </row>
     <row r="51">
@@ -1527,7 +1527,7 @@
         </is>
       </c>
       <c r="B51" s="4" t="n">
-        <v>10083869378</v>
+        <v>10000000000</v>
       </c>
       <c r="C51" s="4" t="n">
         <v>10000000000</v>
@@ -1536,7 +1536,7 @@
         <v>10000000000</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>10000000000</v>
+        <v>10083869378</v>
       </c>
     </row>
     <row r="52">
@@ -1546,16 +1546,16 @@
         </is>
       </c>
       <c r="B52" s="4" t="n">
+        <v>26091547738863</v>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>43788429454609</v>
+      </c>
+      <c r="D52" s="4" t="n">
+        <v>53244133820194</v>
+      </c>
+      <c r="E52" s="4" t="n">
         <v>80632256999009</v>
-      </c>
-      <c r="C52" s="4" t="n">
-        <v>53244133820194</v>
-      </c>
-      <c r="D52" s="4" t="n">
-        <v>43788429454609</v>
-      </c>
-      <c r="E52" s="4" t="n">
-        <v>26091547738863</v>
       </c>
     </row>
     <row r="53">
@@ -1565,16 +1565,16 @@
         </is>
       </c>
       <c r="B53" s="4" t="n">
+        <v>15102289530963</v>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>20158922867321</v>
+      </c>
+      <c r="D53" s="4" t="n">
+        <v>26947161543516</v>
+      </c>
+      <c r="E53" s="4" t="n">
         <v>36532676815634</v>
-      </c>
-      <c r="C53" s="4" t="n">
-        <v>26947161543516</v>
-      </c>
-      <c r="D53" s="4" t="n">
-        <v>20158922867321</v>
-      </c>
-      <c r="E53" s="4" t="n">
-        <v>15102289530963</v>
       </c>
     </row>
     <row r="54">
@@ -1584,16 +1584,16 @@
         </is>
       </c>
       <c r="B54" s="4" t="n">
+        <v>13378593348270</v>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>19197091992778</v>
+      </c>
+      <c r="D54" s="4" t="n">
+        <v>25934267565771</v>
+      </c>
+      <c r="E54" s="4" t="n">
         <v>35016932279815</v>
-      </c>
-      <c r="C54" s="4" t="n">
-        <v>25934267565771</v>
-      </c>
-      <c r="D54" s="4" t="n">
-        <v>19197091992778</v>
-      </c>
-      <c r="E54" s="4" t="n">
-        <v>13378593348270</v>
       </c>
     </row>
     <row r="55">
@@ -1603,16 +1603,16 @@
         </is>
       </c>
       <c r="B55" s="4" t="n">
+        <v>6871600000000</v>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>18061885497900</v>
+      </c>
+      <c r="D55" s="4" t="n">
+        <v>20522995942980</v>
+      </c>
+      <c r="E55" s="4" t="n">
         <v>31079695096211</v>
-      </c>
-      <c r="C55" s="4" t="n">
-        <v>20522995942980</v>
-      </c>
-      <c r="D55" s="4" t="n">
-        <v>18061885497900</v>
-      </c>
-      <c r="E55" s="4" t="n">
-        <v>6871600000000</v>
       </c>
     </row>
     <row r="56">
@@ -1622,16 +1622,16 @@
         </is>
       </c>
       <c r="B56" s="4" t="n">
+        <v>240252940500</v>
+      </c>
+      <c r="C56" s="4" t="n">
+        <v>606772700</v>
+      </c>
+      <c r="D56" s="4" t="n">
+        <v>66489220</v>
+      </c>
+      <c r="E56" s="4" t="n">
         <v>2000410883</v>
-      </c>
-      <c r="C56" s="4" t="n">
-        <v>66489220</v>
-      </c>
-      <c r="D56" s="4" t="n">
-        <v>606772700</v>
-      </c>
-      <c r="E56" s="4" t="n">
-        <v>240252940500</v>
       </c>
     </row>
     <row r="57">
@@ -1644,10 +1644,10 @@
         <v>0</v>
       </c>
       <c r="C57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="4" t="n">
         <v>126000000000</v>
-      </c>
-      <c r="D57" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="E57" s="4" t="n">
         <v>0</v>
@@ -1660,16 +1660,16 @@
         </is>
       </c>
       <c r="B58" s="4" t="n">
+        <v>316020156985</v>
+      </c>
+      <c r="C58" s="4" t="n">
+        <v>496359203753</v>
+      </c>
+      <c r="D58" s="4" t="n">
+        <v>878447688270</v>
+      </c>
+      <c r="E58" s="4" t="n">
         <v>1384739664586</v>
-      </c>
-      <c r="C58" s="4" t="n">
-        <v>878447688270</v>
-      </c>
-      <c r="D58" s="4" t="n">
-        <v>496359203753</v>
-      </c>
-      <c r="E58" s="4" t="n">
-        <v>316020156985</v>
       </c>
     </row>
     <row r="59">
@@ -1679,16 +1679,16 @@
         </is>
       </c>
       <c r="B59" s="4" t="n">
+        <v>123723915438</v>
+      </c>
+      <c r="C59" s="4" t="n">
+        <v>145714265723</v>
+      </c>
+      <c r="D59" s="4" t="n">
+        <v>183986993939</v>
+      </c>
+      <c r="E59" s="4" t="n">
         <v>231830280548</v>
-      </c>
-      <c r="C59" s="4" t="n">
-        <v>183986993939</v>
-      </c>
-      <c r="D59" s="4" t="n">
-        <v>145714265723</v>
-      </c>
-      <c r="E59" s="4" t="n">
-        <v>123723915438</v>
       </c>
     </row>
     <row r="60">
@@ -1698,16 +1698,16 @@
         </is>
       </c>
       <c r="B60" s="4" t="n">
+        <v>132305599362</v>
+      </c>
+      <c r="C60" s="4" t="n">
+        <v>136932073861</v>
+      </c>
+      <c r="D60" s="4" t="n">
+        <v>191122324100</v>
+      </c>
+      <c r="E60" s="4" t="n">
         <v>265828841247</v>
-      </c>
-      <c r="C60" s="4" t="n">
-        <v>191122324100</v>
-      </c>
-      <c r="D60" s="4" t="n">
-        <v>136932073861</v>
-      </c>
-      <c r="E60" s="4" t="n">
-        <v>132305599362</v>
       </c>
     </row>
     <row r="61">
@@ -1755,16 +1755,16 @@
         </is>
       </c>
       <c r="B63" s="4" t="n">
+        <v>121870618991</v>
+      </c>
+      <c r="C63" s="4" t="n">
+        <v>119141014630</v>
+      </c>
+      <c r="D63" s="4" t="n">
+        <v>174100135424</v>
+      </c>
+      <c r="E63" s="4" t="n">
         <v>120138271307</v>
-      </c>
-      <c r="C63" s="4" t="n">
-        <v>174100135424</v>
-      </c>
-      <c r="D63" s="4" t="n">
-        <v>119141014630</v>
-      </c>
-      <c r="E63" s="4" t="n">
-        <v>121870618991</v>
       </c>
     </row>
     <row r="64">
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="B65" s="4" t="n">
-        <v>290000000</v>
+        <v>350000000</v>
       </c>
       <c r="C65" s="4" t="n">
         <v>290000000</v>
@@ -1802,7 +1802,7 @@
         <v>290000000</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>350000000</v>
+        <v>290000000</v>
       </c>
     </row>
     <row r="66">
@@ -1812,16 +1812,16 @@
         </is>
       </c>
       <c r="B66" s="4" t="n">
+        <v>1723696182693</v>
+      </c>
+      <c r="C66" s="4" t="n">
+        <v>961830874543</v>
+      </c>
+      <c r="D66" s="4" t="n">
+        <v>1012893977745</v>
+      </c>
+      <c r="E66" s="4" t="n">
         <v>1515744535819</v>
-      </c>
-      <c r="C66" s="4" t="n">
-        <v>1012893977745</v>
-      </c>
-      <c r="D66" s="4" t="n">
-        <v>961830874543</v>
-      </c>
-      <c r="E66" s="4" t="n">
-        <v>1723696182693</v>
       </c>
     </row>
     <row r="67">
@@ -1964,16 +1964,16 @@
         </is>
       </c>
       <c r="B74" s="4" t="n">
+        <v>15031084236</v>
+      </c>
+      <c r="C74" s="4" t="n">
+        <v>6030077736</v>
+      </c>
+      <c r="D74" s="4" t="n">
+        <v>6512947402</v>
+      </c>
+      <c r="E74" s="4" t="n">
         <v>5743148982</v>
-      </c>
-      <c r="C74" s="4" t="n">
-        <v>6512947402</v>
-      </c>
-      <c r="D74" s="4" t="n">
-        <v>6030077736</v>
-      </c>
-      <c r="E74" s="4" t="n">
-        <v>15031084236</v>
       </c>
     </row>
     <row r="75">
@@ -2002,16 +2002,16 @@
         </is>
       </c>
       <c r="B76" s="4" t="n">
+        <v>10989258207900</v>
+      </c>
+      <c r="C76" s="4" t="n">
+        <v>23629506587288</v>
+      </c>
+      <c r="D76" s="4" t="n">
+        <v>26296972276678</v>
+      </c>
+      <c r="E76" s="4" t="n">
         <v>44099580183375</v>
-      </c>
-      <c r="C76" s="4" t="n">
-        <v>26296972276678</v>
-      </c>
-      <c r="D76" s="4" t="n">
-        <v>23629506587288</v>
-      </c>
-      <c r="E76" s="4" t="n">
-        <v>10989258207900</v>
       </c>
     </row>
     <row r="77">
@@ -2021,16 +2021,16 @@
         </is>
       </c>
       <c r="B77" s="4" t="n">
+        <v>1126140700000</v>
+      </c>
+      <c r="C77" s="4" t="n">
+        <v>2176994200000</v>
+      </c>
+      <c r="D77" s="4" t="n">
+        <v>19613221200000</v>
+      </c>
+      <c r="E77" s="4" t="n">
         <v>23113080210000</v>
-      </c>
-      <c r="C77" s="4" t="n">
-        <v>19613221200000</v>
-      </c>
-      <c r="D77" s="4" t="n">
-        <v>2176994200000</v>
-      </c>
-      <c r="E77" s="4" t="n">
-        <v>1126140700000</v>
       </c>
     </row>
     <row r="78">
@@ -2040,16 +2040,16 @@
         </is>
       </c>
       <c r="B78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" s="4" t="n">
+        <v>9191910000000</v>
+      </c>
+      <c r="D78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="4" t="n">
         <v>8606980418518</v>
-      </c>
-      <c r="C78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D78" s="4" t="n">
-        <v>9191910000000</v>
-      </c>
-      <c r="E78" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -2097,16 +2097,16 @@
         </is>
       </c>
       <c r="B81" s="4" t="n">
+        <v>-10561943926</v>
+      </c>
+      <c r="C81" s="4" t="n">
+        <v>-16520032167</v>
+      </c>
+      <c r="D81" s="4" t="n">
+        <v>-4961252868</v>
+      </c>
+      <c r="E81" s="4" t="n">
         <v>7475370203</v>
-      </c>
-      <c r="C81" s="4" t="n">
-        <v>-4961252868</v>
-      </c>
-      <c r="D81" s="4" t="n">
-        <v>-16520032167</v>
-      </c>
-      <c r="E81" s="4" t="n">
-        <v>-10561943926</v>
       </c>
     </row>
     <row r="82">
@@ -2192,16 +2192,16 @@
         </is>
       </c>
       <c r="B86" s="4" t="n">
+        <v>9873679451826</v>
+      </c>
+      <c r="C86" s="4" t="n">
+        <v>12277122419455</v>
+      </c>
+      <c r="D86" s="4" t="n">
+        <v>6688712329546</v>
+      </c>
+      <c r="E86" s="4" t="n">
         <v>12372044184654</v>
-      </c>
-      <c r="C86" s="4" t="n">
-        <v>6688712329546</v>
-      </c>
-      <c r="D86" s="4" t="n">
-        <v>12277122419455</v>
-      </c>
-      <c r="E86" s="4" t="n">
-        <v>9873679451826</v>
       </c>
     </row>
     <row r="87">
@@ -2287,16 +2287,16 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
+        <v>26091547738863</v>
+      </c>
+      <c r="C91" s="4" t="n">
+        <v>43788429454609</v>
+      </c>
+      <c r="D91" s="4" t="n">
+        <v>53244133820194</v>
+      </c>
+      <c r="E91" s="4" t="n">
         <v>80632256999009</v>
-      </c>
-      <c r="C91" s="4" t="n">
-        <v>53244133820194</v>
-      </c>
-      <c r="D91" s="4" t="n">
-        <v>43788429454609</v>
-      </c>
-      <c r="E91" s="4" t="n">
-        <v>26091547738863</v>
       </c>
     </row>
     <row r="92">
@@ -2305,10 +2305,10 @@
           <t>Cổ phiếu ưu đãi</t>
         </is>
       </c>
-      <c r="B92" s="4" t="inlineStr"/>
-      <c r="C92" s="4" t="inlineStr"/>
-      <c r="D92" s="4" t="inlineStr"/>
-      <c r="E92" s="4" t="inlineStr"/>
+      <c r="B92" s="4" t="n"/>
+      <c r="C92" s="4" t="n"/>
+      <c r="D92" s="4" t="n"/>
+      <c r="E92" s="4" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
@@ -2317,16 +2317,16 @@
         </is>
       </c>
       <c r="B93" s="4" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="C93" s="4" t="n">
+        <v>1292046000000</v>
+      </c>
+      <c r="D93" s="4" t="n">
+        <v>2232105785348</v>
+      </c>
+      <c r="E93" s="4" t="n">
         <v>3657418739619</v>
-      </c>
-      <c r="C93" s="4" t="n">
-        <v>2232105785348</v>
-      </c>
-      <c r="D93" s="4" t="n">
-        <v>1292046000000</v>
-      </c>
-      <c r="E93" s="4" t="n">
-        <v>1000000000</v>
       </c>
     </row>
     <row r="94">
@@ -2374,16 +2374,16 @@
         </is>
       </c>
       <c r="B96" s="4" t="n">
+        <v>5305624911458</v>
+      </c>
+      <c r="C96" s="4" t="n">
+        <v>31649585853</v>
+      </c>
+      <c r="D96" s="4" t="n">
+        <v>30358344178</v>
+      </c>
+      <c r="E96" s="4" t="n">
         <v>51121802352</v>
-      </c>
-      <c r="C96" s="4" t="n">
-        <v>30358344178</v>
-      </c>
-      <c r="D96" s="4" t="n">
-        <v>31649585853</v>
-      </c>
-      <c r="E96" s="4" t="n">
-        <v>5305624911458</v>
       </c>
     </row>
     <row r="97">
@@ -2545,16 +2545,16 @@
         </is>
       </c>
       <c r="B105" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" s="4" t="n">
+        <v>2657487551</v>
+      </c>
+      <c r="D105" s="4" t="n">
+        <v>8471319232</v>
+      </c>
+      <c r="E105" s="4" t="n">
         <v>53765213326</v>
-      </c>
-      <c r="C105" s="4" t="n">
-        <v>8471319232</v>
-      </c>
-      <c r="D105" s="4" t="n">
-        <v>2657487551</v>
-      </c>
-      <c r="E105" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -2602,16 +2602,16 @@
         </is>
       </c>
       <c r="B108" s="4" t="n">
+        <v>266845205536</v>
+      </c>
+      <c r="C108" s="4" t="n">
+        <v>203693703731</v>
+      </c>
+      <c r="D108" s="4" t="n">
+        <v>251238807204</v>
+      </c>
+      <c r="E108" s="4" t="n">
         <v>375518055392</v>
-      </c>
-      <c r="C108" s="4" t="n">
-        <v>251238807204</v>
-      </c>
-      <c r="D108" s="4" t="n">
-        <v>203693703731</v>
-      </c>
-      <c r="E108" s="4" t="n">
-        <v>266845205536</v>
       </c>
     </row>
     <row r="109">
@@ -2754,16 +2754,16 @@
         </is>
       </c>
       <c r="B116" s="4" t="n">
+        <v>1126140700000</v>
+      </c>
+      <c r="C116" s="4" t="n">
+        <v>2176994200000</v>
+      </c>
+      <c r="D116" s="4" t="n">
+        <v>19613221200000</v>
+      </c>
+      <c r="E116" s="4" t="n">
         <v>23113080210000</v>
-      </c>
-      <c r="C116" s="4" t="n">
-        <v>19613221200000</v>
-      </c>
-      <c r="D116" s="4" t="n">
-        <v>2176994200000</v>
-      </c>
-      <c r="E116" s="4" t="n">
-        <v>1126140700000</v>
       </c>
     </row>
     <row r="117">
@@ -2811,16 +2811,16 @@
         </is>
       </c>
       <c r="B119" s="4" t="n">
+        <v>9872987551840</v>
+      </c>
+      <c r="C119" s="4" t="n">
+        <v>12257063891765</v>
+      </c>
+      <c r="D119" s="4" t="n">
+        <v>6665324621285</v>
+      </c>
+      <c r="E119" s="4" t="n">
         <v>12347939323386</v>
-      </c>
-      <c r="C119" s="4" t="n">
-        <v>6665324621285</v>
-      </c>
-      <c r="D119" s="4" t="n">
-        <v>12257063891765</v>
-      </c>
-      <c r="E119" s="4" t="n">
-        <v>9872987551840</v>
       </c>
     </row>
     <row r="120">
@@ -2830,16 +2830,16 @@
         </is>
       </c>
       <c r="B120" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="4" t="n">
+        <v>2657487551</v>
+      </c>
+      <c r="D120" s="4" t="n">
+        <v>8471319232</v>
+      </c>
+      <c r="E120" s="4" t="n">
         <v>53765213326</v>
-      </c>
-      <c r="C120" s="4" t="n">
-        <v>8471319232</v>
-      </c>
-      <c r="D120" s="4" t="n">
-        <v>2657487551</v>
-      </c>
-      <c r="E120" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -2906,16 +2906,16 @@
         </is>
       </c>
       <c r="B124" s="4" t="n">
+        <v>13106909118</v>
+      </c>
+      <c r="C124" s="4" t="n">
+        <v>16254492342</v>
+      </c>
+      <c r="D124" s="4" t="n">
+        <v>18754492342</v>
+      </c>
+      <c r="E124" s="4" t="n">
         <v>20000000030</v>
-      </c>
-      <c r="C124" s="4" t="n">
-        <v>18754492342</v>
-      </c>
-      <c r="D124" s="4" t="n">
-        <v>16254492342</v>
-      </c>
-      <c r="E124" s="4" t="n">
-        <v>13106909118</v>
       </c>
     </row>
     <row r="125">
@@ -2925,16 +2925,16 @@
         </is>
       </c>
       <c r="B125" s="4" t="n">
+        <v>25929858136745</v>
+      </c>
+      <c r="C125" s="4" t="n">
+        <v>40594155139482</v>
+      </c>
+      <c r="D125" s="4" t="n">
+        <v>49341572003957</v>
+      </c>
+      <c r="E125" s="4" t="n">
         <v>76597293421692</v>
-      </c>
-      <c r="C125" s="4" t="n">
-        <v>49341572003957</v>
-      </c>
-      <c r="D125" s="4" t="n">
-        <v>40594155139482</v>
-      </c>
-      <c r="E125" s="4" t="n">
-        <v>25929858136745</v>
       </c>
     </row>
     <row r="126">
@@ -2944,16 +2944,16 @@
         </is>
       </c>
       <c r="B126" s="4" t="n">
+        <v>9354605486589</v>
+      </c>
+      <c r="C126" s="4" t="n">
+        <v>16619167038247</v>
+      </c>
+      <c r="D126" s="4" t="n">
+        <v>25911246001189</v>
+      </c>
+      <c r="E126" s="4" t="n">
         <v>43859732477143</v>
-      </c>
-      <c r="C126" s="4" t="n">
-        <v>25911246001189</v>
-      </c>
-      <c r="D126" s="4" t="n">
-        <v>16619167038247</v>
-      </c>
-      <c r="E126" s="4" t="n">
-        <v>9354605486589</v>
       </c>
     </row>
     <row r="127">
@@ -2963,16 +2963,16 @@
         </is>
       </c>
       <c r="B127" s="4" t="n">
+        <v>10511124650851</v>
+      </c>
+      <c r="C127" s="4" t="n">
+        <v>15040774984321</v>
+      </c>
+      <c r="D127" s="4" t="n">
+        <v>17670549755100</v>
+      </c>
+      <c r="E127" s="4" t="n">
         <v>25218442812696</v>
-      </c>
-      <c r="C127" s="4" t="n">
-        <v>17670549755100</v>
-      </c>
-      <c r="D127" s="4" t="n">
-        <v>15040774984321</v>
-      </c>
-      <c r="E127" s="4" t="n">
-        <v>10511124650851</v>
       </c>
     </row>
     <row r="128">
@@ -2982,16 +2982,16 @@
         </is>
       </c>
       <c r="B128" s="4" t="n">
+        <v>183085158587</v>
+      </c>
+      <c r="C128" s="4" t="n">
+        <v>337852529010</v>
+      </c>
+      <c r="D128" s="4" t="n">
+        <v>539116528852</v>
+      </c>
+      <c r="E128" s="4" t="n">
         <v>686848052984</v>
-      </c>
-      <c r="C128" s="4" t="n">
-        <v>539116528852</v>
-      </c>
-      <c r="D128" s="4" t="n">
-        <v>337852529010</v>
-      </c>
-      <c r="E128" s="4" t="n">
-        <v>183085158587</v>
       </c>
     </row>
     <row r="129">
@@ -3001,16 +3001,16 @@
         </is>
       </c>
       <c r="B129" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C129" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D129" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E129" s="4" t="n">
         <v>195489000</v>
-      </c>
-      <c r="C129" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D129" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E129" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -3020,16 +3020,16 @@
         </is>
       </c>
       <c r="B130" s="4" t="n">
+        <v>183085158587</v>
+      </c>
+      <c r="C130" s="4" t="n">
+        <v>337852529010</v>
+      </c>
+      <c r="D130" s="4" t="n">
+        <v>539116528852</v>
+      </c>
+      <c r="E130" s="4" t="n">
         <v>686652563984</v>
-      </c>
-      <c r="C130" s="4" t="n">
-        <v>539116528852</v>
-      </c>
-      <c r="D130" s="4" t="n">
-        <v>337852529010</v>
-      </c>
-      <c r="E130" s="4" t="n">
-        <v>183085158587</v>
       </c>
     </row>
     <row r="131">
@@ -3039,16 +3039,16 @@
         </is>
       </c>
       <c r="B131" s="4" t="n">
+        <v>26781966648</v>
+      </c>
+      <c r="C131" s="4" t="n">
+        <v>2693396029</v>
+      </c>
+      <c r="D131" s="4" t="n">
+        <v>4752786</v>
+      </c>
+      <c r="E131" s="4" t="n">
         <v>1200000</v>
-      </c>
-      <c r="C131" s="4" t="n">
-        <v>4752786</v>
-      </c>
-      <c r="D131" s="4" t="n">
-        <v>2693396029</v>
-      </c>
-      <c r="E131" s="4" t="n">
-        <v>26781966648</v>
       </c>
     </row>
     <row r="132">
@@ -3077,16 +3077,16 @@
         </is>
       </c>
       <c r="B133" s="4" t="n">
+        <v>156303191939</v>
+      </c>
+      <c r="C133" s="4" t="n">
+        <v>335159132981</v>
+      </c>
+      <c r="D133" s="4" t="n">
+        <v>539111776066</v>
+      </c>
+      <c r="E133" s="4" t="n">
         <v>686651363984</v>
-      </c>
-      <c r="C133" s="4" t="n">
-        <v>539111776066</v>
-      </c>
-      <c r="D133" s="4" t="n">
-        <v>335159132981</v>
-      </c>
-      <c r="E133" s="4" t="n">
-        <v>156303191939</v>
       </c>
     </row>
     <row r="134">
@@ -3115,16 +3115,16 @@
         </is>
       </c>
       <c r="B135" s="4" t="n">
+        <v>23877481391</v>
+      </c>
+      <c r="C135" s="4" t="n">
+        <v>16059167017</v>
+      </c>
+      <c r="D135" s="4" t="n">
+        <v>93625988628</v>
+      </c>
+      <c r="E135" s="4" t="n">
         <v>32804970727</v>
-      </c>
-      <c r="C135" s="4" t="n">
-        <v>93625988628</v>
-      </c>
-      <c r="D135" s="4" t="n">
-        <v>16059167017</v>
-      </c>
-      <c r="E135" s="4" t="n">
-        <v>23877481391</v>
       </c>
     </row>
     <row r="136">
@@ -3153,16 +3153,16 @@
         </is>
       </c>
       <c r="B137" s="4" t="n">
+        <v>-266750000</v>
+      </c>
+      <c r="C137" s="4" t="n">
+        <v>-132000000</v>
+      </c>
+      <c r="D137" s="4" t="n">
+        <v>-171600000</v>
+      </c>
+      <c r="E137" s="4" t="n">
         <v>-198000000</v>
-      </c>
-      <c r="C137" s="4" t="n">
-        <v>-171600000</v>
-      </c>
-      <c r="D137" s="4" t="n">
-        <v>-132000000</v>
-      </c>
-      <c r="E137" s="4" t="n">
-        <v>-266750000</v>
       </c>
     </row>
     <row r="138">
@@ -3172,16 +3172,16 @@
         </is>
       </c>
       <c r="B138" s="4" t="n">
+        <v>11248150250</v>
+      </c>
+      <c r="C138" s="4" t="n">
+        <v>75000000</v>
+      </c>
+      <c r="D138" s="4" t="n">
+        <v>219400000</v>
+      </c>
+      <c r="E138" s="4" t="n">
         <v>410200000</v>
-      </c>
-      <c r="C138" s="4" t="n">
-        <v>219400000</v>
-      </c>
-      <c r="D138" s="4" t="n">
-        <v>75000000</v>
-      </c>
-      <c r="E138" s="4" t="n">
-        <v>11248150250</v>
       </c>
     </row>
     <row r="139">
@@ -3191,16 +3191,16 @@
         </is>
       </c>
       <c r="B139" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C139" s="4" t="n">
+        <v>246690000</v>
+      </c>
+      <c r="D139" s="4" t="n">
+        <v>259390000</v>
+      </c>
+      <c r="E139" s="4" t="n">
         <v>1640794000</v>
-      </c>
-      <c r="C139" s="4" t="n">
-        <v>259390000</v>
-      </c>
-      <c r="D139" s="4" t="n">
-        <v>246690000</v>
-      </c>
-      <c r="E139" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -3210,16 +3210,16 @@
         </is>
       </c>
       <c r="B140" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C140" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D140" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" s="4" t="n">
         <v>12981358</v>
-      </c>
-      <c r="C140" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D140" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E140" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -3248,16 +3248,16 @@
         </is>
       </c>
       <c r="B142" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C142" s="4" t="n">
+        <v>3033431775000</v>
+      </c>
+      <c r="D142" s="4" t="n">
+        <v>3533431775000</v>
+      </c>
+      <c r="E142" s="4" t="n">
         <v>3610268431824</v>
-      </c>
-      <c r="C142" s="4" t="n">
-        <v>3533431775000</v>
-      </c>
-      <c r="D142" s="4" t="n">
-        <v>3033431775000</v>
-      </c>
-      <c r="E142" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -3343,16 +3343,16 @@
         </is>
       </c>
       <c r="B147" s="4" t="n">
+        <v>184298800</v>
+      </c>
+      <c r="C147" s="4" t="n">
+        <v>189298800</v>
+      </c>
+      <c r="D147" s="4" t="n">
+        <v>195229298800</v>
+      </c>
+      <c r="E147" s="4" t="n">
         <v>183408219803</v>
-      </c>
-      <c r="C147" s="4" t="n">
-        <v>195229298800</v>
-      </c>
-      <c r="D147" s="4" t="n">
-        <v>189298800</v>
-      </c>
-      <c r="E147" s="4" t="n">
-        <v>184298800</v>
       </c>
     </row>
     <row r="148">
@@ -3381,16 +3381,16 @@
         </is>
       </c>
       <c r="B149" s="4" t="n">
+        <v>6871600000000</v>
+      </c>
+      <c r="C149" s="4" t="n">
+        <v>18061885497900</v>
+      </c>
+      <c r="D149" s="4" t="n">
+        <v>20522995942980</v>
+      </c>
+      <c r="E149" s="4" t="n">
         <v>31079695096211</v>
-      </c>
-      <c r="C149" s="4" t="n">
-        <v>20522995942980</v>
-      </c>
-      <c r="D149" s="4" t="n">
-        <v>18061885497900</v>
-      </c>
-      <c r="E149" s="4" t="n">
-        <v>6871600000000</v>
       </c>
     </row>
     <row r="150">
@@ -3457,16 +3457,16 @@
         </is>
       </c>
       <c r="B153" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C153" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D153" s="4" t="n">
+        <v>3574904342006</v>
+      </c>
+      <c r="E153" s="4" t="n">
         <v>1504310847194</v>
-      </c>
-      <c r="C153" s="4" t="n">
-        <v>3574904342006</v>
-      </c>
-      <c r="D153" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E153" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -3514,16 +3514,16 @@
         </is>
       </c>
       <c r="B156" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C156" s="4" t="n">
+        <v>819874627</v>
+      </c>
+      <c r="D156" s="4" t="n">
+        <v>756498450</v>
+      </c>
+      <c r="E156" s="4" t="n">
         <v>1459010095</v>
-      </c>
-      <c r="C156" s="4" t="n">
-        <v>756498450</v>
-      </c>
-      <c r="D156" s="4" t="n">
-        <v>819874627</v>
-      </c>
-      <c r="E156" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="157">
@@ -3609,16 +3609,16 @@
         </is>
       </c>
       <c r="B161" s="4" t="n">
+        <v>1708634544957</v>
+      </c>
+      <c r="C161" s="4" t="n">
+        <v>955770243307</v>
+      </c>
+      <c r="D161" s="4" t="n">
+        <v>1006350476843</v>
+      </c>
+      <c r="E161" s="4" t="n">
         <v>1509970833337</v>
-      </c>
-      <c r="C161" s="4" t="n">
-        <v>1006350476843</v>
-      </c>
-      <c r="D161" s="4" t="n">
-        <v>955770243307</v>
-      </c>
-      <c r="E161" s="4" t="n">
-        <v>1708634544957</v>
       </c>
     </row>
     <row r="162">
@@ -3647,16 +3647,16 @@
         </is>
       </c>
       <c r="B163" s="4" t="n">
+        <v>1126140700000</v>
+      </c>
+      <c r="C163" s="4" t="n">
+        <v>11368904200000</v>
+      </c>
+      <c r="D163" s="4" t="n">
+        <v>19613221200000</v>
+      </c>
+      <c r="E163" s="4" t="n">
         <v>31720060628518</v>
-      </c>
-      <c r="C163" s="4" t="n">
-        <v>19613221200000</v>
-      </c>
-      <c r="D163" s="4" t="n">
-        <v>11368904200000</v>
-      </c>
-      <c r="E163" s="4" t="n">
-        <v>1126140700000</v>
       </c>
     </row>
     <row r="164">
@@ -3685,16 +3685,16 @@
         </is>
       </c>
       <c r="B165" s="4" t="n">
+        <v>9872987551840</v>
+      </c>
+      <c r="C165" s="4" t="n">
+        <v>12257063891765</v>
+      </c>
+      <c r="D165" s="4" t="n">
+        <v>6665324621285</v>
+      </c>
+      <c r="E165" s="4" t="n">
         <v>12347939323386</v>
-      </c>
-      <c r="C165" s="4" t="n">
-        <v>6665324621285</v>
-      </c>
-      <c r="D165" s="4" t="n">
-        <v>12257063891765</v>
-      </c>
-      <c r="E165" s="4" t="n">
-        <v>9872987551840</v>
       </c>
     </row>
     <row r="166">
@@ -3704,16 +3704,16 @@
         </is>
       </c>
       <c r="B166" s="4" t="n">
+        <v>691899986</v>
+      </c>
+      <c r="C166" s="4" t="n">
+        <v>20058527690</v>
+      </c>
+      <c r="D166" s="4" t="n">
+        <v>23387708261</v>
+      </c>
+      <c r="E166" s="4" t="n">
         <v>24104861268</v>
-      </c>
-      <c r="C166" s="4" t="n">
-        <v>23387708261</v>
-      </c>
-      <c r="D166" s="4" t="n">
-        <v>20058527690</v>
-      </c>
-      <c r="E166" s="4" t="n">
-        <v>691899986</v>
       </c>
     </row>
     <row r="167">
@@ -3818,16 +3818,16 @@
         </is>
       </c>
       <c r="B172" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C172" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D172" s="4" t="n">
+        <v>1961322120</v>
+      </c>
+      <c r="E172" s="4" t="n">
         <v>2311308021</v>
-      </c>
-      <c r="C172" s="4" t="n">
-        <v>1961322120</v>
-      </c>
-      <c r="D172" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E172" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="173">
@@ -3856,16 +3856,16 @@
         </is>
       </c>
       <c r="B174" s="4" t="n">
+        <v>843650040000</v>
+      </c>
+      <c r="C174" s="4" t="n">
+        <v>1634479940000</v>
+      </c>
+      <c r="D174" s="4" t="n">
+        <v>17055403900000</v>
+      </c>
+      <c r="E174" s="4" t="n">
         <v>22556742060000</v>
-      </c>
-      <c r="C174" s="4" t="n">
-        <v>17055403900000</v>
-      </c>
-      <c r="D174" s="4" t="n">
-        <v>1634479940000</v>
-      </c>
-      <c r="E174" s="4" t="n">
-        <v>843650040000</v>
       </c>
     </row>
     <row r="175">
@@ -3875,16 +3875,16 @@
         </is>
       </c>
       <c r="B175" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C175" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D175" s="4" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E175" s="4" t="n">
         <v>2720000</v>
-      </c>
-      <c r="C175" s="4" t="n">
-        <v>20000</v>
-      </c>
-      <c r="D175" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="E175" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="176">
@@ -3894,16 +3894,16 @@
         </is>
       </c>
       <c r="B176" s="4" t="n">
+        <v>9799131256</v>
+      </c>
+      <c r="C176" s="4" t="n">
+        <v>23749500000</v>
+      </c>
+      <c r="D176" s="4" t="n">
+        <v>7282100000</v>
+      </c>
+      <c r="E176" s="4" t="n">
         <v>1860100000</v>
-      </c>
-      <c r="C176" s="4" t="n">
-        <v>7282100000</v>
-      </c>
-      <c r="D176" s="4" t="n">
-        <v>23749500000</v>
-      </c>
-      <c r="E176" s="4" t="n">
-        <v>9799131256</v>
       </c>
     </row>
     <row r="177">
@@ -3932,16 +3932,16 @@
         </is>
       </c>
       <c r="B178" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C178" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D178" s="4" t="n">
+        <v>18786720000</v>
+      </c>
+      <c r="E178" s="4" t="n">
         <v>1230262890000</v>
-      </c>
-      <c r="C178" s="4" t="n">
-        <v>18786720000</v>
-      </c>
-      <c r="D178" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E178" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="179">
@@ -3970,16 +3970,16 @@
         </is>
       </c>
       <c r="B180" s="4" t="n">
+        <v>146560432630000</v>
+      </c>
+      <c r="C180" s="4" t="n">
+        <v>143415009129900</v>
+      </c>
+      <c r="D180" s="4" t="n">
+        <v>231123600446000</v>
+      </c>
+      <c r="E180" s="4" t="n">
         <v>325307278790000</v>
-      </c>
-      <c r="C180" s="4" t="n">
-        <v>231123600446000</v>
-      </c>
-      <c r="D180" s="4" t="n">
-        <v>143415009129900</v>
-      </c>
-      <c r="E180" s="4" t="n">
-        <v>146560432630000</v>
       </c>
     </row>
     <row r="181">
@@ -3989,16 +3989,16 @@
         </is>
       </c>
       <c r="B181" s="4" t="n">
+        <v>84523895380000</v>
+      </c>
+      <c r="C181" s="4" t="n">
+        <v>77561084029900</v>
+      </c>
+      <c r="D181" s="4" t="n">
+        <v>141951366816000</v>
+      </c>
+      <c r="E181" s="4" t="n">
         <v>240019596860000</v>
-      </c>
-      <c r="C181" s="4" t="n">
-        <v>141951366816000</v>
-      </c>
-      <c r="D181" s="4" t="n">
-        <v>77561084029900</v>
-      </c>
-      <c r="E181" s="4" t="n">
-        <v>84523895380000</v>
       </c>
     </row>
     <row r="182">
@@ -4008,16 +4008,16 @@
         </is>
       </c>
       <c r="B182" s="4" t="n">
+        <v>139546850000</v>
+      </c>
+      <c r="C182" s="4" t="n">
+        <v>314582980000</v>
+      </c>
+      <c r="D182" s="4" t="n">
+        <v>1013558230000</v>
+      </c>
+      <c r="E182" s="4" t="n">
         <v>1467945100000</v>
-      </c>
-      <c r="C182" s="4" t="n">
-        <v>1013558230000</v>
-      </c>
-      <c r="D182" s="4" t="n">
-        <v>314582980000</v>
-      </c>
-      <c r="E182" s="4" t="n">
-        <v>139546850000</v>
       </c>
     </row>
     <row r="183">
@@ -4027,16 +4027,16 @@
         </is>
       </c>
       <c r="B183" s="4" t="n">
+        <v>60455199550000</v>
+      </c>
+      <c r="C183" s="4" t="n">
+        <v>62731799490000</v>
+      </c>
+      <c r="D183" s="4" t="n">
+        <v>72409443760000</v>
+      </c>
+      <c r="E183" s="4" t="n">
         <v>56063707010000</v>
-      </c>
-      <c r="C183" s="4" t="n">
-        <v>72409443760000</v>
-      </c>
-      <c r="D183" s="4" t="n">
-        <v>62731799490000</v>
-      </c>
-      <c r="E183" s="4" t="n">
-        <v>60455199550000</v>
       </c>
     </row>
     <row r="184">
@@ -4046,16 +4046,16 @@
         </is>
       </c>
       <c r="B184" s="4" t="n">
+        <v>735109450000</v>
+      </c>
+      <c r="C184" s="4" t="n">
+        <v>1862706260000</v>
+      </c>
+      <c r="D184" s="4" t="n">
+        <v>15028179710000</v>
+      </c>
+      <c r="E184" s="4" t="n">
         <v>26601662760000</v>
-      </c>
-      <c r="C184" s="4" t="n">
-        <v>15028179710000</v>
-      </c>
-      <c r="D184" s="4" t="n">
-        <v>1862706260000</v>
-      </c>
-      <c r="E184" s="4" t="n">
-        <v>735109450000</v>
       </c>
     </row>
     <row r="185">
@@ -4065,16 +4065,16 @@
         </is>
       </c>
       <c r="B185" s="4" t="n">
+        <v>706681400000</v>
+      </c>
+      <c r="C185" s="4" t="n">
+        <v>944836370000</v>
+      </c>
+      <c r="D185" s="4" t="n">
+        <v>721051930000</v>
+      </c>
+      <c r="E185" s="4" t="n">
         <v>1154367060000</v>
-      </c>
-      <c r="C185" s="4" t="n">
-        <v>721051930000</v>
-      </c>
-      <c r="D185" s="4" t="n">
-        <v>944836370000</v>
-      </c>
-      <c r="E185" s="4" t="n">
-        <v>706681400000</v>
       </c>
     </row>
     <row r="186">
@@ -4103,16 +4103,16 @@
         </is>
       </c>
       <c r="B187" s="4" t="n">
+        <v>719450400000</v>
+      </c>
+      <c r="C187" s="4" t="n">
+        <v>472237200000</v>
+      </c>
+      <c r="D187" s="4" t="n">
+        <v>348405300000</v>
+      </c>
+      <c r="E187" s="4" t="n">
         <v>192827990000</v>
-      </c>
-      <c r="C187" s="4" t="n">
-        <v>348405300000</v>
-      </c>
-      <c r="D187" s="4" t="n">
-        <v>472237200000</v>
-      </c>
-      <c r="E187" s="4" t="n">
-        <v>719450400000</v>
       </c>
     </row>
     <row r="188">
@@ -4122,16 +4122,16 @@
         </is>
       </c>
       <c r="B188" s="4" t="n">
+        <v>634486460000</v>
+      </c>
+      <c r="C188" s="4" t="n">
+        <v>417620180000</v>
+      </c>
+      <c r="D188" s="4" t="n">
+        <v>132398410000</v>
+      </c>
+      <c r="E188" s="4" t="n">
         <v>174185350000</v>
-      </c>
-      <c r="C188" s="4" t="n">
-        <v>132398410000</v>
-      </c>
-      <c r="D188" s="4" t="n">
-        <v>417620180000</v>
-      </c>
-      <c r="E188" s="4" t="n">
-        <v>634486460000</v>
       </c>
     </row>
     <row r="189">
@@ -4141,16 +4141,16 @@
         </is>
       </c>
       <c r="B189" s="4" t="n">
+        <v>84963940000</v>
+      </c>
+      <c r="C189" s="4" t="n">
+        <v>54617020000</v>
+      </c>
+      <c r="D189" s="4" t="n">
+        <v>216006890000</v>
+      </c>
+      <c r="E189" s="4" t="n">
         <v>18642640000</v>
-      </c>
-      <c r="C189" s="4" t="n">
-        <v>216006890000</v>
-      </c>
-      <c r="D189" s="4" t="n">
-        <v>54617020000</v>
-      </c>
-      <c r="E189" s="4" t="n">
-        <v>84963940000</v>
       </c>
     </row>
     <row r="190">
@@ -4198,16 +4198,16 @@
         </is>
       </c>
       <c r="B192" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C192" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D192" s="4" t="n">
+        <v>875589460000</v>
+      </c>
+      <c r="E192" s="4" t="n">
         <v>1291904460000</v>
-      </c>
-      <c r="C192" s="4" t="n">
-        <v>875589460000</v>
-      </c>
-      <c r="D192" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E192" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="193">
@@ -4236,16 +4236,16 @@
         </is>
       </c>
       <c r="B194" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C194" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D194" s="4" t="n">
+        <v>15338753340000</v>
+      </c>
+      <c r="E194" s="4" t="n">
         <v>9407201530000</v>
-      </c>
-      <c r="C194" s="4" t="n">
-        <v>15338753340000</v>
-      </c>
-      <c r="D194" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E194" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="195">
@@ -4274,16 +4274,16 @@
         </is>
       </c>
       <c r="B196" s="4" t="n">
+        <v>2330045069459</v>
+      </c>
+      <c r="C196" s="4" t="n">
+        <v>5774724796539</v>
+      </c>
+      <c r="D196" s="4" t="n">
+        <v>10024246349048</v>
+      </c>
+      <c r="E196" s="4" t="n">
         <v>10702593296252</v>
-      </c>
-      <c r="C196" s="4" t="n">
-        <v>10024246349048</v>
-      </c>
-      <c r="D196" s="4" t="n">
-        <v>5774724796539</v>
-      </c>
-      <c r="E196" s="4" t="n">
-        <v>2330045069459</v>
       </c>
     </row>
     <row r="197">
@@ -4293,16 +4293,16 @@
         </is>
       </c>
       <c r="B197" s="4" t="n">
+        <v>2278125882711</v>
+      </c>
+      <c r="C197" s="4" t="n">
+        <v>2945784273957</v>
+      </c>
+      <c r="D197" s="4" t="n">
+        <v>8245482244688</v>
+      </c>
+      <c r="E197" s="4" t="n">
         <v>6447211380125</v>
-      </c>
-      <c r="C197" s="4" t="n">
-        <v>8245482244688</v>
-      </c>
-      <c r="D197" s="4" t="n">
-        <v>2945784273957</v>
-      </c>
-      <c r="E197" s="4" t="n">
-        <v>2278125882711</v>
       </c>
     </row>
     <row r="198">
@@ -4521,16 +4521,16 @@
         </is>
       </c>
       <c r="B209" s="4" t="n">
+        <v>51919186748</v>
+      </c>
+      <c r="C209" s="4" t="n">
+        <v>1031489346567</v>
+      </c>
+      <c r="D209" s="4" t="n">
+        <v>44613698630</v>
+      </c>
+      <c r="E209" s="4" t="n">
         <v>49373986618</v>
-      </c>
-      <c r="C209" s="4" t="n">
-        <v>44613698630</v>
-      </c>
-      <c r="D209" s="4" t="n">
-        <v>1031489346567</v>
-      </c>
-      <c r="E209" s="4" t="n">
-        <v>51919186748</v>
       </c>
     </row>
   </sheetData>
@@ -4547,11 +4547,11 @@
   <dimension ref="A1:E80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="114" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4562,22 +4562,22 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>2025</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>2022</t>
         </is>
       </c>
     </row>
@@ -4588,16 +4588,16 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
+        <v>5218182207076</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>5257070533399</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>7615253240537</v>
+      </c>
+      <c r="E2" s="4" t="n">
         <v>11217426514650</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>7615253240537</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>5257070533399</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>5218182207076</v>
       </c>
     </row>
     <row r="3">
@@ -4626,16 +4626,16 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
+        <v>5218182207076</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>5257070533399</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>7615253240537</v>
+      </c>
+      <c r="E4" s="4" t="n">
         <v>11217426514650</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>7615253240537</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>5257070533399</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>5218182207076</v>
       </c>
     </row>
     <row r="5">
@@ -4645,16 +4645,16 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
+        <v>-990754662144</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>-664101469631</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>-695459394838</v>
+      </c>
+      <c r="E5" s="4" t="n">
         <v>-1213554689735</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>-695459394838</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>-664101469631</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>-990754662144</v>
       </c>
     </row>
     <row r="6">
@@ -4664,16 +4664,16 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
+        <v>4227427544932</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>4592969063768</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>6919793845699</v>
+      </c>
+      <c r="E6" s="4" t="n">
         <v>10003871824915</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>6919793845699</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>4592969063768</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>4227427544932</v>
       </c>
     </row>
     <row r="7">
@@ -4683,16 +4683,16 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
+        <v>-480433213874</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>-500212004426</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>-566893494770</v>
+      </c>
+      <c r="E7" s="4" t="n">
         <v>-658975463710</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>-566893494770</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>-500212004426</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>-480433213874</v>
       </c>
     </row>
     <row r="8">
@@ -4702,16 +4702,16 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
+        <v>3033107909184</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>3029925582883</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>4802352563838</v>
+      </c>
+      <c r="E8" s="4" t="n">
         <v>7109123949934</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>4802352563838</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>3029925582883</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>3033107909184</v>
       </c>
     </row>
     <row r="9">
@@ -4721,16 +4721,16 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
+        <v>3057657087640</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>3028297410899</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>4802105868186</v>
+      </c>
+      <c r="E9" s="4" t="n">
         <v>7108700741609</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>4802105868186</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>3028297410899</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>3057657087640</v>
       </c>
     </row>
     <row r="10">
@@ -4740,16 +4740,16 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
+        <v>-631684895743</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>-626761513445</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>-955991010186</v>
+      </c>
+      <c r="E10" s="4" t="n">
         <v>-1422857625411</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>-955991010186</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>-626761513445</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>-631684895743</v>
       </c>
     </row>
     <row r="11">
@@ -4759,16 +4759,16 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
+        <v>691899986</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>1907070175</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>3580065571</v>
+      </c>
+      <c r="E11" s="4" t="n">
         <v>-2514261090</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>3580065571</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>1907070175</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>691899986</v>
       </c>
     </row>
     <row r="12">
@@ -4778,16 +4778,16 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
+        <v>2426664091883</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>2403442967629</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>3849694923571</v>
+      </c>
+      <c r="E12" s="4" t="n">
         <v>5683328855108</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>3849694923571</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>2403442967629</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>2426664091883</v>
       </c>
     </row>
     <row r="13">
@@ -4816,16 +4816,16 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
+        <v>2426664091883</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>2403442967629</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>3849694923571</v>
+      </c>
+      <c r="E14" s="4" t="n">
         <v>5683328855108</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>3849694923571</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>2403442967629</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>2426664091883</v>
       </c>
     </row>
     <row r="15">
@@ -4835,16 +4835,16 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
+        <v>21548</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>14119</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>8716</v>
+      </c>
+      <c r="E15" s="4" t="n">
         <v>2713</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>8716</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>14119</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>21548</v>
       </c>
     </row>
     <row r="16">
@@ -4873,16 +4873,16 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
+        <v>888247795556</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>476833068936</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>600923377250</v>
+      </c>
+      <c r="E17" s="4" t="n">
         <v>957608985434</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>600923377250</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>476833068936</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>888247795556</v>
       </c>
     </row>
     <row r="18">
@@ -4911,16 +4911,16 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
+        <v>1302953436567</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>944470298386</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>1180992811061</v>
+      </c>
+      <c r="E19" s="4" t="n">
         <v>1715251565918</v>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>1180992811061</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>944470298386</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>1302953436567</v>
       </c>
     </row>
     <row r="20">
@@ -4949,16 +4949,16 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
+        <v>52348947599</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>49528058050</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>50962737249</v>
+      </c>
+      <c r="E21" s="4" t="n">
         <v>109980172740</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>50962737249</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>49528058050</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>52348947599</v>
       </c>
     </row>
     <row r="22">
@@ -5006,16 +5006,16 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
+        <v>137749081244</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>46276350627</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>4185017363</v>
+      </c>
+      <c r="E24" s="4" t="n">
         <v>6603197687</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>4185017363</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>46276350627</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>137749081244</v>
       </c>
     </row>
     <row r="25">
@@ -5044,16 +5044,16 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
+        <v>901204582596</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>1643446234600</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>2449688939032</v>
+      </c>
+      <c r="E26" s="4" t="n">
         <v>3669453931882</v>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>2449688939032</v>
-      </c>
-      <c r="D26" s="4" t="n">
-        <v>1643446234600</v>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>901204582596</v>
       </c>
     </row>
     <row r="27">
@@ -5063,16 +5063,16 @@
         </is>
       </c>
       <c r="B27" s="4" t="n">
+        <v>901204582596</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>1643446234600</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>2448980152070</v>
+      </c>
+      <c r="E27" s="4" t="n">
         <v>3662416587827</v>
-      </c>
-      <c r="C27" s="4" t="n">
-        <v>2448980152070</v>
-      </c>
-      <c r="D27" s="4" t="n">
-        <v>1643446234600</v>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>901204582596</v>
       </c>
     </row>
     <row r="28">
@@ -5082,16 +5082,16 @@
         </is>
       </c>
       <c r="B28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>683706962</v>
+      </c>
+      <c r="E28" s="4" t="n">
         <v>6910975255</v>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>683706962</v>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -5101,16 +5101,16 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>25080000</v>
+      </c>
+      <c r="E29" s="4" t="n">
         <v>126368800</v>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>25080000</v>
-      </c>
-      <c r="D29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -5120,16 +5120,16 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
+        <v>18529621544</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>42491805310</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>110341784335</v>
+      </c>
+      <c r="E30" s="4" t="n">
         <v>180059518864</v>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>110341784335</v>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>42491805310</v>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>18529621544</v>
       </c>
     </row>
     <row r="31">
@@ -5139,16 +5139,16 @@
         </is>
       </c>
       <c r="B31" s="4" t="n">
+        <v>1502853415354</v>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>1602447022922</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>2621919468982</v>
+      </c>
+      <c r="E31" s="4" t="n">
         <v>3727517878641</v>
-      </c>
-      <c r="C31" s="4" t="n">
-        <v>2621919468982</v>
-      </c>
-      <c r="D31" s="4" t="n">
-        <v>1602447022922</v>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>1502853415354</v>
       </c>
     </row>
     <row r="32">
@@ -5158,16 +5158,16 @@
         </is>
       </c>
       <c r="B32" s="4" t="n">
+        <v>257993106848</v>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>370456358951</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>432978205265</v>
+      </c>
+      <c r="E32" s="4" t="n">
         <v>548520255484</v>
-      </c>
-      <c r="C32" s="4" t="n">
-        <v>432978205265</v>
-      </c>
-      <c r="D32" s="4" t="n">
-        <v>370456358951</v>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>257993106848</v>
       </c>
     </row>
     <row r="33">
@@ -5196,16 +5196,16 @@
         </is>
       </c>
       <c r="B34" s="4" t="n">
+        <v>156302219768</v>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>81121335617</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>163260900000</v>
+      </c>
+      <c r="E34" s="4" t="n">
         <v>302431008000</v>
-      </c>
-      <c r="C34" s="4" t="n">
-        <v>163260900000</v>
-      </c>
-      <c r="D34" s="4" t="n">
-        <v>81121335617</v>
-      </c>
-      <c r="E34" s="4" t="n">
-        <v>156302219768</v>
       </c>
     </row>
     <row r="35">
@@ -5215,16 +5215,16 @@
         </is>
       </c>
       <c r="B35" s="4" t="n">
+        <v>-198923624516</v>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>-179035354683</v>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>-204396149905</v>
+      </c>
+      <c r="E35" s="4" t="n">
         <v>-431640082069</v>
-      </c>
-      <c r="C35" s="4" t="n">
-        <v>-204396149905</v>
-      </c>
-      <c r="D35" s="4" t="n">
-        <v>-179035354683</v>
-      </c>
-      <c r="E35" s="4" t="n">
-        <v>-198923624516</v>
       </c>
     </row>
     <row r="36">
@@ -5234,16 +5234,16 @@
         </is>
       </c>
       <c r="B36" s="4" t="n">
+        <v>-198913624516</v>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>-179035354683</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>-204145264905</v>
+      </c>
+      <c r="E36" s="4" t="n">
         <v>-427957520911</v>
-      </c>
-      <c r="C36" s="4" t="n">
-        <v>-204145264905</v>
-      </c>
-      <c r="D36" s="4" t="n">
-        <v>-179035354683</v>
-      </c>
-      <c r="E36" s="4" t="n">
-        <v>-198913624516</v>
       </c>
     </row>
     <row r="37">
@@ -5253,16 +5253,16 @@
         </is>
       </c>
       <c r="B37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>-250885000</v>
+      </c>
+      <c r="E37" s="4" t="n">
         <v>-3682561158</v>
-      </c>
-      <c r="C37" s="4" t="n">
-        <v>-250885000</v>
-      </c>
-      <c r="D37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -5272,7 +5272,7 @@
         </is>
       </c>
       <c r="B38" s="4" t="n">
-        <v>0</v>
+        <v>-10000000</v>
       </c>
       <c r="C38" s="4" t="n">
         <v>0</v>
@@ -5281,7 +5281,7 @@
         <v>0</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>-10000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -5348,16 +5348,16 @@
         </is>
       </c>
       <c r="B42" s="4" t="n">
+        <v>-3599620</v>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>-4771003744</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>-6031468910</v>
+      </c>
+      <c r="E42" s="4" t="n">
         <v>-1951876404</v>
-      </c>
-      <c r="C42" s="4" t="n">
-        <v>-6031468910</v>
-      </c>
-      <c r="D42" s="4" t="n">
-        <v>-4771003744</v>
-      </c>
-      <c r="E42" s="4" t="n">
-        <v>-3599620</v>
       </c>
     </row>
     <row r="43">
@@ -5386,16 +5386,16 @@
         </is>
       </c>
       <c r="B44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="4" t="n">
         <v>-13459159</v>
-      </c>
-      <c r="C44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -5405,16 +5405,16 @@
         </is>
       </c>
       <c r="B45" s="4" t="n">
+        <v>-154528078451</v>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>-183646638072</v>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>-259060189756</v>
+      </c>
+      <c r="E45" s="4" t="n">
         <v>-391454796421</v>
-      </c>
-      <c r="C45" s="4" t="n">
-        <v>-259060189756</v>
-      </c>
-      <c r="D45" s="4" t="n">
-        <v>-183646638072</v>
-      </c>
-      <c r="E45" s="4" t="n">
-        <v>-154528078451</v>
       </c>
     </row>
     <row r="46">
@@ -5424,16 +5424,16 @@
         </is>
       </c>
       <c r="B46" s="4" t="n">
-        <v>0</v>
+        <v>-274074074</v>
       </c>
       <c r="C46" s="4" t="n">
-        <v>0</v>
+        <v>-208000</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>-208000</v>
+        <v>0</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>-274074074</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -5481,16 +5481,16 @@
         </is>
       </c>
       <c r="B49" s="4" t="n">
+        <v>-48078060820</v>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>-43185736098</v>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>-44478890519</v>
+      </c>
+      <c r="E49" s="4" t="n">
         <v>-101719576574</v>
-      </c>
-      <c r="C49" s="4" t="n">
-        <v>-44478890519</v>
-      </c>
-      <c r="D49" s="4" t="n">
-        <v>-43185736098</v>
-      </c>
-      <c r="E49" s="4" t="n">
-        <v>-48078060820</v>
       </c>
     </row>
     <row r="50">
@@ -5519,16 +5519,16 @@
         </is>
       </c>
       <c r="B51" s="4" t="n">
+        <v>-588947224663</v>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>-253462529034</v>
+      </c>
+      <c r="D51" s="4" t="n">
+        <v>-181492695748</v>
+      </c>
+      <c r="E51" s="4" t="n">
         <v>-286774899108</v>
-      </c>
-      <c r="C51" s="4" t="n">
-        <v>-181492695748</v>
-      </c>
-      <c r="D51" s="4" t="n">
-        <v>-253462529034</v>
-      </c>
-      <c r="E51" s="4" t="n">
-        <v>-588947224663</v>
       </c>
     </row>
     <row r="52">
@@ -5557,16 +5557,16 @@
         </is>
       </c>
       <c r="B53" s="4" t="n">
+        <v>24523594439</v>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>18812470414</v>
+      </c>
+      <c r="D53" s="4" t="n">
+        <v>26516220809</v>
+      </c>
+      <c r="E53" s="4" t="n">
         <v>46094785235</v>
-      </c>
-      <c r="C53" s="4" t="n">
-        <v>26516220809</v>
-      </c>
-      <c r="D53" s="4" t="n">
-        <v>18812470414</v>
-      </c>
-      <c r="E53" s="4" t="n">
-        <v>24523594439</v>
       </c>
     </row>
     <row r="54">
@@ -5576,7 +5576,7 @@
         </is>
       </c>
       <c r="B54" s="4" t="n">
-        <v>0</v>
+        <v>14002400000</v>
       </c>
       <c r="C54" s="4" t="n">
         <v>0</v>
@@ -5585,7 +5585,7 @@
         <v>0</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>14002400000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -5595,16 +5595,16 @@
         </is>
       </c>
       <c r="B55" s="4" t="n">
+        <v>10521194439</v>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>12870125334</v>
+      </c>
+      <c r="D55" s="4" t="n">
+        <v>17491002103</v>
+      </c>
+      <c r="E55" s="4" t="n">
         <v>45376233569</v>
-      </c>
-      <c r="C55" s="4" t="n">
-        <v>17491002103</v>
-      </c>
-      <c r="D55" s="4" t="n">
-        <v>12870125334</v>
-      </c>
-      <c r="E55" s="4" t="n">
-        <v>10521194439</v>
       </c>
     </row>
     <row r="56">
@@ -5633,16 +5633,16 @@
         </is>
       </c>
       <c r="B57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="4" t="n">
+        <v>5942345080</v>
+      </c>
+      <c r="D57" s="4" t="n">
+        <v>9025218706</v>
+      </c>
+      <c r="E57" s="4" t="n">
         <v>718551666</v>
-      </c>
-      <c r="C57" s="4" t="n">
-        <v>9025218706</v>
-      </c>
-      <c r="D57" s="4" t="n">
-        <v>5942345080</v>
-      </c>
-      <c r="E57" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -5652,16 +5652,16 @@
         </is>
       </c>
       <c r="B58" s="4" t="n">
+        <v>-738410016313</v>
+      </c>
+      <c r="C58" s="4" t="n">
+        <v>-1081643946873</v>
+      </c>
+      <c r="D58" s="4" t="n">
+        <v>-1577064007900</v>
+      </c>
+      <c r="E58" s="4" t="n">
         <v>-2281867196506</v>
-      </c>
-      <c r="C58" s="4" t="n">
-        <v>-1577064007900</v>
-      </c>
-      <c r="D58" s="4" t="n">
-        <v>-1081643946873</v>
-      </c>
-      <c r="E58" s="4" t="n">
-        <v>-738410016313</v>
       </c>
     </row>
     <row r="59">
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="B59" s="4" t="n">
-        <v>0</v>
+        <v>-1400000000</v>
       </c>
       <c r="C59" s="4" t="n">
         <v>0</v>
@@ -5680,7 +5680,7 @@
         <v>0</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>-1400000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -5690,16 +5690,16 @@
         </is>
       </c>
       <c r="B60" s="4" t="n">
+        <v>-609169047616</v>
+      </c>
+      <c r="C60" s="4" t="n">
+        <v>-893985755421</v>
+      </c>
+      <c r="D60" s="4" t="n">
+        <v>-1471244444534</v>
+      </c>
+      <c r="E60" s="4" t="n">
         <v>-2055011378498</v>
-      </c>
-      <c r="C60" s="4" t="n">
-        <v>-1471244444534</v>
-      </c>
-      <c r="D60" s="4" t="n">
-        <v>-893985755421</v>
-      </c>
-      <c r="E60" s="4" t="n">
-        <v>-609169047616</v>
       </c>
     </row>
     <row r="61">
@@ -5747,16 +5747,16 @@
         </is>
       </c>
       <c r="B63" s="4" t="n">
+        <v>-127840968697</v>
+      </c>
+      <c r="C63" s="4" t="n">
+        <v>-187658191452</v>
+      </c>
+      <c r="D63" s="4" t="n">
+        <v>-105819563366</v>
+      </c>
+      <c r="E63" s="4" t="n">
         <v>-226855818008</v>
-      </c>
-      <c r="C63" s="4" t="n">
-        <v>-105819563366</v>
-      </c>
-      <c r="D63" s="4" t="n">
-        <v>-187658191452</v>
-      </c>
-      <c r="E63" s="4" t="n">
-        <v>-127840968697</v>
       </c>
     </row>
     <row r="64">
@@ -5785,16 +5785,16 @@
         </is>
       </c>
       <c r="B65" s="4" t="n">
+        <v>3057657087640</v>
+      </c>
+      <c r="C65" s="4" t="n">
+        <v>3028297410899</v>
+      </c>
+      <c r="D65" s="4" t="n">
+        <v>4801673046224</v>
+      </c>
+      <c r="E65" s="4" t="n">
         <v>7105472327512</v>
-      </c>
-      <c r="C65" s="4" t="n">
-        <v>4801673046224</v>
-      </c>
-      <c r="D65" s="4" t="n">
-        <v>3028297410899</v>
-      </c>
-      <c r="E65" s="4" t="n">
-        <v>3057657087640</v>
       </c>
     </row>
     <row r="66">
@@ -5804,16 +5804,16 @@
         </is>
       </c>
       <c r="B66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="4" t="n">
+        <v>432821962</v>
+      </c>
+      <c r="E66" s="4" t="n">
         <v>3228414097</v>
-      </c>
-      <c r="C66" s="4" t="n">
-        <v>432821962</v>
-      </c>
-      <c r="D66" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E66" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -5861,16 +5861,16 @@
         </is>
       </c>
       <c r="B69" s="4" t="n">
+        <v>-8596795059</v>
+      </c>
+      <c r="C69" s="4" t="n">
+        <v>-5958088241</v>
+      </c>
+      <c r="D69" s="4" t="n">
+        <v>11558779299</v>
+      </c>
+      <c r="E69" s="4" t="n">
         <v>12436623071</v>
-      </c>
-      <c r="C69" s="4" t="n">
-        <v>11558779299</v>
-      </c>
-      <c r="D69" s="4" t="n">
-        <v>-5958088241</v>
-      </c>
-      <c r="E69" s="4" t="n">
-        <v>-8596795059</v>
       </c>
     </row>
     <row r="70">
@@ -5994,16 +5994,16 @@
         </is>
       </c>
       <c r="B76" s="4" t="n">
+        <v>2418067296824</v>
+      </c>
+      <c r="C76" s="4" t="n">
+        <v>2397484879388</v>
+      </c>
+      <c r="D76" s="4" t="n">
+        <v>3861253702870</v>
+      </c>
+      <c r="E76" s="4" t="n">
         <v>5695765478179</v>
-      </c>
-      <c r="C76" s="4" t="n">
-        <v>3861253702870</v>
-      </c>
-      <c r="D76" s="4" t="n">
-        <v>2397484879388</v>
-      </c>
-      <c r="E76" s="4" t="n">
-        <v>2418067296824</v>
       </c>
     </row>
     <row r="77">
@@ -6013,16 +6013,16 @@
         </is>
       </c>
       <c r="B77" s="4" t="n">
+        <v>2418067296824</v>
+      </c>
+      <c r="C77" s="4" t="n">
+        <v>2397484879388</v>
+      </c>
+      <c r="D77" s="4" t="n">
+        <v>3861253702870</v>
+      </c>
+      <c r="E77" s="4" t="n">
         <v>5695765478179</v>
-      </c>
-      <c r="C77" s="4" t="n">
-        <v>3861253702870</v>
-      </c>
-      <c r="D77" s="4" t="n">
-        <v>2397484879388</v>
-      </c>
-      <c r="E77" s="4" t="n">
-        <v>2418067296824</v>
       </c>
     </row>
     <row r="78">
@@ -6070,16 +6070,16 @@
         </is>
       </c>
       <c r="B80" s="4" t="n">
+        <v>-8596795059</v>
+      </c>
+      <c r="C80" s="4" t="n">
+        <v>-5958088241</v>
+      </c>
+      <c r="D80" s="4" t="n">
+        <v>11558779299</v>
+      </c>
+      <c r="E80" s="4" t="n">
         <v>12436623071</v>
-      </c>
-      <c r="C80" s="4" t="n">
-        <v>11558779299</v>
-      </c>
-      <c r="D80" s="4" t="n">
-        <v>-5958088241</v>
-      </c>
-      <c r="E80" s="4" t="n">
-        <v>-8596795059</v>
       </c>
     </row>
   </sheetData>
@@ -6096,11 +6096,11 @@
   <dimension ref="A1:E149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="113" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6111,22 +6111,22 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>2025</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>2022</t>
         </is>
       </c>
     </row>
@@ -6137,16 +6137,16 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
+        <v>3057657087640</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>3028297410899</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>4802105868186</v>
+      </c>
+      <c r="E2" s="4" t="n">
         <v>7108703741609</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>4802105868186</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>3028297410899</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>3057657087640</v>
       </c>
     </row>
     <row r="3">
@@ -6156,16 +6156,16 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
+        <v>22646115484</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>22954477706</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>23565200377</v>
+      </c>
+      <c r="E3" s="4" t="n">
         <v>24873836043</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>23565200377</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>22954477706</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>22646115484</v>
       </c>
     </row>
     <row r="4">
@@ -6175,16 +6175,16 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
+        <v>270349620</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>4636253744</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>6071068910</v>
+      </c>
+      <c r="E4" s="4" t="n">
         <v>26400000</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>6071068910</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>4636253744</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>270349620</v>
       </c>
     </row>
     <row r="5">
@@ -6216,10 +6216,10 @@
         <v>0</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0</v>
+        <v>-11180667</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-11180667</v>
+        <v>0</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>0</v>
@@ -6232,16 +6232,16 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
+        <v>609169047616</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>893985755421</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>1471244444534</v>
+      </c>
+      <c r="E7" s="4" t="n">
         <v>2055011378498</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>1471244444534</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>893985755421</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>609169047616</v>
       </c>
     </row>
     <row r="8">
@@ -6251,16 +6251,16 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
+        <v>-156303191939</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>-335159132981</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>-539111776066</v>
+      </c>
+      <c r="E8" s="4" t="n">
         <v>-686651363984</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>-539111776066</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>-335159132981</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>-156303191939</v>
       </c>
     </row>
     <row r="9">
@@ -6270,16 +6270,16 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
+        <v>1551393773235</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>-12963130531875</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>-9943684470023</v>
+      </c>
+      <c r="E9" s="4" t="n">
         <v>-29065070402164</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>-9943684470023</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>-12963130531875</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>1551393773235</v>
       </c>
     </row>
     <row r="10">
@@ -6289,16 +6289,16 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
+        <v>-3450109025019</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>740836667695</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>2686954618085</v>
+      </c>
+      <c r="E10" s="4" t="n">
         <v>16025337394</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>2686954618085</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>740836667695</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>-3450109025019</v>
       </c>
     </row>
     <row r="11">
@@ -6327,16 +6327,16 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
+        <v>2519094220855</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>-3478363005107</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>2516743124189</v>
+      </c>
+      <c r="E12" s="4" t="n">
         <v>85568505507</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>2516743124189</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>-3478363005107</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>2519094220855</v>
       </c>
     </row>
     <row r="13">
@@ -6346,16 +6346,16 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
+        <v>-5620395497</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>-21009726316</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>-18967765286</v>
+      </c>
+      <c r="E13" s="4" t="n">
         <v>31220548802</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>-18967765286</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>-21009726316</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>-5620395497</v>
       </c>
     </row>
     <row r="14">
@@ -6365,16 +6365,16 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
+        <v>-551285122912</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>-901950985028</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>-1342453255799</v>
+      </c>
+      <c r="E14" s="4" t="n">
         <v>-2033252688434</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>-1342453255799</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>-901950985028</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>-551285122912</v>
       </c>
     </row>
     <row r="15">
@@ -6384,16 +6384,16 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
+        <v>-539650865595</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>-440729850165</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>-583532014718</v>
+      </c>
+      <c r="E15" s="4" t="n">
         <v>-969623062726</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>-583532014718</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>-440729850165</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>-539650865595</v>
       </c>
     </row>
     <row r="16">
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>0</v>
+        <v>524989326844</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>0</v>
@@ -6412,7 +6412,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>524989326844</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -6422,16 +6422,16 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>0</v>
+        <v>-524989326844</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0</v>
+        <v>-60000000</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-60000000</v>
+        <v>0</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-524989326844</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -6441,16 +6441,16 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
+        <v>5084833181656</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>-9348426947753</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>-4179809664082</v>
+      </c>
+      <c r="E18" s="4" t="n">
         <v>-20564385947691</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>-4179809664082</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>-9348426947753</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>5084833181656</v>
       </c>
     </row>
     <row r="19">
@@ -6460,16 +6460,16 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
+        <v>-18887284000</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>-5938748551</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>-15530023681</v>
+      </c>
+      <c r="E19" s="4" t="n">
         <v>-126608197153</v>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>-15530023681</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>-5938748551</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>-18887284000</v>
       </c>
     </row>
     <row r="20">
@@ -6482,10 +6482,10 @@
         <v>0</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0</v>
+        <v>475000000</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>475000000</v>
+        <v>0</v>
       </c>
       <c r="E20" s="4" t="n">
         <v>0</v>
@@ -6536,16 +6536,16 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>-3033431775000</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="4" t="n">
         <v>-175249480890</v>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>-3033431775000</v>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -6555,16 +6555,16 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="4" t="n">
         <v>8412824066</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -6593,16 +6593,16 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
+        <v>-18887284000</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>-3038895523551</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>-15530023681</v>
+      </c>
+      <c r="E26" s="4" t="n">
         <v>-293444853977</v>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>-15530023681</v>
-      </c>
-      <c r="D26" s="4" t="n">
-        <v>-3038895523551</v>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>-18887284000</v>
       </c>
     </row>
     <row r="27">
@@ -6612,16 +6612,16 @@
         </is>
       </c>
       <c r="B27" s="4" t="n">
+        <v>1893900000</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>10242763500000</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>2252600000</v>
+      </c>
+      <c r="E27" s="4" t="n">
         <v>12106839428518</v>
-      </c>
-      <c r="C27" s="4" t="n">
-        <v>2252600000</v>
-      </c>
-      <c r="D27" s="4" t="n">
-        <v>10242763500000</v>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>1893900000</v>
       </c>
     </row>
     <row r="28">
@@ -6650,16 +6650,16 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
+        <v>16481400000000</v>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>82761482790113</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>81148615568719</v>
+      </c>
+      <c r="E29" s="4" t="n">
         <v>95576293979754</v>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>81148615568719</v>
-      </c>
-      <c r="D29" s="4" t="n">
-        <v>82761482790113</v>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>16481400000000</v>
       </c>
     </row>
     <row r="30">
@@ -6669,16 +6669,16 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
+        <v>-19594182377039</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>-78439556027027</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>-77477067820028</v>
+      </c>
+      <c r="E30" s="4" t="n">
         <v>-86581825426523</v>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>-77477067820028</v>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>-78439556027027</v>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>-19594182377039</v>
       </c>
     </row>
     <row r="31">
@@ -6707,16 +6707,16 @@
         </is>
       </c>
       <c r="B32" s="4" t="n">
-        <v>0</v>
+        <v>-675447477440</v>
       </c>
       <c r="C32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="4" t="n">
         <v>-1196040613480</v>
       </c>
-      <c r="D32" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E32" s="4" t="n">
-        <v>-675447477440</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -6726,16 +6726,16 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
+        <v>-3786335954479</v>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>14564690263086</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>2477759735211</v>
+      </c>
+      <c r="E33" s="4" t="n">
         <v>21101307981749</v>
-      </c>
-      <c r="C33" s="4" t="n">
-        <v>2477759735211</v>
-      </c>
-      <c r="D33" s="4" t="n">
-        <v>14564690263086</v>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>-3786335954479</v>
       </c>
     </row>
     <row r="34">
@@ -6745,16 +6745,16 @@
         </is>
       </c>
       <c r="B34" s="4" t="n">
+        <v>1279609943177</v>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>2177367791782</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>-1717579952552</v>
+      </c>
+      <c r="E34" s="4" t="n">
         <v>243477180081</v>
-      </c>
-      <c r="C34" s="4" t="n">
-        <v>-1717579952552</v>
-      </c>
-      <c r="D34" s="4" t="n">
-        <v>2177367791782</v>
-      </c>
-      <c r="E34" s="4" t="n">
-        <v>1279609943177</v>
       </c>
     </row>
     <row r="35">
@@ -6764,16 +6764,16 @@
         </is>
       </c>
       <c r="B35" s="4" t="n">
+        <v>1125203259229</v>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>2404813202406</v>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>4582180994188</v>
+      </c>
+      <c r="E35" s="4" t="n">
         <v>2864601041636</v>
-      </c>
-      <c r="C35" s="4" t="n">
-        <v>4582180994188</v>
-      </c>
-      <c r="D35" s="4" t="n">
-        <v>2404813202406</v>
-      </c>
-      <c r="E35" s="4" t="n">
-        <v>1125203259229</v>
       </c>
     </row>
     <row r="36">
@@ -6802,16 +6802,16 @@
         </is>
       </c>
       <c r="B37" s="4" t="n">
+        <v>2404813202406</v>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>4582180994188</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>2864601041636</v>
+      </c>
+      <c r="E37" s="4" t="n">
         <v>3108078221717</v>
-      </c>
-      <c r="C37" s="4" t="n">
-        <v>2864601041636</v>
-      </c>
-      <c r="D37" s="4" t="n">
-        <v>4582180994188</v>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>2404813202406</v>
       </c>
     </row>
     <row r="38">
@@ -6897,16 +6897,16 @@
         </is>
       </c>
       <c r="B42" s="4" t="n">
+        <v>16481400000000</v>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>82761482790113</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>81148615568719</v>
+      </c>
+      <c r="E42" s="4" t="n">
         <v>95576293979754</v>
-      </c>
-      <c r="C42" s="4" t="n">
-        <v>81148615568719</v>
-      </c>
-      <c r="D42" s="4" t="n">
-        <v>82761482790113</v>
-      </c>
-      <c r="E42" s="4" t="n">
-        <v>16481400000000</v>
       </c>
     </row>
     <row r="43">
@@ -6954,16 +6954,16 @@
         </is>
       </c>
       <c r="B45" s="4" t="n">
+        <v>-19594182377039</v>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>-78439556027027</v>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>-77477067820028</v>
+      </c>
+      <c r="E45" s="4" t="n">
         <v>-86581825426523</v>
-      </c>
-      <c r="C45" s="4" t="n">
-        <v>-77477067820028</v>
-      </c>
-      <c r="D45" s="4" t="n">
-        <v>-78439556027027</v>
-      </c>
-      <c r="E45" s="4" t="n">
-        <v>-19594182377039</v>
       </c>
     </row>
     <row r="46">
@@ -6973,16 +6973,16 @@
         </is>
       </c>
       <c r="B46" s="4" t="n">
+        <v>1125203259229</v>
+      </c>
+      <c r="C46" s="4" t="n">
+        <v>2404813202406</v>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>4547180994188</v>
+      </c>
+      <c r="E46" s="4" t="n">
         <v>2864601041636</v>
-      </c>
-      <c r="C46" s="4" t="n">
-        <v>4547180994188</v>
-      </c>
-      <c r="D46" s="4" t="n">
-        <v>2404813202406</v>
-      </c>
-      <c r="E46" s="4" t="n">
-        <v>1125203259229</v>
       </c>
     </row>
     <row r="47">
@@ -7030,16 +7030,16 @@
         </is>
       </c>
       <c r="B49" s="4" t="n">
+        <v>2404813202406</v>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>4547180994188</v>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>2864601041636</v>
+      </c>
+      <c r="E49" s="4" t="n">
         <v>3108078221717</v>
-      </c>
-      <c r="C49" s="4" t="n">
-        <v>2864601041636</v>
-      </c>
-      <c r="D49" s="4" t="n">
-        <v>4547180994188</v>
-      </c>
-      <c r="E49" s="4" t="n">
-        <v>2404813202406</v>
       </c>
     </row>
     <row r="50">
@@ -7071,10 +7071,10 @@
         <v>0</v>
       </c>
       <c r="C51" s="4" t="n">
-        <v>0</v>
+        <v>35000000000</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>35000000000</v>
+        <v>0</v>
       </c>
       <c r="E51" s="4" t="n">
         <v>0</v>
@@ -7106,16 +7106,16 @@
         </is>
       </c>
       <c r="B53" s="4" t="n">
+        <v>276521066989343</v>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>341251631768076</v>
+      </c>
+      <c r="D53" s="4" t="n">
+        <v>499928912941086</v>
+      </c>
+      <c r="E53" s="4" t="n">
         <v>738046448339303</v>
-      </c>
-      <c r="C53" s="4" t="n">
-        <v>499928912941086</v>
-      </c>
-      <c r="D53" s="4" t="n">
-        <v>341251631768076</v>
-      </c>
-      <c r="E53" s="4" t="n">
-        <v>276521066989343</v>
       </c>
     </row>
     <row r="54">
@@ -7125,16 +7125,16 @@
         </is>
       </c>
       <c r="B54" s="4" t="n">
+        <v>-284951627339958</v>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>-356333054468634</v>
+      </c>
+      <c r="D54" s="4" t="n">
+        <v>-575279337471679</v>
+      </c>
+      <c r="E54" s="4" t="n">
         <v>-843973115884084</v>
-      </c>
-      <c r="C54" s="4" t="n">
-        <v>-575279337471679</v>
-      </c>
-      <c r="D54" s="4" t="n">
-        <v>-356333054468634</v>
-      </c>
-      <c r="E54" s="4" t="n">
-        <v>-284951627339958</v>
       </c>
     </row>
     <row r="55">
@@ -7258,16 +7258,16 @@
         </is>
       </c>
       <c r="B61" s="4" t="n">
+        <v>305615543755483</v>
+      </c>
+      <c r="C61" s="4" t="n">
+        <v>526772783372466</v>
+      </c>
+      <c r="D61" s="4" t="n">
+        <v>786635095183819</v>
+      </c>
+      <c r="E61" s="4" t="n">
         <v>1198232900374700</v>
-      </c>
-      <c r="C61" s="4" t="n">
-        <v>786635095183819</v>
-      </c>
-      <c r="D61" s="4" t="n">
-        <v>526772783372466</v>
-      </c>
-      <c r="E61" s="4" t="n">
-        <v>305615543755483</v>
       </c>
     </row>
     <row r="62">
@@ -7277,16 +7277,16 @@
         </is>
       </c>
       <c r="B62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" s="4" t="n">
+        <v>43719133278</v>
+      </c>
+      <c r="E62" s="4" t="n">
         <v>25613581008</v>
-      </c>
-      <c r="C62" s="4" t="n">
-        <v>43719133278</v>
-      </c>
-      <c r="D62" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -7296,16 +7296,16 @@
         </is>
       </c>
       <c r="B63" s="4" t="n">
+        <v>-57278984467</v>
+      </c>
+      <c r="C63" s="4" t="n">
+        <v>-52070652886</v>
+      </c>
+      <c r="D63" s="4" t="n">
+        <v>-47576177569</v>
+      </c>
+      <c r="E63" s="4" t="n">
         <v>-60816680131</v>
-      </c>
-      <c r="C63" s="4" t="n">
-        <v>-47576177569</v>
-      </c>
-      <c r="D63" s="4" t="n">
-        <v>-52070652886</v>
-      </c>
-      <c r="E63" s="4" t="n">
-        <v>-57278984467</v>
       </c>
     </row>
     <row r="64">
@@ -7353,16 +7353,16 @@
         </is>
       </c>
       <c r="B66" s="4" t="n">
+        <v>84249052539715</v>
+      </c>
+      <c r="C66" s="4" t="n">
+        <v>121040499898739</v>
+      </c>
+      <c r="D66" s="4" t="n">
+        <v>190416150569365</v>
+      </c>
+      <c r="E66" s="4" t="n">
         <v>139355134797811</v>
-      </c>
-      <c r="C66" s="4" t="n">
-        <v>190416150569365</v>
-      </c>
-      <c r="D66" s="4" t="n">
-        <v>121040499898739</v>
-      </c>
-      <c r="E66" s="4" t="n">
-        <v>84249052539715</v>
       </c>
     </row>
     <row r="67">
@@ -7372,16 +7372,16 @@
         </is>
       </c>
       <c r="B67" s="4" t="n">
+        <v>-84197133352967</v>
+      </c>
+      <c r="C67" s="4" t="n">
+        <v>-120060929738920</v>
+      </c>
+      <c r="D67" s="4" t="n">
+        <v>-191403026217302</v>
+      </c>
+      <c r="E67" s="4" t="n">
         <v>-139350374509823</v>
-      </c>
-      <c r="C67" s="4" t="n">
-        <v>-191403026217302</v>
-      </c>
-      <c r="D67" s="4" t="n">
-        <v>-120060929738920</v>
-      </c>
-      <c r="E67" s="4" t="n">
-        <v>-84197133352967</v>
       </c>
     </row>
     <row r="68">
@@ -7391,16 +7391,16 @@
         </is>
       </c>
       <c r="B68" s="4" t="n">
+        <v>-2247052204419</v>
+      </c>
+      <c r="C68" s="4" t="n">
+        <v>3444679727080</v>
+      </c>
+      <c r="D68" s="4" t="n">
+        <v>4249521552509</v>
+      </c>
+      <c r="E68" s="4" t="n">
         <v>678346947204</v>
-      </c>
-      <c r="C68" s="4" t="n">
-        <v>4249521552509</v>
-      </c>
-      <c r="D68" s="4" t="n">
-        <v>3444679727080</v>
-      </c>
-      <c r="E68" s="4" t="n">
-        <v>-2247052204419</v>
       </c>
     </row>
     <row r="69">
@@ -7410,16 +7410,16 @@
         </is>
       </c>
       <c r="B69" s="4" t="n">
+        <v>4577097273878</v>
+      </c>
+      <c r="C69" s="4" t="n">
+        <v>2330045069459</v>
+      </c>
+      <c r="D69" s="4" t="n">
+        <v>5774724796539</v>
+      </c>
+      <c r="E69" s="4" t="n">
         <v>10024246349048</v>
-      </c>
-      <c r="C69" s="4" t="n">
-        <v>5774724796539</v>
-      </c>
-      <c r="D69" s="4" t="n">
-        <v>2330045069459</v>
-      </c>
-      <c r="E69" s="4" t="n">
-        <v>4577097273878</v>
       </c>
     </row>
     <row r="70">
@@ -7429,16 +7429,16 @@
         </is>
       </c>
       <c r="B70" s="4" t="n">
+        <v>4577097273878</v>
+      </c>
+      <c r="C70" s="4" t="n">
+        <v>2330045069459</v>
+      </c>
+      <c r="D70" s="4" t="n">
+        <v>5774724796539</v>
+      </c>
+      <c r="E70" s="4" t="n">
         <v>10024246349048</v>
-      </c>
-      <c r="C70" s="4" t="n">
-        <v>5774724796539</v>
-      </c>
-      <c r="D70" s="4" t="n">
-        <v>2330045069459</v>
-      </c>
-      <c r="E70" s="4" t="n">
-        <v>4577097273878</v>
       </c>
     </row>
     <row r="71">
@@ -7448,16 +7448,16 @@
         </is>
       </c>
       <c r="B71" s="4" t="n">
+        <v>2278125882711</v>
+      </c>
+      <c r="C71" s="4" t="n">
+        <v>2945784273957</v>
+      </c>
+      <c r="D71" s="4" t="n">
+        <v>8245482244688</v>
+      </c>
+      <c r="E71" s="4" t="n">
         <v>6447211380125</v>
-      </c>
-      <c r="C71" s="4" t="n">
-        <v>8245482244688</v>
-      </c>
-      <c r="D71" s="4" t="n">
-        <v>2945784273957</v>
-      </c>
-      <c r="E71" s="4" t="n">
-        <v>2278125882711</v>
       </c>
     </row>
     <row r="72">
@@ -7505,16 +7505,16 @@
         </is>
       </c>
       <c r="B74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" s="4" t="n">
+        <v>1797451176015</v>
+      </c>
+      <c r="D74" s="4" t="n">
+        <v>1734150405730</v>
+      </c>
+      <c r="E74" s="4" t="n">
         <v>4206007929509</v>
-      </c>
-      <c r="C74" s="4" t="n">
-        <v>1734150405730</v>
-      </c>
-      <c r="D74" s="4" t="n">
-        <v>1797451176015</v>
-      </c>
-      <c r="E74" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -7524,16 +7524,16 @@
         </is>
       </c>
       <c r="B75" s="4" t="n">
+        <v>51919186748</v>
+      </c>
+      <c r="C75" s="4" t="n">
+        <v>1031489346567</v>
+      </c>
+      <c r="D75" s="4" t="n">
+        <v>44613698630</v>
+      </c>
+      <c r="E75" s="4" t="n">
         <v>49373986618</v>
-      </c>
-      <c r="C75" s="4" t="n">
-        <v>44613698630</v>
-      </c>
-      <c r="D75" s="4" t="n">
-        <v>1031489346567</v>
-      </c>
-      <c r="E75" s="4" t="n">
-        <v>51919186748</v>
       </c>
     </row>
     <row r="76">
@@ -7638,16 +7638,16 @@
         </is>
       </c>
       <c r="B81" s="4" t="n">
+        <v>2330045069459</v>
+      </c>
+      <c r="C81" s="4" t="n">
+        <v>5774724796539</v>
+      </c>
+      <c r="D81" s="4" t="n">
+        <v>10024246349048</v>
+      </c>
+      <c r="E81" s="4" t="n">
         <v>10702593296252</v>
-      </c>
-      <c r="C81" s="4" t="n">
-        <v>10024246349048</v>
-      </c>
-      <c r="D81" s="4" t="n">
-        <v>5774724796539</v>
-      </c>
-      <c r="E81" s="4" t="n">
-        <v>2330045069459</v>
       </c>
     </row>
     <row r="82">
@@ -7657,16 +7657,16 @@
         </is>
       </c>
       <c r="B82" s="4" t="n">
+        <v>2330045069459</v>
+      </c>
+      <c r="C82" s="4" t="n">
+        <v>5774724796539</v>
+      </c>
+      <c r="D82" s="4" t="n">
+        <v>10024246349048</v>
+      </c>
+      <c r="E82" s="4" t="n">
         <v>10702593296252</v>
-      </c>
-      <c r="C82" s="4" t="n">
-        <v>10024246349048</v>
-      </c>
-      <c r="D82" s="4" t="n">
-        <v>5774724796539</v>
-      </c>
-      <c r="E82" s="4" t="n">
-        <v>2330045069459</v>
       </c>
     </row>
     <row r="83">
@@ -7676,16 +7676,16 @@
         </is>
       </c>
       <c r="B83" s="4" t="n">
+        <v>2278125882711</v>
+      </c>
+      <c r="C83" s="4" t="n">
+        <v>2945784273957</v>
+      </c>
+      <c r="D83" s="4" t="n">
+        <v>8245482244688</v>
+      </c>
+      <c r="E83" s="4" t="n">
         <v>6447211380125</v>
-      </c>
-      <c r="C83" s="4" t="n">
-        <v>8245482244688</v>
-      </c>
-      <c r="D83" s="4" t="n">
-        <v>2945784273957</v>
-      </c>
-      <c r="E83" s="4" t="n">
-        <v>2278125882711</v>
       </c>
     </row>
     <row r="84">
@@ -7771,16 +7771,16 @@
         </is>
       </c>
       <c r="B88" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C88" s="4" t="n">
+        <v>1797451176015</v>
+      </c>
+      <c r="D88" s="4" t="n">
+        <v>1734150405730</v>
+      </c>
+      <c r="E88" s="4" t="n">
         <v>4206007929509</v>
-      </c>
-      <c r="C88" s="4" t="n">
-        <v>1734150405730</v>
-      </c>
-      <c r="D88" s="4" t="n">
-        <v>1797451176015</v>
-      </c>
-      <c r="E88" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -7790,16 +7790,16 @@
         </is>
       </c>
       <c r="B89" s="4" t="n">
+        <v>51919186748</v>
+      </c>
+      <c r="C89" s="4" t="n">
+        <v>1031489346567</v>
+      </c>
+      <c r="D89" s="4" t="n">
+        <v>44613698630</v>
+      </c>
+      <c r="E89" s="4" t="n">
         <v>49373986618</v>
-      </c>
-      <c r="C89" s="4" t="n">
-        <v>44613698630</v>
-      </c>
-      <c r="D89" s="4" t="n">
-        <v>1031489346567</v>
-      </c>
-      <c r="E89" s="4" t="n">
-        <v>51919186748</v>
       </c>
     </row>
     <row r="90">
@@ -7866,16 +7866,16 @@
         </is>
       </c>
       <c r="B93" s="4" t="n">
+        <v>475782320781</v>
+      </c>
+      <c r="C93" s="4" t="n">
+        <v>586406173223</v>
+      </c>
+      <c r="D93" s="4" t="n">
+        <v>961768937755</v>
+      </c>
+      <c r="E93" s="4" t="n">
         <v>1393260250557</v>
-      </c>
-      <c r="C93" s="4" t="n">
-        <v>961768937755</v>
-      </c>
-      <c r="D93" s="4" t="n">
-        <v>586406173223</v>
-      </c>
-      <c r="E93" s="4" t="n">
-        <v>475782320781</v>
       </c>
     </row>
     <row r="94">
@@ -7904,16 +7904,16 @@
         </is>
       </c>
       <c r="B95" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="4" t="n">
         <v>5631437562</v>
-      </c>
-      <c r="C95" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D95" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E95" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -7923,16 +7923,16 @@
         </is>
       </c>
       <c r="B96" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C96" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" s="4" t="n">
         <v>3679561158</v>
-      </c>
-      <c r="C96" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E96" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -8037,16 +8037,16 @@
         </is>
       </c>
       <c r="B102" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="4" t="n">
         <v>1951876404</v>
-      </c>
-      <c r="C102" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D102" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E102" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -8189,16 +8189,16 @@
         </is>
       </c>
       <c r="B110" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" s="4" t="n">
         <v>-6910975255</v>
-      </c>
-      <c r="C110" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D110" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E110" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -8208,16 +8208,16 @@
         </is>
       </c>
       <c r="B111" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" s="4" t="n">
         <v>-6910975255</v>
-      </c>
-      <c r="C111" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D111" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E111" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -8417,16 +8417,16 @@
         </is>
       </c>
       <c r="B122" s="4" t="n">
+        <v>3054260481126</v>
+      </c>
+      <c r="C122" s="4" t="n">
+        <v>-8839931663375</v>
+      </c>
+      <c r="D122" s="4" t="n">
+        <v>-13561407750219</v>
+      </c>
+      <c r="E122" s="4" t="n">
         <v>-26825430350091</v>
-      </c>
-      <c r="C122" s="4" t="n">
-        <v>-13561407750219</v>
-      </c>
-      <c r="D122" s="4" t="n">
-        <v>-8839931663375</v>
-      </c>
-      <c r="E122" s="4" t="n">
-        <v>3054260481126</v>
       </c>
     </row>
     <row r="123">
@@ -8436,16 +8436,16 @@
         </is>
       </c>
       <c r="B123" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" s="4" t="n">
+        <v>-17278163500</v>
+      </c>
+      <c r="E123" s="4" t="n">
         <v>-18413443303</v>
-      </c>
-      <c r="C123" s="4" t="n">
-        <v>-17278163500</v>
-      </c>
-      <c r="D123" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E123" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -8455,16 +8455,16 @@
         </is>
       </c>
       <c r="B124" s="4" t="n">
+        <v>511166300000</v>
+      </c>
+      <c r="C124" s="4" t="n">
+        <v>-1291046000000</v>
+      </c>
+      <c r="D124" s="4" t="n">
+        <v>-1440059785348</v>
+      </c>
+      <c r="E124" s="4" t="n">
         <v>-1335312954271</v>
-      </c>
-      <c r="C124" s="4" t="n">
-        <v>-1440059785348</v>
-      </c>
-      <c r="D124" s="4" t="n">
-        <v>-1291046000000</v>
-      </c>
-      <c r="E124" s="4" t="n">
-        <v>511166300000</v>
       </c>
     </row>
     <row r="125">
@@ -8474,16 +8474,16 @@
         </is>
       </c>
       <c r="B125" s="4" t="n">
+        <v>6497424202012</v>
+      </c>
+      <c r="C125" s="4" t="n">
+        <v>-7264561551658</v>
+      </c>
+      <c r="D125" s="4" t="n">
+        <v>-9292078962942</v>
+      </c>
+      <c r="E125" s="4" t="n">
         <v>-17948486475954</v>
-      </c>
-      <c r="C125" s="4" t="n">
-        <v>-9292078962942</v>
-      </c>
-      <c r="D125" s="4" t="n">
-        <v>-7264561551658</v>
-      </c>
-      <c r="E125" s="4" t="n">
-        <v>6497424202012</v>
       </c>
     </row>
     <row r="126">
@@ -8493,16 +8493,16 @@
         </is>
       </c>
       <c r="B126" s="4" t="n">
+        <v>-3947364654478</v>
+      </c>
+      <c r="C126" s="4" t="n">
+        <v>-292097988743</v>
+      </c>
+      <c r="D126" s="4" t="n">
+        <v>-2614293738429</v>
+      </c>
+      <c r="E126" s="4" t="n">
         <v>-7531928504136</v>
-      </c>
-      <c r="C126" s="4" t="n">
-        <v>-2614293738429</v>
-      </c>
-      <c r="D126" s="4" t="n">
-        <v>-292097988743</v>
-      </c>
-      <c r="E126" s="4" t="n">
-        <v>-3947364654478</v>
       </c>
     </row>
     <row r="127">
@@ -8512,16 +8512,16 @@
         </is>
       </c>
       <c r="B127" s="4" t="n">
+        <v>-6965366408</v>
+      </c>
+      <c r="C127" s="4" t="n">
+        <v>7773877026</v>
+      </c>
+      <c r="D127" s="4" t="n">
+        <v>-197697100000</v>
+      </c>
+      <c r="E127" s="4" t="n">
         <v>8906516573</v>
-      </c>
-      <c r="C127" s="4" t="n">
-        <v>-197697100000</v>
-      </c>
-      <c r="D127" s="4" t="n">
-        <v>7773877026</v>
-      </c>
-      <c r="E127" s="4" t="n">
-        <v>-6965366408</v>
       </c>
     </row>
     <row r="128">
@@ -8531,16 +8531,16 @@
         </is>
       </c>
       <c r="B128" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" s="4" t="n">
         <v>-195489000</v>
-      </c>
-      <c r="C128" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D128" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E128" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -8664,16 +8664,16 @@
         </is>
       </c>
       <c r="B135" s="4" t="n">
+        <v>165790274167</v>
+      </c>
+      <c r="C135" s="4" t="n">
+        <v>180391762558</v>
+      </c>
+      <c r="D135" s="4" t="n">
+        <v>337847776224</v>
+      </c>
+      <c r="E135" s="4" t="n">
         <v>539115328852</v>
-      </c>
-      <c r="C135" s="4" t="n">
-        <v>337847776224</v>
-      </c>
-      <c r="D135" s="4" t="n">
-        <v>180391762558</v>
-      </c>
-      <c r="E135" s="4" t="n">
-        <v>165790274167</v>
       </c>
     </row>
     <row r="136">
@@ -8683,16 +8683,16 @@
         </is>
       </c>
       <c r="B136" s="4" t="n">
+        <v>115365106128</v>
+      </c>
+      <c r="C136" s="4" t="n">
+        <v>7818314374</v>
+      </c>
+      <c r="D136" s="4" t="n">
+        <v>-77566821611</v>
+      </c>
+      <c r="E136" s="4" t="n">
         <v>-65178982099</v>
-      </c>
-      <c r="C136" s="4" t="n">
-        <v>-77566821611</v>
-      </c>
-      <c r="D136" s="4" t="n">
-        <v>7818314374</v>
-      </c>
-      <c r="E136" s="4" t="n">
-        <v>115365106128</v>
       </c>
     </row>
     <row r="137">
@@ -8721,16 +8721,16 @@
         </is>
       </c>
       <c r="B138" s="4" t="n">
+        <v>240252940500</v>
+      </c>
+      <c r="C138" s="4" t="n">
+        <v>-239841359017</v>
+      </c>
+      <c r="D138" s="4" t="n">
+        <v>125459716520</v>
+      </c>
+      <c r="E138" s="4" t="n">
         <v>1933921663</v>
-      </c>
-      <c r="C138" s="4" t="n">
-        <v>125459716520</v>
-      </c>
-      <c r="D138" s="4" t="n">
-        <v>-239841359017</v>
-      </c>
-      <c r="E138" s="4" t="n">
-        <v>240252940500</v>
       </c>
     </row>
     <row r="139">
@@ -8759,16 +8759,16 @@
         </is>
       </c>
       <c r="B140" s="4" t="n">
+        <v>-150000000</v>
+      </c>
+      <c r="C140" s="4" t="n">
+        <v>819874627</v>
+      </c>
+      <c r="D140" s="4" t="n">
+        <v>-63376177</v>
+      </c>
+      <c r="E140" s="4" t="n">
         <v>702511645</v>
-      </c>
-      <c r="C140" s="4" t="n">
-        <v>-63376177</v>
-      </c>
-      <c r="D140" s="4" t="n">
-        <v>819874627</v>
-      </c>
-      <c r="E140" s="4" t="n">
-        <v>-150000000</v>
       </c>
     </row>
     <row r="141">
@@ -8778,16 +8778,16 @@
         </is>
       </c>
       <c r="B141" s="4" t="n">
+        <v>-16576646902</v>
+      </c>
+      <c r="C141" s="4" t="n">
+        <v>-5692616512</v>
+      </c>
+      <c r="D141" s="4" t="n">
+        <v>9629489049</v>
+      </c>
+      <c r="E141" s="4" t="n">
         <v>53057413631</v>
-      </c>
-      <c r="C141" s="4" t="n">
-        <v>9629489049</v>
-      </c>
-      <c r="D141" s="4" t="n">
-        <v>-5692616512</v>
-      </c>
-      <c r="E141" s="4" t="n">
-        <v>-16576646902</v>
       </c>
     </row>
     <row r="142">
@@ -8797,16 +8797,16 @@
         </is>
       </c>
       <c r="B142" s="4" t="n">
+        <v>20022806384</v>
+      </c>
+      <c r="C142" s="4" t="n">
+        <v>21990350285</v>
+      </c>
+      <c r="D142" s="4" t="n">
+        <v>38272728216</v>
+      </c>
+      <c r="E142" s="4" t="n">
         <v>47843286609</v>
-      </c>
-      <c r="C142" s="4" t="n">
-        <v>38272728216</v>
-      </c>
-      <c r="D142" s="4" t="n">
-        <v>21990350285</v>
-      </c>
-      <c r="E142" s="4" t="n">
-        <v>20022806384</v>
       </c>
     </row>
     <row r="143">
@@ -8854,7 +8854,7 @@
         </is>
       </c>
       <c r="B145" s="4" t="n">
-        <v>0</v>
+        <v>524989326844</v>
       </c>
       <c r="C145" s="4" t="n">
         <v>0</v>
@@ -8863,7 +8863,7 @@
         <v>0</v>
       </c>
       <c r="E145" s="4" t="n">
-        <v>524989326844</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -8873,16 +8873,16 @@
         </is>
       </c>
       <c r="B146" s="4" t="n">
-        <v>0</v>
+        <v>-524989326844</v>
       </c>
       <c r="C146" s="4" t="n">
-        <v>0</v>
+        <v>-60000000</v>
       </c>
       <c r="D146" s="4" t="n">
-        <v>-60000000</v>
+        <v>0</v>
       </c>
       <c r="E146" s="4" t="n">
-        <v>-524989326844</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -8892,16 +8892,16 @@
         </is>
       </c>
       <c r="B147" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C147" s="4" t="n">
+        <v>12591704106</v>
+      </c>
+      <c r="D147" s="4" t="n">
+        <v>-74600938496</v>
+      </c>
+      <c r="E147" s="4" t="n">
         <v>52947827083</v>
-      </c>
-      <c r="C147" s="4" t="n">
-        <v>-74600938496</v>
-      </c>
-      <c r="D147" s="4" t="n">
-        <v>12591704106</v>
-      </c>
-      <c r="E147" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -8911,16 +8911,16 @@
         </is>
       </c>
       <c r="B148" s="4" t="n">
+        <v>-299426675811568</v>
+      </c>
+      <c r="C148" s="4" t="n">
+        <v>-509174180451761</v>
+      </c>
+      <c r="D148" s="4" t="n">
+        <v>-706044416408489</v>
+      </c>
+      <c r="E148" s="4" t="n">
         <v>-1091597443071580</v>
-      </c>
-      <c r="C148" s="4" t="n">
-        <v>-706044416408489</v>
-      </c>
-      <c r="D148" s="4" t="n">
-        <v>-509174180451761</v>
-      </c>
-      <c r="E148" s="4" t="n">
-        <v>-299426675811568</v>
       </c>
     </row>
     <row r="149">
@@ -8956,11 +8956,11 @@
   <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
     <col width="3" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -8971,19 +8971,11 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="42" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>Khối "CHỈ SỐ TÀI CHÍNH" tính bằng công thức từ khối "DỮ LIỆU TRÍCH XUẤT" bên dưới, không phải số nhập tay. Khối "DỮ LIỆU TRÍCH XUẤT" được dò tự động theo TÊN khoản mục (đúng theo tên gốc trong báo cáo) và theo NĂM từ 3 sheet balance_sheet / income_statement — không tham chiếu ô cố định. Có thể sửa nhãn khoản mục ở cột A khối này nếu công ty đổi tên dòng; công thức sẽ tự dò lại. Các năm được xếp tăng dần từ trái sang phải.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>Lưu ý: Đây là công ty chứng khoán: "Giá vốn hàng bán" được thay bằng "Chi phí hoạt động", "Phải thu khách hàng"/"Hàng tồn kho" không có số liệu (khoản mục thời kỳ trước 2016, luôn = 0) nên Số ngày phải thu và Số ngày tồn kho hiển thị "n/a".</t>
-        </is>
-      </c>
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="6" t="n"/>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="7" t="n"/>
     </row>
     <row r="4"/>
     <row r="5">
@@ -9004,19 +8996,19 @@
         </is>
       </c>
       <c r="B6" s="11">
+        <f>'balance_sheet'!B1</f>
+        <v/>
+      </c>
+      <c r="C6" s="11">
+        <f>'balance_sheet'!C1</f>
+        <v/>
+      </c>
+      <c r="D6" s="11">
+        <f>'balance_sheet'!D1</f>
+        <v/>
+      </c>
+      <c r="E6" s="11">
         <f>'balance_sheet'!E1</f>
-        <v/>
-      </c>
-      <c r="C6" s="11">
-        <f>'balance_sheet'!D1</f>
-        <v/>
-      </c>
-      <c r="D6" s="11">
-        <f>'balance_sheet'!C1</f>
-        <v/>
-      </c>
-      <c r="E6" s="11">
-        <f>'balance_sheet'!B1</f>
         <v/>
       </c>
     </row>
@@ -9530,19 +9522,19 @@
         </is>
       </c>
       <c r="B39" s="11">
+        <f>'balance_sheet'!B1</f>
+        <v/>
+      </c>
+      <c r="C39" s="11">
+        <f>'balance_sheet'!C1</f>
+        <v/>
+      </c>
+      <c r="D39" s="11">
+        <f>'balance_sheet'!D1</f>
+        <v/>
+      </c>
+      <c r="E39" s="11">
         <f>'balance_sheet'!E1</f>
-        <v/>
-      </c>
-      <c r="C39" s="11">
-        <f>'balance_sheet'!D1</f>
-        <v/>
-      </c>
-      <c r="D39" s="11">
-        <f>'balance_sheet'!C1</f>
-        <v/>
-      </c>
-      <c r="E39" s="11">
-        <f>'balance_sheet'!B1</f>
         <v/>
       </c>
     </row>

--- a/financials/TCX/TCX_financials.xlsx
+++ b/financials/TCX/TCX_financials.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_sheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="income_statement" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cash_flow" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chi_so_tai_chinh" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="balance_sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="income_statement" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="cash_flow" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="chi_so_tai_chinh" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -555,11 +555,11 @@
   <dimension ref="A1:E209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="88" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -570,22 +570,22 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>2022</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
         </is>
       </c>
     </row>
@@ -596,16 +596,16 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
+        <v>76612765855403</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>49394749963613</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>40628257426641</v>
+      </c>
+      <c r="E2" s="4" t="n">
         <v>25948479990644</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>40628257426641</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>49394749963613</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>76612765855403</v>
       </c>
     </row>
     <row r="3">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
+        <v>3108078221717</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>2864601041636</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>4582180994188</v>
+      </c>
+      <c r="E3" s="4" t="n">
         <v>2404813202406</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>4582180994188</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>2864601041636</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>3108078221717</v>
       </c>
     </row>
     <row r="4">
@@ -634,16 +634,16 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
+        <v>3108078221717</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>2864601041636</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>4547180994188</v>
+      </c>
+      <c r="E4" s="4" t="n">
         <v>2404813202406</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>4547180994188</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>2864601041636</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>3108078221717</v>
       </c>
     </row>
     <row r="5">
@@ -656,10 +656,10 @@
         <v>0</v>
       </c>
       <c r="C5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="4" t="n">
         <v>35000000000</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>0</v>
@@ -672,16 +672,16 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0</v>
+        <v>38923020900</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0</v>
+        <v>17278163500</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>17278163500</v>
+        <v>0</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>38923020900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
+        <v>-12757948678</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>-10806072274</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>-4774603364</v>
+      </c>
+      <c r="E7" s="4" t="n">
         <v>-3599620</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>-4774603364</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>-10806072274</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>-12757948678</v>
       </c>
     </row>
     <row r="8">
@@ -710,16 +710,16 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
+        <v>727456098295</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>656597329458</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>3064760726090</v>
+      </c>
+      <c r="E8" s="4" t="n">
         <v>3658318396519</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>3064760726090</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>656597329458</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>727456098295</v>
       </c>
     </row>
     <row r="9">
@@ -748,16 +748,16 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
+        <v>5729878954</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>1949853033</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>1707458921</v>
+      </c>
+      <c r="E10" s="4" t="n">
         <v>1512267704</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>1707458921</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>1949853033</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>5729878954</v>
       </c>
     </row>
     <row r="11">
@@ -805,16 +805,16 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
+        <v>2271195630</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>22076558945</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>2709273571142</v>
+      </c>
+      <c r="E13" s="4" t="n">
         <v>3450110238837</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>2709273571142</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>22076558945</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>2271195630</v>
       </c>
     </row>
     <row r="14">
@@ -919,16 +919,16 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
+        <v>13408458353</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>52699169656</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>33780597159</v>
+      </c>
+      <c r="E19" s="4" t="n">
         <v>7373703649</v>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>33780597159</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>52699169656</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>13408458353</v>
       </c>
     </row>
     <row r="20">
@@ -995,16 +995,16 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
+        <v>4019491143606</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>3849383856581</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>3160172027968</v>
+      </c>
+      <c r="E23" s="4" t="n">
         <v>143067748219</v>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>3160172027968</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>3849383856581</v>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>4019491143606</v>
       </c>
     </row>
     <row r="24">
@@ -1109,16 +1109,16 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
+        <v>107181206706</v>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>50740739690</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>64589748067</v>
+      </c>
+      <c r="E29" s="4" t="n">
         <v>84726784106</v>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>64589748067</v>
-      </c>
-      <c r="D29" s="4" t="n">
-        <v>50740739690</v>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>107181206706</v>
       </c>
     </row>
     <row r="30">
@@ -1128,16 +1128,16 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
+        <v>33220423249</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>39993555777</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>50134678668</v>
+      </c>
+      <c r="E30" s="4" t="n">
         <v>68067359617</v>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>50134678668</v>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>39993555777</v>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>33220423249</v>
       </c>
     </row>
     <row r="31">
@@ -1147,16 +1147,16 @@
         </is>
       </c>
       <c r="B31" s="4" t="n">
+        <v>126797126020</v>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>117475687200</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>109934766200</v>
+      </c>
+      <c r="E31" s="4" t="n">
         <v>110681859040</v>
-      </c>
-      <c r="C31" s="4" t="n">
-        <v>109934766200</v>
-      </c>
-      <c r="D31" s="4" t="n">
-        <v>117475687200</v>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>126797126020</v>
       </c>
     </row>
     <row r="32">
@@ -1166,16 +1166,16 @@
         </is>
       </c>
       <c r="B32" s="4" t="n">
+        <v>-93576702771</v>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>-77482131423</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>-59800087532</v>
+      </c>
+      <c r="E32" s="4" t="n">
         <v>-42614499423</v>
-      </c>
-      <c r="C32" s="4" t="n">
-        <v>-59800087532</v>
-      </c>
-      <c r="D32" s="4" t="n">
-        <v>-77482131423</v>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>-93576702771</v>
       </c>
     </row>
     <row r="33">
@@ -1242,16 +1242,16 @@
         </is>
       </c>
       <c r="B36" s="4" t="n">
+        <v>73960783457</v>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>10747183913</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>14455069399</v>
+      </c>
+      <c r="E36" s="4" t="n">
         <v>16659424489</v>
-      </c>
-      <c r="C36" s="4" t="n">
-        <v>14455069399</v>
-      </c>
-      <c r="D36" s="4" t="n">
-        <v>10747183913</v>
-      </c>
-      <c r="E36" s="4" t="n">
-        <v>73960783457</v>
       </c>
     </row>
     <row r="37">
@@ -1261,16 +1261,16 @@
         </is>
       </c>
       <c r="B37" s="4" t="n">
+        <v>138768470729</v>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>66775606490</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>64600335490</v>
+      </c>
+      <c r="E37" s="4" t="n">
         <v>61426279490</v>
-      </c>
-      <c r="C37" s="4" t="n">
-        <v>64600335490</v>
-      </c>
-      <c r="D37" s="4" t="n">
-        <v>66775606490</v>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>138768470729</v>
       </c>
     </row>
     <row r="38">
@@ -1280,16 +1280,16 @@
         </is>
       </c>
       <c r="B38" s="4" t="n">
+        <v>-64807687272</v>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>-56028422577</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>-50145266091</v>
+      </c>
+      <c r="E38" s="4" t="n">
         <v>-44766855001</v>
-      </c>
-      <c r="C38" s="4" t="n">
-        <v>-50145266091</v>
-      </c>
-      <c r="D38" s="4" t="n">
-        <v>-56028422577</v>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>-64807687272</v>
       </c>
     </row>
     <row r="39">
@@ -1375,16 +1375,16 @@
         </is>
       </c>
       <c r="B43" s="4" t="n">
-        <v>0</v>
+        <v>3610268431824</v>
       </c>
       <c r="C43" s="4" t="n">
+        <v>3533431775000</v>
+      </c>
+      <c r="D43" s="4" t="n">
         <v>3033431775000</v>
       </c>
-      <c r="D43" s="4" t="n">
-        <v>3533431775000</v>
-      </c>
       <c r="E43" s="4" t="n">
-        <v>3610268431824</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1432,16 +1432,16 @@
         </is>
       </c>
       <c r="B46" s="4" t="n">
-        <v>0</v>
+        <v>3200268431824</v>
       </c>
       <c r="C46" s="4" t="n">
-        <v>0</v>
+        <v>3033431775000</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>3033431775000</v>
+        <v>0</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>3200268431824</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1470,16 +1470,16 @@
         </is>
       </c>
       <c r="B48" s="4" t="n">
+        <v>248276291750</v>
+      </c>
+      <c r="C48" s="4" t="n">
+        <v>256740022659</v>
+      </c>
+      <c r="D48" s="4" t="n">
+        <v>59493017350</v>
+      </c>
+      <c r="E48" s="4" t="n">
         <v>58340964113</v>
-      </c>
-      <c r="C48" s="4" t="n">
-        <v>59493017350</v>
-      </c>
-      <c r="D48" s="4" t="n">
-        <v>256740022659</v>
-      </c>
-      <c r="E48" s="4" t="n">
-        <v>248276291750</v>
       </c>
     </row>
     <row r="49">
@@ -1489,16 +1489,16 @@
         </is>
       </c>
       <c r="B49" s="4" t="n">
+        <v>16980000795</v>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>8909838294</v>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>8860645504</v>
+      </c>
+      <c r="E49" s="4" t="n">
         <v>14257812698</v>
-      </c>
-      <c r="C49" s="4" t="n">
-        <v>8860645504</v>
-      </c>
-      <c r="D49" s="4" t="n">
-        <v>8909838294</v>
-      </c>
-      <c r="E49" s="4" t="n">
-        <v>16980000795</v>
       </c>
     </row>
     <row r="50">
@@ -1508,16 +1508,16 @@
         </is>
       </c>
       <c r="B50" s="4" t="n">
+        <v>17804201744</v>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>23846393223</v>
+      </c>
+      <c r="D50" s="4" t="n">
+        <v>24188580704</v>
+      </c>
+      <c r="E50" s="4" t="n">
         <v>20791943497</v>
-      </c>
-      <c r="C50" s="4" t="n">
-        <v>24188580704</v>
-      </c>
-      <c r="D50" s="4" t="n">
-        <v>23846393223</v>
-      </c>
-      <c r="E50" s="4" t="n">
-        <v>17804201744</v>
       </c>
     </row>
     <row r="51">
@@ -1527,7 +1527,7 @@
         </is>
       </c>
       <c r="B51" s="4" t="n">
-        <v>10000000000</v>
+        <v>10083869378</v>
       </c>
       <c r="C51" s="4" t="n">
         <v>10000000000</v>
@@ -1536,7 +1536,7 @@
         <v>10000000000</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>10083869378</v>
+        <v>10000000000</v>
       </c>
     </row>
     <row r="52">
@@ -1546,16 +1546,16 @@
         </is>
       </c>
       <c r="B52" s="4" t="n">
+        <v>80632256999009</v>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>53244133820194</v>
+      </c>
+      <c r="D52" s="4" t="n">
+        <v>43788429454609</v>
+      </c>
+      <c r="E52" s="4" t="n">
         <v>26091547738863</v>
-      </c>
-      <c r="C52" s="4" t="n">
-        <v>43788429454609</v>
-      </c>
-      <c r="D52" s="4" t="n">
-        <v>53244133820194</v>
-      </c>
-      <c r="E52" s="4" t="n">
-        <v>80632256999009</v>
       </c>
     </row>
     <row r="53">
@@ -1565,16 +1565,16 @@
         </is>
       </c>
       <c r="B53" s="4" t="n">
+        <v>36532676815634</v>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>26947161543516</v>
+      </c>
+      <c r="D53" s="4" t="n">
+        <v>20158922867321</v>
+      </c>
+      <c r="E53" s="4" t="n">
         <v>15102289530963</v>
-      </c>
-      <c r="C53" s="4" t="n">
-        <v>20158922867321</v>
-      </c>
-      <c r="D53" s="4" t="n">
-        <v>26947161543516</v>
-      </c>
-      <c r="E53" s="4" t="n">
-        <v>36532676815634</v>
       </c>
     </row>
     <row r="54">
@@ -1584,16 +1584,16 @@
         </is>
       </c>
       <c r="B54" s="4" t="n">
+        <v>35016932279815</v>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>25934267565771</v>
+      </c>
+      <c r="D54" s="4" t="n">
+        <v>19197091992778</v>
+      </c>
+      <c r="E54" s="4" t="n">
         <v>13378593348270</v>
-      </c>
-      <c r="C54" s="4" t="n">
-        <v>19197091992778</v>
-      </c>
-      <c r="D54" s="4" t="n">
-        <v>25934267565771</v>
-      </c>
-      <c r="E54" s="4" t="n">
-        <v>35016932279815</v>
       </c>
     </row>
     <row r="55">
@@ -1603,16 +1603,16 @@
         </is>
       </c>
       <c r="B55" s="4" t="n">
+        <v>31079695096211</v>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>20522995942980</v>
+      </c>
+      <c r="D55" s="4" t="n">
+        <v>18061885497900</v>
+      </c>
+      <c r="E55" s="4" t="n">
         <v>6871600000000</v>
-      </c>
-      <c r="C55" s="4" t="n">
-        <v>18061885497900</v>
-      </c>
-      <c r="D55" s="4" t="n">
-        <v>20522995942980</v>
-      </c>
-      <c r="E55" s="4" t="n">
-        <v>31079695096211</v>
       </c>
     </row>
     <row r="56">
@@ -1622,16 +1622,16 @@
         </is>
       </c>
       <c r="B56" s="4" t="n">
+        <v>2000410883</v>
+      </c>
+      <c r="C56" s="4" t="n">
+        <v>66489220</v>
+      </c>
+      <c r="D56" s="4" t="n">
+        <v>606772700</v>
+      </c>
+      <c r="E56" s="4" t="n">
         <v>240252940500</v>
-      </c>
-      <c r="C56" s="4" t="n">
-        <v>606772700</v>
-      </c>
-      <c r="D56" s="4" t="n">
-        <v>66489220</v>
-      </c>
-      <c r="E56" s="4" t="n">
-        <v>2000410883</v>
       </c>
     </row>
     <row r="57">
@@ -1644,10 +1644,10 @@
         <v>0</v>
       </c>
       <c r="C57" s="4" t="n">
-        <v>0</v>
+        <v>126000000000</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>126000000000</v>
+        <v>0</v>
       </c>
       <c r="E57" s="4" t="n">
         <v>0</v>
@@ -1660,16 +1660,16 @@
         </is>
       </c>
       <c r="B58" s="4" t="n">
+        <v>1384739664586</v>
+      </c>
+      <c r="C58" s="4" t="n">
+        <v>878447688270</v>
+      </c>
+      <c r="D58" s="4" t="n">
+        <v>496359203753</v>
+      </c>
+      <c r="E58" s="4" t="n">
         <v>316020156985</v>
-      </c>
-      <c r="C58" s="4" t="n">
-        <v>496359203753</v>
-      </c>
-      <c r="D58" s="4" t="n">
-        <v>878447688270</v>
-      </c>
-      <c r="E58" s="4" t="n">
-        <v>1384739664586</v>
       </c>
     </row>
     <row r="59">
@@ -1679,16 +1679,16 @@
         </is>
       </c>
       <c r="B59" s="4" t="n">
+        <v>231830280548</v>
+      </c>
+      <c r="C59" s="4" t="n">
+        <v>183986993939</v>
+      </c>
+      <c r="D59" s="4" t="n">
+        <v>145714265723</v>
+      </c>
+      <c r="E59" s="4" t="n">
         <v>123723915438</v>
-      </c>
-      <c r="C59" s="4" t="n">
-        <v>145714265723</v>
-      </c>
-      <c r="D59" s="4" t="n">
-        <v>183986993939</v>
-      </c>
-      <c r="E59" s="4" t="n">
-        <v>231830280548</v>
       </c>
     </row>
     <row r="60">
@@ -1698,16 +1698,16 @@
         </is>
       </c>
       <c r="B60" s="4" t="n">
+        <v>265828841247</v>
+      </c>
+      <c r="C60" s="4" t="n">
+        <v>191122324100</v>
+      </c>
+      <c r="D60" s="4" t="n">
+        <v>136932073861</v>
+      </c>
+      <c r="E60" s="4" t="n">
         <v>132305599362</v>
-      </c>
-      <c r="C60" s="4" t="n">
-        <v>136932073861</v>
-      </c>
-      <c r="D60" s="4" t="n">
-        <v>191122324100</v>
-      </c>
-      <c r="E60" s="4" t="n">
-        <v>265828841247</v>
       </c>
     </row>
     <row r="61">
@@ -1755,16 +1755,16 @@
         </is>
       </c>
       <c r="B63" s="4" t="n">
+        <v>120138271307</v>
+      </c>
+      <c r="C63" s="4" t="n">
+        <v>174100135424</v>
+      </c>
+      <c r="D63" s="4" t="n">
+        <v>119141014630</v>
+      </c>
+      <c r="E63" s="4" t="n">
         <v>121870618991</v>
-      </c>
-      <c r="C63" s="4" t="n">
-        <v>119141014630</v>
-      </c>
-      <c r="D63" s="4" t="n">
-        <v>174100135424</v>
-      </c>
-      <c r="E63" s="4" t="n">
-        <v>120138271307</v>
       </c>
     </row>
     <row r="64">
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="B65" s="4" t="n">
-        <v>350000000</v>
+        <v>290000000</v>
       </c>
       <c r="C65" s="4" t="n">
         <v>290000000</v>
@@ -1802,7 +1802,7 @@
         <v>290000000</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>290000000</v>
+        <v>350000000</v>
       </c>
     </row>
     <row r="66">
@@ -1812,16 +1812,16 @@
         </is>
       </c>
       <c r="B66" s="4" t="n">
+        <v>1515744535819</v>
+      </c>
+      <c r="C66" s="4" t="n">
+        <v>1012893977745</v>
+      </c>
+      <c r="D66" s="4" t="n">
+        <v>961830874543</v>
+      </c>
+      <c r="E66" s="4" t="n">
         <v>1723696182693</v>
-      </c>
-      <c r="C66" s="4" t="n">
-        <v>961830874543</v>
-      </c>
-      <c r="D66" s="4" t="n">
-        <v>1012893977745</v>
-      </c>
-      <c r="E66" s="4" t="n">
-        <v>1515744535819</v>
       </c>
     </row>
     <row r="67">
@@ -1964,16 +1964,16 @@
         </is>
       </c>
       <c r="B74" s="4" t="n">
+        <v>5743148982</v>
+      </c>
+      <c r="C74" s="4" t="n">
+        <v>6512947402</v>
+      </c>
+      <c r="D74" s="4" t="n">
+        <v>6030077736</v>
+      </c>
+      <c r="E74" s="4" t="n">
         <v>15031084236</v>
-      </c>
-      <c r="C74" s="4" t="n">
-        <v>6030077736</v>
-      </c>
-      <c r="D74" s="4" t="n">
-        <v>6512947402</v>
-      </c>
-      <c r="E74" s="4" t="n">
-        <v>5743148982</v>
       </c>
     </row>
     <row r="75">
@@ -2002,16 +2002,16 @@
         </is>
       </c>
       <c r="B76" s="4" t="n">
+        <v>44099580183375</v>
+      </c>
+      <c r="C76" s="4" t="n">
+        <v>26296972276678</v>
+      </c>
+      <c r="D76" s="4" t="n">
+        <v>23629506587288</v>
+      </c>
+      <c r="E76" s="4" t="n">
         <v>10989258207900</v>
-      </c>
-      <c r="C76" s="4" t="n">
-        <v>23629506587288</v>
-      </c>
-      <c r="D76" s="4" t="n">
-        <v>26296972276678</v>
-      </c>
-      <c r="E76" s="4" t="n">
-        <v>44099580183375</v>
       </c>
     </row>
     <row r="77">
@@ -2021,16 +2021,16 @@
         </is>
       </c>
       <c r="B77" s="4" t="n">
+        <v>23113080210000</v>
+      </c>
+      <c r="C77" s="4" t="n">
+        <v>19613221200000</v>
+      </c>
+      <c r="D77" s="4" t="n">
+        <v>2176994200000</v>
+      </c>
+      <c r="E77" s="4" t="n">
         <v>1126140700000</v>
-      </c>
-      <c r="C77" s="4" t="n">
-        <v>2176994200000</v>
-      </c>
-      <c r="D77" s="4" t="n">
-        <v>19613221200000</v>
-      </c>
-      <c r="E77" s="4" t="n">
-        <v>23113080210000</v>
       </c>
     </row>
     <row r="78">
@@ -2040,16 +2040,16 @@
         </is>
       </c>
       <c r="B78" s="4" t="n">
-        <v>0</v>
+        <v>8606980418518</v>
       </c>
       <c r="C78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="4" t="n">
         <v>9191910000000</v>
       </c>
-      <c r="D78" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E78" s="4" t="n">
-        <v>8606980418518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -2097,16 +2097,16 @@
         </is>
       </c>
       <c r="B81" s="4" t="n">
+        <v>7475370203</v>
+      </c>
+      <c r="C81" s="4" t="n">
+        <v>-4961252868</v>
+      </c>
+      <c r="D81" s="4" t="n">
+        <v>-16520032167</v>
+      </c>
+      <c r="E81" s="4" t="n">
         <v>-10561943926</v>
-      </c>
-      <c r="C81" s="4" t="n">
-        <v>-16520032167</v>
-      </c>
-      <c r="D81" s="4" t="n">
-        <v>-4961252868</v>
-      </c>
-      <c r="E81" s="4" t="n">
-        <v>7475370203</v>
       </c>
     </row>
     <row r="82">
@@ -2192,16 +2192,16 @@
         </is>
       </c>
       <c r="B86" s="4" t="n">
+        <v>12372044184654</v>
+      </c>
+      <c r="C86" s="4" t="n">
+        <v>6688712329546</v>
+      </c>
+      <c r="D86" s="4" t="n">
+        <v>12277122419455</v>
+      </c>
+      <c r="E86" s="4" t="n">
         <v>9873679451826</v>
-      </c>
-      <c r="C86" s="4" t="n">
-        <v>12277122419455</v>
-      </c>
-      <c r="D86" s="4" t="n">
-        <v>6688712329546</v>
-      </c>
-      <c r="E86" s="4" t="n">
-        <v>12372044184654</v>
       </c>
     </row>
     <row r="87">
@@ -2287,16 +2287,16 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
+        <v>80632256999009</v>
+      </c>
+      <c r="C91" s="4" t="n">
+        <v>53244133820194</v>
+      </c>
+      <c r="D91" s="4" t="n">
+        <v>43788429454609</v>
+      </c>
+      <c r="E91" s="4" t="n">
         <v>26091547738863</v>
-      </c>
-      <c r="C91" s="4" t="n">
-        <v>43788429454609</v>
-      </c>
-      <c r="D91" s="4" t="n">
-        <v>53244133820194</v>
-      </c>
-      <c r="E91" s="4" t="n">
-        <v>80632256999009</v>
       </c>
     </row>
     <row r="92">
@@ -2305,10 +2305,10 @@
           <t>Cổ phiếu ưu đãi</t>
         </is>
       </c>
-      <c r="B92" s="4" t="n"/>
-      <c r="C92" s="4" t="n"/>
-      <c r="D92" s="4" t="n"/>
-      <c r="E92" s="4" t="n"/>
+      <c r="B92" s="4" t="inlineStr"/>
+      <c r="C92" s="4" t="inlineStr"/>
+      <c r="D92" s="4" t="inlineStr"/>
+      <c r="E92" s="4" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
@@ -2317,16 +2317,16 @@
         </is>
       </c>
       <c r="B93" s="4" t="n">
+        <v>3657418739619</v>
+      </c>
+      <c r="C93" s="4" t="n">
+        <v>2232105785348</v>
+      </c>
+      <c r="D93" s="4" t="n">
+        <v>1292046000000</v>
+      </c>
+      <c r="E93" s="4" t="n">
         <v>1000000000</v>
-      </c>
-      <c r="C93" s="4" t="n">
-        <v>1292046000000</v>
-      </c>
-      <c r="D93" s="4" t="n">
-        <v>2232105785348</v>
-      </c>
-      <c r="E93" s="4" t="n">
-        <v>3657418739619</v>
       </c>
     </row>
     <row r="94">
@@ -2374,16 +2374,16 @@
         </is>
       </c>
       <c r="B96" s="4" t="n">
+        <v>51121802352</v>
+      </c>
+      <c r="C96" s="4" t="n">
+        <v>30358344178</v>
+      </c>
+      <c r="D96" s="4" t="n">
+        <v>31649585853</v>
+      </c>
+      <c r="E96" s="4" t="n">
         <v>5305624911458</v>
-      </c>
-      <c r="C96" s="4" t="n">
-        <v>31649585853</v>
-      </c>
-      <c r="D96" s="4" t="n">
-        <v>30358344178</v>
-      </c>
-      <c r="E96" s="4" t="n">
-        <v>51121802352</v>
       </c>
     </row>
     <row r="97">
@@ -2545,16 +2545,16 @@
         </is>
       </c>
       <c r="B105" s="4" t="n">
-        <v>0</v>
+        <v>53765213326</v>
       </c>
       <c r="C105" s="4" t="n">
+        <v>8471319232</v>
+      </c>
+      <c r="D105" s="4" t="n">
         <v>2657487551</v>
       </c>
-      <c r="D105" s="4" t="n">
-        <v>8471319232</v>
-      </c>
       <c r="E105" s="4" t="n">
-        <v>53765213326</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -2602,16 +2602,16 @@
         </is>
       </c>
       <c r="B108" s="4" t="n">
+        <v>375518055392</v>
+      </c>
+      <c r="C108" s="4" t="n">
+        <v>251238807204</v>
+      </c>
+      <c r="D108" s="4" t="n">
+        <v>203693703731</v>
+      </c>
+      <c r="E108" s="4" t="n">
         <v>266845205536</v>
-      </c>
-      <c r="C108" s="4" t="n">
-        <v>203693703731</v>
-      </c>
-      <c r="D108" s="4" t="n">
-        <v>251238807204</v>
-      </c>
-      <c r="E108" s="4" t="n">
-        <v>375518055392</v>
       </c>
     </row>
     <row r="109">
@@ -2754,16 +2754,16 @@
         </is>
       </c>
       <c r="B116" s="4" t="n">
+        <v>23113080210000</v>
+      </c>
+      <c r="C116" s="4" t="n">
+        <v>19613221200000</v>
+      </c>
+      <c r="D116" s="4" t="n">
+        <v>2176994200000</v>
+      </c>
+      <c r="E116" s="4" t="n">
         <v>1126140700000</v>
-      </c>
-      <c r="C116" s="4" t="n">
-        <v>2176994200000</v>
-      </c>
-      <c r="D116" s="4" t="n">
-        <v>19613221200000</v>
-      </c>
-      <c r="E116" s="4" t="n">
-        <v>23113080210000</v>
       </c>
     </row>
     <row r="117">
@@ -2811,16 +2811,16 @@
         </is>
       </c>
       <c r="B119" s="4" t="n">
+        <v>12347939323386</v>
+      </c>
+      <c r="C119" s="4" t="n">
+        <v>6665324621285</v>
+      </c>
+      <c r="D119" s="4" t="n">
+        <v>12257063891765</v>
+      </c>
+      <c r="E119" s="4" t="n">
         <v>9872987551840</v>
-      </c>
-      <c r="C119" s="4" t="n">
-        <v>12257063891765</v>
-      </c>
-      <c r="D119" s="4" t="n">
-        <v>6665324621285</v>
-      </c>
-      <c r="E119" s="4" t="n">
-        <v>12347939323386</v>
       </c>
     </row>
     <row r="120">
@@ -2830,16 +2830,16 @@
         </is>
       </c>
       <c r="B120" s="4" t="n">
-        <v>0</v>
+        <v>53765213326</v>
       </c>
       <c r="C120" s="4" t="n">
+        <v>8471319232</v>
+      </c>
+      <c r="D120" s="4" t="n">
         <v>2657487551</v>
       </c>
-      <c r="D120" s="4" t="n">
-        <v>8471319232</v>
-      </c>
       <c r="E120" s="4" t="n">
-        <v>53765213326</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -2906,16 +2906,16 @@
         </is>
       </c>
       <c r="B124" s="4" t="n">
+        <v>20000000030</v>
+      </c>
+      <c r="C124" s="4" t="n">
+        <v>18754492342</v>
+      </c>
+      <c r="D124" s="4" t="n">
+        <v>16254492342</v>
+      </c>
+      <c r="E124" s="4" t="n">
         <v>13106909118</v>
-      </c>
-      <c r="C124" s="4" t="n">
-        <v>16254492342</v>
-      </c>
-      <c r="D124" s="4" t="n">
-        <v>18754492342</v>
-      </c>
-      <c r="E124" s="4" t="n">
-        <v>20000000030</v>
       </c>
     </row>
     <row r="125">
@@ -2925,16 +2925,16 @@
         </is>
       </c>
       <c r="B125" s="4" t="n">
+        <v>76597293421692</v>
+      </c>
+      <c r="C125" s="4" t="n">
+        <v>49341572003957</v>
+      </c>
+      <c r="D125" s="4" t="n">
+        <v>40594155139482</v>
+      </c>
+      <c r="E125" s="4" t="n">
         <v>25929858136745</v>
-      </c>
-      <c r="C125" s="4" t="n">
-        <v>40594155139482</v>
-      </c>
-      <c r="D125" s="4" t="n">
-        <v>49341572003957</v>
-      </c>
-      <c r="E125" s="4" t="n">
-        <v>76597293421692</v>
       </c>
     </row>
     <row r="126">
@@ -2944,16 +2944,16 @@
         </is>
       </c>
       <c r="B126" s="4" t="n">
+        <v>43859732477143</v>
+      </c>
+      <c r="C126" s="4" t="n">
+        <v>25911246001189</v>
+      </c>
+      <c r="D126" s="4" t="n">
+        <v>16619167038247</v>
+      </c>
+      <c r="E126" s="4" t="n">
         <v>9354605486589</v>
-      </c>
-      <c r="C126" s="4" t="n">
-        <v>16619167038247</v>
-      </c>
-      <c r="D126" s="4" t="n">
-        <v>25911246001189</v>
-      </c>
-      <c r="E126" s="4" t="n">
-        <v>43859732477143</v>
       </c>
     </row>
     <row r="127">
@@ -2963,16 +2963,16 @@
         </is>
       </c>
       <c r="B127" s="4" t="n">
+        <v>25218442812696</v>
+      </c>
+      <c r="C127" s="4" t="n">
+        <v>17670549755100</v>
+      </c>
+      <c r="D127" s="4" t="n">
+        <v>15040774984321</v>
+      </c>
+      <c r="E127" s="4" t="n">
         <v>10511124650851</v>
-      </c>
-      <c r="C127" s="4" t="n">
-        <v>15040774984321</v>
-      </c>
-      <c r="D127" s="4" t="n">
-        <v>17670549755100</v>
-      </c>
-      <c r="E127" s="4" t="n">
-        <v>25218442812696</v>
       </c>
     </row>
     <row r="128">
@@ -2982,16 +2982,16 @@
         </is>
       </c>
       <c r="B128" s="4" t="n">
+        <v>686848052984</v>
+      </c>
+      <c r="C128" s="4" t="n">
+        <v>539116528852</v>
+      </c>
+      <c r="D128" s="4" t="n">
+        <v>337852529010</v>
+      </c>
+      <c r="E128" s="4" t="n">
         <v>183085158587</v>
-      </c>
-      <c r="C128" s="4" t="n">
-        <v>337852529010</v>
-      </c>
-      <c r="D128" s="4" t="n">
-        <v>539116528852</v>
-      </c>
-      <c r="E128" s="4" t="n">
-        <v>686848052984</v>
       </c>
     </row>
     <row r="129">
@@ -3001,7 +3001,7 @@
         </is>
       </c>
       <c r="B129" s="4" t="n">
-        <v>0</v>
+        <v>195489000</v>
       </c>
       <c r="C129" s="4" t="n">
         <v>0</v>
@@ -3010,7 +3010,7 @@
         <v>0</v>
       </c>
       <c r="E129" s="4" t="n">
-        <v>195489000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -3020,16 +3020,16 @@
         </is>
       </c>
       <c r="B130" s="4" t="n">
+        <v>686652563984</v>
+      </c>
+      <c r="C130" s="4" t="n">
+        <v>539116528852</v>
+      </c>
+      <c r="D130" s="4" t="n">
+        <v>337852529010</v>
+      </c>
+      <c r="E130" s="4" t="n">
         <v>183085158587</v>
-      </c>
-      <c r="C130" s="4" t="n">
-        <v>337852529010</v>
-      </c>
-      <c r="D130" s="4" t="n">
-        <v>539116528852</v>
-      </c>
-      <c r="E130" s="4" t="n">
-        <v>686652563984</v>
       </c>
     </row>
     <row r="131">
@@ -3039,16 +3039,16 @@
         </is>
       </c>
       <c r="B131" s="4" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="C131" s="4" t="n">
+        <v>4752786</v>
+      </c>
+      <c r="D131" s="4" t="n">
+        <v>2693396029</v>
+      </c>
+      <c r="E131" s="4" t="n">
         <v>26781966648</v>
-      </c>
-      <c r="C131" s="4" t="n">
-        <v>2693396029</v>
-      </c>
-      <c r="D131" s="4" t="n">
-        <v>4752786</v>
-      </c>
-      <c r="E131" s="4" t="n">
-        <v>1200000</v>
       </c>
     </row>
     <row r="132">
@@ -3077,16 +3077,16 @@
         </is>
       </c>
       <c r="B133" s="4" t="n">
+        <v>686651363984</v>
+      </c>
+      <c r="C133" s="4" t="n">
+        <v>539111776066</v>
+      </c>
+      <c r="D133" s="4" t="n">
+        <v>335159132981</v>
+      </c>
+      <c r="E133" s="4" t="n">
         <v>156303191939</v>
-      </c>
-      <c r="C133" s="4" t="n">
-        <v>335159132981</v>
-      </c>
-      <c r="D133" s="4" t="n">
-        <v>539111776066</v>
-      </c>
-      <c r="E133" s="4" t="n">
-        <v>686651363984</v>
       </c>
     </row>
     <row r="134">
@@ -3115,16 +3115,16 @@
         </is>
       </c>
       <c r="B135" s="4" t="n">
+        <v>32804970727</v>
+      </c>
+      <c r="C135" s="4" t="n">
+        <v>93625988628</v>
+      </c>
+      <c r="D135" s="4" t="n">
+        <v>16059167017</v>
+      </c>
+      <c r="E135" s="4" t="n">
         <v>23877481391</v>
-      </c>
-      <c r="C135" s="4" t="n">
-        <v>16059167017</v>
-      </c>
-      <c r="D135" s="4" t="n">
-        <v>93625988628</v>
-      </c>
-      <c r="E135" s="4" t="n">
-        <v>32804970727</v>
       </c>
     </row>
     <row r="136">
@@ -3153,16 +3153,16 @@
         </is>
       </c>
       <c r="B137" s="4" t="n">
+        <v>-198000000</v>
+      </c>
+      <c r="C137" s="4" t="n">
+        <v>-171600000</v>
+      </c>
+      <c r="D137" s="4" t="n">
+        <v>-132000000</v>
+      </c>
+      <c r="E137" s="4" t="n">
         <v>-266750000</v>
-      </c>
-      <c r="C137" s="4" t="n">
-        <v>-132000000</v>
-      </c>
-      <c r="D137" s="4" t="n">
-        <v>-171600000</v>
-      </c>
-      <c r="E137" s="4" t="n">
-        <v>-198000000</v>
       </c>
     </row>
     <row r="138">
@@ -3172,16 +3172,16 @@
         </is>
       </c>
       <c r="B138" s="4" t="n">
+        <v>410200000</v>
+      </c>
+      <c r="C138" s="4" t="n">
+        <v>219400000</v>
+      </c>
+      <c r="D138" s="4" t="n">
+        <v>75000000</v>
+      </c>
+      <c r="E138" s="4" t="n">
         <v>11248150250</v>
-      </c>
-      <c r="C138" s="4" t="n">
-        <v>75000000</v>
-      </c>
-      <c r="D138" s="4" t="n">
-        <v>219400000</v>
-      </c>
-      <c r="E138" s="4" t="n">
-        <v>410200000</v>
       </c>
     </row>
     <row r="139">
@@ -3191,16 +3191,16 @@
         </is>
       </c>
       <c r="B139" s="4" t="n">
-        <v>0</v>
+        <v>1640794000</v>
       </c>
       <c r="C139" s="4" t="n">
+        <v>259390000</v>
+      </c>
+      <c r="D139" s="4" t="n">
         <v>246690000</v>
       </c>
-      <c r="D139" s="4" t="n">
-        <v>259390000</v>
-      </c>
       <c r="E139" s="4" t="n">
-        <v>1640794000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -3210,7 +3210,7 @@
         </is>
       </c>
       <c r="B140" s="4" t="n">
-        <v>0</v>
+        <v>12981358</v>
       </c>
       <c r="C140" s="4" t="n">
         <v>0</v>
@@ -3219,7 +3219,7 @@
         <v>0</v>
       </c>
       <c r="E140" s="4" t="n">
-        <v>12981358</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -3248,16 +3248,16 @@
         </is>
       </c>
       <c r="B142" s="4" t="n">
-        <v>0</v>
+        <v>3610268431824</v>
       </c>
       <c r="C142" s="4" t="n">
+        <v>3533431775000</v>
+      </c>
+      <c r="D142" s="4" t="n">
         <v>3033431775000</v>
       </c>
-      <c r="D142" s="4" t="n">
-        <v>3533431775000</v>
-      </c>
       <c r="E142" s="4" t="n">
-        <v>3610268431824</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -3343,16 +3343,16 @@
         </is>
       </c>
       <c r="B147" s="4" t="n">
+        <v>183408219803</v>
+      </c>
+      <c r="C147" s="4" t="n">
+        <v>195229298800</v>
+      </c>
+      <c r="D147" s="4" t="n">
+        <v>189298800</v>
+      </c>
+      <c r="E147" s="4" t="n">
         <v>184298800</v>
-      </c>
-      <c r="C147" s="4" t="n">
-        <v>189298800</v>
-      </c>
-      <c r="D147" s="4" t="n">
-        <v>195229298800</v>
-      </c>
-      <c r="E147" s="4" t="n">
-        <v>183408219803</v>
       </c>
     </row>
     <row r="148">
@@ -3381,16 +3381,16 @@
         </is>
       </c>
       <c r="B149" s="4" t="n">
+        <v>31079695096211</v>
+      </c>
+      <c r="C149" s="4" t="n">
+        <v>20522995942980</v>
+      </c>
+      <c r="D149" s="4" t="n">
+        <v>18061885497900</v>
+      </c>
+      <c r="E149" s="4" t="n">
         <v>6871600000000</v>
-      </c>
-      <c r="C149" s="4" t="n">
-        <v>18061885497900</v>
-      </c>
-      <c r="D149" s="4" t="n">
-        <v>20522995942980</v>
-      </c>
-      <c r="E149" s="4" t="n">
-        <v>31079695096211</v>
       </c>
     </row>
     <row r="150">
@@ -3457,16 +3457,16 @@
         </is>
       </c>
       <c r="B153" s="4" t="n">
-        <v>0</v>
+        <v>1504310847194</v>
       </c>
       <c r="C153" s="4" t="n">
-        <v>0</v>
+        <v>3574904342006</v>
       </c>
       <c r="D153" s="4" t="n">
-        <v>3574904342006</v>
+        <v>0</v>
       </c>
       <c r="E153" s="4" t="n">
-        <v>1504310847194</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -3514,16 +3514,16 @@
         </is>
       </c>
       <c r="B156" s="4" t="n">
-        <v>0</v>
+        <v>1459010095</v>
       </c>
       <c r="C156" s="4" t="n">
+        <v>756498450</v>
+      </c>
+      <c r="D156" s="4" t="n">
         <v>819874627</v>
       </c>
-      <c r="D156" s="4" t="n">
-        <v>756498450</v>
-      </c>
       <c r="E156" s="4" t="n">
-        <v>1459010095</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
@@ -3609,16 +3609,16 @@
         </is>
       </c>
       <c r="B161" s="4" t="n">
+        <v>1509970833337</v>
+      </c>
+      <c r="C161" s="4" t="n">
+        <v>1006350476843</v>
+      </c>
+      <c r="D161" s="4" t="n">
+        <v>955770243307</v>
+      </c>
+      <c r="E161" s="4" t="n">
         <v>1708634544957</v>
-      </c>
-      <c r="C161" s="4" t="n">
-        <v>955770243307</v>
-      </c>
-      <c r="D161" s="4" t="n">
-        <v>1006350476843</v>
-      </c>
-      <c r="E161" s="4" t="n">
-        <v>1509970833337</v>
       </c>
     </row>
     <row r="162">
@@ -3647,16 +3647,16 @@
         </is>
       </c>
       <c r="B163" s="4" t="n">
+        <v>31720060628518</v>
+      </c>
+      <c r="C163" s="4" t="n">
+        <v>19613221200000</v>
+      </c>
+      <c r="D163" s="4" t="n">
+        <v>11368904200000</v>
+      </c>
+      <c r="E163" s="4" t="n">
         <v>1126140700000</v>
-      </c>
-      <c r="C163" s="4" t="n">
-        <v>11368904200000</v>
-      </c>
-      <c r="D163" s="4" t="n">
-        <v>19613221200000</v>
-      </c>
-      <c r="E163" s="4" t="n">
-        <v>31720060628518</v>
       </c>
     </row>
     <row r="164">
@@ -3685,16 +3685,16 @@
         </is>
       </c>
       <c r="B165" s="4" t="n">
+        <v>12347939323386</v>
+      </c>
+      <c r="C165" s="4" t="n">
+        <v>6665324621285</v>
+      </c>
+      <c r="D165" s="4" t="n">
+        <v>12257063891765</v>
+      </c>
+      <c r="E165" s="4" t="n">
         <v>9872987551840</v>
-      </c>
-      <c r="C165" s="4" t="n">
-        <v>12257063891765</v>
-      </c>
-      <c r="D165" s="4" t="n">
-        <v>6665324621285</v>
-      </c>
-      <c r="E165" s="4" t="n">
-        <v>12347939323386</v>
       </c>
     </row>
     <row r="166">
@@ -3704,16 +3704,16 @@
         </is>
       </c>
       <c r="B166" s="4" t="n">
+        <v>24104861268</v>
+      </c>
+      <c r="C166" s="4" t="n">
+        <v>23387708261</v>
+      </c>
+      <c r="D166" s="4" t="n">
+        <v>20058527690</v>
+      </c>
+      <c r="E166" s="4" t="n">
         <v>691899986</v>
-      </c>
-      <c r="C166" s="4" t="n">
-        <v>20058527690</v>
-      </c>
-      <c r="D166" s="4" t="n">
-        <v>23387708261</v>
-      </c>
-      <c r="E166" s="4" t="n">
-        <v>24104861268</v>
       </c>
     </row>
     <row r="167">
@@ -3818,16 +3818,16 @@
         </is>
       </c>
       <c r="B172" s="4" t="n">
-        <v>0</v>
+        <v>2311308021</v>
       </c>
       <c r="C172" s="4" t="n">
-        <v>0</v>
+        <v>1961322120</v>
       </c>
       <c r="D172" s="4" t="n">
-        <v>1961322120</v>
+        <v>0</v>
       </c>
       <c r="E172" s="4" t="n">
-        <v>2311308021</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173">
@@ -3856,16 +3856,16 @@
         </is>
       </c>
       <c r="B174" s="4" t="n">
+        <v>22556742060000</v>
+      </c>
+      <c r="C174" s="4" t="n">
+        <v>17055403900000</v>
+      </c>
+      <c r="D174" s="4" t="n">
+        <v>1634479940000</v>
+      </c>
+      <c r="E174" s="4" t="n">
         <v>843650040000</v>
-      </c>
-      <c r="C174" s="4" t="n">
-        <v>1634479940000</v>
-      </c>
-      <c r="D174" s="4" t="n">
-        <v>17055403900000</v>
-      </c>
-      <c r="E174" s="4" t="n">
-        <v>22556742060000</v>
       </c>
     </row>
     <row r="175">
@@ -3875,16 +3875,16 @@
         </is>
       </c>
       <c r="B175" s="4" t="n">
-        <v>0</v>
+        <v>2720000</v>
       </c>
       <c r="C175" s="4" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D175" s="4" t="n">
         <v>50000</v>
       </c>
-      <c r="D175" s="4" t="n">
-        <v>20000</v>
-      </c>
       <c r="E175" s="4" t="n">
-        <v>2720000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
@@ -3894,16 +3894,16 @@
         </is>
       </c>
       <c r="B176" s="4" t="n">
+        <v>1860100000</v>
+      </c>
+      <c r="C176" s="4" t="n">
+        <v>7282100000</v>
+      </c>
+      <c r="D176" s="4" t="n">
+        <v>23749500000</v>
+      </c>
+      <c r="E176" s="4" t="n">
         <v>9799131256</v>
-      </c>
-      <c r="C176" s="4" t="n">
-        <v>23749500000</v>
-      </c>
-      <c r="D176" s="4" t="n">
-        <v>7282100000</v>
-      </c>
-      <c r="E176" s="4" t="n">
-        <v>1860100000</v>
       </c>
     </row>
     <row r="177">
@@ -3932,16 +3932,16 @@
         </is>
       </c>
       <c r="B178" s="4" t="n">
-        <v>0</v>
+        <v>1230262890000</v>
       </c>
       <c r="C178" s="4" t="n">
-        <v>0</v>
+        <v>18786720000</v>
       </c>
       <c r="D178" s="4" t="n">
-        <v>18786720000</v>
+        <v>0</v>
       </c>
       <c r="E178" s="4" t="n">
-        <v>1230262890000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179">
@@ -3970,16 +3970,16 @@
         </is>
       </c>
       <c r="B180" s="4" t="n">
+        <v>325307278790000</v>
+      </c>
+      <c r="C180" s="4" t="n">
+        <v>231123600446000</v>
+      </c>
+      <c r="D180" s="4" t="n">
+        <v>143415009129900</v>
+      </c>
+      <c r="E180" s="4" t="n">
         <v>146560432630000</v>
-      </c>
-      <c r="C180" s="4" t="n">
-        <v>143415009129900</v>
-      </c>
-      <c r="D180" s="4" t="n">
-        <v>231123600446000</v>
-      </c>
-      <c r="E180" s="4" t="n">
-        <v>325307278790000</v>
       </c>
     </row>
     <row r="181">
@@ -3989,16 +3989,16 @@
         </is>
       </c>
       <c r="B181" s="4" t="n">
+        <v>240019596860000</v>
+      </c>
+      <c r="C181" s="4" t="n">
+        <v>141951366816000</v>
+      </c>
+      <c r="D181" s="4" t="n">
+        <v>77561084029900</v>
+      </c>
+      <c r="E181" s="4" t="n">
         <v>84523895380000</v>
-      </c>
-      <c r="C181" s="4" t="n">
-        <v>77561084029900</v>
-      </c>
-      <c r="D181" s="4" t="n">
-        <v>141951366816000</v>
-      </c>
-      <c r="E181" s="4" t="n">
-        <v>240019596860000</v>
       </c>
     </row>
     <row r="182">
@@ -4008,16 +4008,16 @@
         </is>
       </c>
       <c r="B182" s="4" t="n">
+        <v>1467945100000</v>
+      </c>
+      <c r="C182" s="4" t="n">
+        <v>1013558230000</v>
+      </c>
+      <c r="D182" s="4" t="n">
+        <v>314582980000</v>
+      </c>
+      <c r="E182" s="4" t="n">
         <v>139546850000</v>
-      </c>
-      <c r="C182" s="4" t="n">
-        <v>314582980000</v>
-      </c>
-      <c r="D182" s="4" t="n">
-        <v>1013558230000</v>
-      </c>
-      <c r="E182" s="4" t="n">
-        <v>1467945100000</v>
       </c>
     </row>
     <row r="183">
@@ -4027,16 +4027,16 @@
         </is>
       </c>
       <c r="B183" s="4" t="n">
+        <v>56063707010000</v>
+      </c>
+      <c r="C183" s="4" t="n">
+        <v>72409443760000</v>
+      </c>
+      <c r="D183" s="4" t="n">
+        <v>62731799490000</v>
+      </c>
+      <c r="E183" s="4" t="n">
         <v>60455199550000</v>
-      </c>
-      <c r="C183" s="4" t="n">
-        <v>62731799490000</v>
-      </c>
-      <c r="D183" s="4" t="n">
-        <v>72409443760000</v>
-      </c>
-      <c r="E183" s="4" t="n">
-        <v>56063707010000</v>
       </c>
     </row>
     <row r="184">
@@ -4046,16 +4046,16 @@
         </is>
       </c>
       <c r="B184" s="4" t="n">
+        <v>26601662760000</v>
+      </c>
+      <c r="C184" s="4" t="n">
+        <v>15028179710000</v>
+      </c>
+      <c r="D184" s="4" t="n">
+        <v>1862706260000</v>
+      </c>
+      <c r="E184" s="4" t="n">
         <v>735109450000</v>
-      </c>
-      <c r="C184" s="4" t="n">
-        <v>1862706260000</v>
-      </c>
-      <c r="D184" s="4" t="n">
-        <v>15028179710000</v>
-      </c>
-      <c r="E184" s="4" t="n">
-        <v>26601662760000</v>
       </c>
     </row>
     <row r="185">
@@ -4065,16 +4065,16 @@
         </is>
       </c>
       <c r="B185" s="4" t="n">
+        <v>1154367060000</v>
+      </c>
+      <c r="C185" s="4" t="n">
+        <v>721051930000</v>
+      </c>
+      <c r="D185" s="4" t="n">
+        <v>944836370000</v>
+      </c>
+      <c r="E185" s="4" t="n">
         <v>706681400000</v>
-      </c>
-      <c r="C185" s="4" t="n">
-        <v>944836370000</v>
-      </c>
-      <c r="D185" s="4" t="n">
-        <v>721051930000</v>
-      </c>
-      <c r="E185" s="4" t="n">
-        <v>1154367060000</v>
       </c>
     </row>
     <row r="186">
@@ -4103,16 +4103,16 @@
         </is>
       </c>
       <c r="B187" s="4" t="n">
+        <v>192827990000</v>
+      </c>
+      <c r="C187" s="4" t="n">
+        <v>348405300000</v>
+      </c>
+      <c r="D187" s="4" t="n">
+        <v>472237200000</v>
+      </c>
+      <c r="E187" s="4" t="n">
         <v>719450400000</v>
-      </c>
-      <c r="C187" s="4" t="n">
-        <v>472237200000</v>
-      </c>
-      <c r="D187" s="4" t="n">
-        <v>348405300000</v>
-      </c>
-      <c r="E187" s="4" t="n">
-        <v>192827990000</v>
       </c>
     </row>
     <row r="188">
@@ -4122,16 +4122,16 @@
         </is>
       </c>
       <c r="B188" s="4" t="n">
+        <v>174185350000</v>
+      </c>
+      <c r="C188" s="4" t="n">
+        <v>132398410000</v>
+      </c>
+      <c r="D188" s="4" t="n">
+        <v>417620180000</v>
+      </c>
+      <c r="E188" s="4" t="n">
         <v>634486460000</v>
-      </c>
-      <c r="C188" s="4" t="n">
-        <v>417620180000</v>
-      </c>
-      <c r="D188" s="4" t="n">
-        <v>132398410000</v>
-      </c>
-      <c r="E188" s="4" t="n">
-        <v>174185350000</v>
       </c>
     </row>
     <row r="189">
@@ -4141,16 +4141,16 @@
         </is>
       </c>
       <c r="B189" s="4" t="n">
+        <v>18642640000</v>
+      </c>
+      <c r="C189" s="4" t="n">
+        <v>216006890000</v>
+      </c>
+      <c r="D189" s="4" t="n">
+        <v>54617020000</v>
+      </c>
+      <c r="E189" s="4" t="n">
         <v>84963940000</v>
-      </c>
-      <c r="C189" s="4" t="n">
-        <v>54617020000</v>
-      </c>
-      <c r="D189" s="4" t="n">
-        <v>216006890000</v>
-      </c>
-      <c r="E189" s="4" t="n">
-        <v>18642640000</v>
       </c>
     </row>
     <row r="190">
@@ -4198,16 +4198,16 @@
         </is>
       </c>
       <c r="B192" s="4" t="n">
-        <v>0</v>
+        <v>1291904460000</v>
       </c>
       <c r="C192" s="4" t="n">
-        <v>0</v>
+        <v>875589460000</v>
       </c>
       <c r="D192" s="4" t="n">
-        <v>875589460000</v>
+        <v>0</v>
       </c>
       <c r="E192" s="4" t="n">
-        <v>1291904460000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193">
@@ -4236,16 +4236,16 @@
         </is>
       </c>
       <c r="B194" s="4" t="n">
-        <v>0</v>
+        <v>9407201530000</v>
       </c>
       <c r="C194" s="4" t="n">
-        <v>0</v>
+        <v>15338753340000</v>
       </c>
       <c r="D194" s="4" t="n">
-        <v>15338753340000</v>
+        <v>0</v>
       </c>
       <c r="E194" s="4" t="n">
-        <v>9407201530000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195">
@@ -4274,16 +4274,16 @@
         </is>
       </c>
       <c r="B196" s="4" t="n">
+        <v>10702593296252</v>
+      </c>
+      <c r="C196" s="4" t="n">
+        <v>10024246349048</v>
+      </c>
+      <c r="D196" s="4" t="n">
+        <v>5774724796539</v>
+      </c>
+      <c r="E196" s="4" t="n">
         <v>2330045069459</v>
-      </c>
-      <c r="C196" s="4" t="n">
-        <v>5774724796539</v>
-      </c>
-      <c r="D196" s="4" t="n">
-        <v>10024246349048</v>
-      </c>
-      <c r="E196" s="4" t="n">
-        <v>10702593296252</v>
       </c>
     </row>
     <row r="197">
@@ -4293,16 +4293,16 @@
         </is>
       </c>
       <c r="B197" s="4" t="n">
+        <v>6447211380125</v>
+      </c>
+      <c r="C197" s="4" t="n">
+        <v>8245482244688</v>
+      </c>
+      <c r="D197" s="4" t="n">
+        <v>2945784273957</v>
+      </c>
+      <c r="E197" s="4" t="n">
         <v>2278125882711</v>
-      </c>
-      <c r="C197" s="4" t="n">
-        <v>2945784273957</v>
-      </c>
-      <c r="D197" s="4" t="n">
-        <v>8245482244688</v>
-      </c>
-      <c r="E197" s="4" t="n">
-        <v>6447211380125</v>
       </c>
     </row>
     <row r="198">
@@ -4521,16 +4521,16 @@
         </is>
       </c>
       <c r="B209" s="4" t="n">
+        <v>49373986618</v>
+      </c>
+      <c r="C209" s="4" t="n">
+        <v>44613698630</v>
+      </c>
+      <c r="D209" s="4" t="n">
+        <v>1031489346567</v>
+      </c>
+      <c r="E209" s="4" t="n">
         <v>51919186748</v>
-      </c>
-      <c r="C209" s="4" t="n">
-        <v>1031489346567</v>
-      </c>
-      <c r="D209" s="4" t="n">
-        <v>44613698630</v>
-      </c>
-      <c r="E209" s="4" t="n">
-        <v>49373986618</v>
       </c>
     </row>
   </sheetData>
@@ -4547,11 +4547,11 @@
   <dimension ref="A1:E80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="114" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4562,22 +4562,22 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>2022</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
         </is>
       </c>
     </row>
@@ -4588,16 +4588,16 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
+        <v>11217426514650</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>7615253240537</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>5257070533399</v>
+      </c>
+      <c r="E2" s="4" t="n">
         <v>5218182207076</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>5257070533399</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>7615253240537</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>11217426514650</v>
       </c>
     </row>
     <row r="3">
@@ -4626,16 +4626,16 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
+        <v>11217426514650</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>7615253240537</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>5257070533399</v>
+      </c>
+      <c r="E4" s="4" t="n">
         <v>5218182207076</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>5257070533399</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>7615253240537</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>11217426514650</v>
       </c>
     </row>
     <row r="5">
@@ -4645,16 +4645,16 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
+        <v>-1213554689735</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>-695459394838</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>-664101469631</v>
+      </c>
+      <c r="E5" s="4" t="n">
         <v>-990754662144</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>-664101469631</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>-695459394838</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>-1213554689735</v>
       </c>
     </row>
     <row r="6">
@@ -4664,16 +4664,16 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
+        <v>10003871824915</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>6919793845699</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>4592969063768</v>
+      </c>
+      <c r="E6" s="4" t="n">
         <v>4227427544932</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>4592969063768</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>6919793845699</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>10003871824915</v>
       </c>
     </row>
     <row r="7">
@@ -4683,16 +4683,16 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
+        <v>-658975463710</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>-566893494770</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>-500212004426</v>
+      </c>
+      <c r="E7" s="4" t="n">
         <v>-480433213874</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>-500212004426</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>-566893494770</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>-658975463710</v>
       </c>
     </row>
     <row r="8">
@@ -4702,16 +4702,16 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
+        <v>7109123949934</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>4802352563838</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>3029925582883</v>
+      </c>
+      <c r="E8" s="4" t="n">
         <v>3033107909184</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>3029925582883</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>4802352563838</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>7109123949934</v>
       </c>
     </row>
     <row r="9">
@@ -4721,16 +4721,16 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
+        <v>7108700741609</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>4802105868186</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>3028297410899</v>
+      </c>
+      <c r="E9" s="4" t="n">
         <v>3057657087640</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>3028297410899</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>4802105868186</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>7108700741609</v>
       </c>
     </row>
     <row r="10">
@@ -4740,16 +4740,16 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
+        <v>-1422857625411</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>-955991010186</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>-626761513445</v>
+      </c>
+      <c r="E10" s="4" t="n">
         <v>-631684895743</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>-626761513445</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>-955991010186</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>-1422857625411</v>
       </c>
     </row>
     <row r="11">
@@ -4759,16 +4759,16 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
+        <v>-2514261090</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>3580065571</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>1907070175</v>
+      </c>
+      <c r="E11" s="4" t="n">
         <v>691899986</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>1907070175</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>3580065571</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>-2514261090</v>
       </c>
     </row>
     <row r="12">
@@ -4778,16 +4778,16 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
+        <v>5683328855108</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>3849694923571</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>2403442967629</v>
+      </c>
+      <c r="E12" s="4" t="n">
         <v>2426664091883</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>2403442967629</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>3849694923571</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>5683328855108</v>
       </c>
     </row>
     <row r="13">
@@ -4816,16 +4816,16 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
+        <v>5683328855108</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>3849694923571</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>2403442967629</v>
+      </c>
+      <c r="E14" s="4" t="n">
         <v>2426664091883</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>2403442967629</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>3849694923571</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>5683328855108</v>
       </c>
     </row>
     <row r="15">
@@ -4835,16 +4835,16 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
+        <v>2713</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>8716</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>14119</v>
+      </c>
+      <c r="E15" s="4" t="n">
         <v>21548</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>14119</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>8716</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>2713</v>
       </c>
     </row>
     <row r="16">
@@ -4873,16 +4873,16 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
+        <v>957608985434</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>600923377250</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>476833068936</v>
+      </c>
+      <c r="E17" s="4" t="n">
         <v>888247795556</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>476833068936</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>600923377250</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>957608985434</v>
       </c>
     </row>
     <row r="18">
@@ -4911,16 +4911,16 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
+        <v>1715251565918</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>1180992811061</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>944470298386</v>
+      </c>
+      <c r="E19" s="4" t="n">
         <v>1302953436567</v>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>944470298386</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>1180992811061</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>1715251565918</v>
       </c>
     </row>
     <row r="20">
@@ -4949,16 +4949,16 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
+        <v>109980172740</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>50962737249</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>49528058050</v>
+      </c>
+      <c r="E21" s="4" t="n">
         <v>52348947599</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>49528058050</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>50962737249</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>109980172740</v>
       </c>
     </row>
     <row r="22">
@@ -5006,16 +5006,16 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
+        <v>6603197687</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>4185017363</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>46276350627</v>
+      </c>
+      <c r="E24" s="4" t="n">
         <v>137749081244</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>46276350627</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>4185017363</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>6603197687</v>
       </c>
     </row>
     <row r="25">
@@ -5044,16 +5044,16 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
+        <v>3669453931882</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>2449688939032</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>1643446234600</v>
+      </c>
+      <c r="E26" s="4" t="n">
         <v>901204582596</v>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>1643446234600</v>
-      </c>
-      <c r="D26" s="4" t="n">
-        <v>2449688939032</v>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>3669453931882</v>
       </c>
     </row>
     <row r="27">
@@ -5063,16 +5063,16 @@
         </is>
       </c>
       <c r="B27" s="4" t="n">
+        <v>3662416587827</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>2448980152070</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>1643446234600</v>
+      </c>
+      <c r="E27" s="4" t="n">
         <v>901204582596</v>
-      </c>
-      <c r="C27" s="4" t="n">
-        <v>1643446234600</v>
-      </c>
-      <c r="D27" s="4" t="n">
-        <v>2448980152070</v>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>3662416587827</v>
       </c>
     </row>
     <row r="28">
@@ -5082,16 +5082,16 @@
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>0</v>
+        <v>6910975255</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0</v>
+        <v>683706962</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>683706962</v>
+        <v>0</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>6910975255</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -5101,16 +5101,16 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>0</v>
+        <v>126368800</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0</v>
+        <v>25080000</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>25080000</v>
+        <v>0</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>126368800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -5120,16 +5120,16 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
+        <v>180059518864</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>110341784335</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>42491805310</v>
+      </c>
+      <c r="E30" s="4" t="n">
         <v>18529621544</v>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>42491805310</v>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>110341784335</v>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>180059518864</v>
       </c>
     </row>
     <row r="31">
@@ -5139,16 +5139,16 @@
         </is>
       </c>
       <c r="B31" s="4" t="n">
+        <v>3727517878641</v>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>2621919468982</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>1602447022922</v>
+      </c>
+      <c r="E31" s="4" t="n">
         <v>1502853415354</v>
-      </c>
-      <c r="C31" s="4" t="n">
-        <v>1602447022922</v>
-      </c>
-      <c r="D31" s="4" t="n">
-        <v>2621919468982</v>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>3727517878641</v>
       </c>
     </row>
     <row r="32">
@@ -5158,16 +5158,16 @@
         </is>
       </c>
       <c r="B32" s="4" t="n">
+        <v>548520255484</v>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>432978205265</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>370456358951</v>
+      </c>
+      <c r="E32" s="4" t="n">
         <v>257993106848</v>
-      </c>
-      <c r="C32" s="4" t="n">
-        <v>370456358951</v>
-      </c>
-      <c r="D32" s="4" t="n">
-        <v>432978205265</v>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>548520255484</v>
       </c>
     </row>
     <row r="33">
@@ -5196,16 +5196,16 @@
         </is>
       </c>
       <c r="B34" s="4" t="n">
+        <v>302431008000</v>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>163260900000</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>81121335617</v>
+      </c>
+      <c r="E34" s="4" t="n">
         <v>156302219768</v>
-      </c>
-      <c r="C34" s="4" t="n">
-        <v>81121335617</v>
-      </c>
-      <c r="D34" s="4" t="n">
-        <v>163260900000</v>
-      </c>
-      <c r="E34" s="4" t="n">
-        <v>302431008000</v>
       </c>
     </row>
     <row r="35">
@@ -5215,16 +5215,16 @@
         </is>
       </c>
       <c r="B35" s="4" t="n">
+        <v>-431640082069</v>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>-204396149905</v>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>-179035354683</v>
+      </c>
+      <c r="E35" s="4" t="n">
         <v>-198923624516</v>
-      </c>
-      <c r="C35" s="4" t="n">
-        <v>-179035354683</v>
-      </c>
-      <c r="D35" s="4" t="n">
-        <v>-204396149905</v>
-      </c>
-      <c r="E35" s="4" t="n">
-        <v>-431640082069</v>
       </c>
     </row>
     <row r="36">
@@ -5234,16 +5234,16 @@
         </is>
       </c>
       <c r="B36" s="4" t="n">
+        <v>-427957520911</v>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>-204145264905</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>-179035354683</v>
+      </c>
+      <c r="E36" s="4" t="n">
         <v>-198913624516</v>
-      </c>
-      <c r="C36" s="4" t="n">
-        <v>-179035354683</v>
-      </c>
-      <c r="D36" s="4" t="n">
-        <v>-204145264905</v>
-      </c>
-      <c r="E36" s="4" t="n">
-        <v>-427957520911</v>
       </c>
     </row>
     <row r="37">
@@ -5253,16 +5253,16 @@
         </is>
       </c>
       <c r="B37" s="4" t="n">
-        <v>0</v>
+        <v>-3682561158</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>0</v>
+        <v>-250885000</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>-250885000</v>
+        <v>0</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>-3682561158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -5272,16 +5272,16 @@
         </is>
       </c>
       <c r="B38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="4" t="n">
         <v>-10000000</v>
-      </c>
-      <c r="C38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -5348,16 +5348,16 @@
         </is>
       </c>
       <c r="B42" s="4" t="n">
+        <v>-1951876404</v>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>-6031468910</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>-4771003744</v>
+      </c>
+      <c r="E42" s="4" t="n">
         <v>-3599620</v>
-      </c>
-      <c r="C42" s="4" t="n">
-        <v>-4771003744</v>
-      </c>
-      <c r="D42" s="4" t="n">
-        <v>-6031468910</v>
-      </c>
-      <c r="E42" s="4" t="n">
-        <v>-1951876404</v>
       </c>
     </row>
     <row r="43">
@@ -5386,7 +5386,7 @@
         </is>
       </c>
       <c r="B44" s="4" t="n">
-        <v>0</v>
+        <v>-13459159</v>
       </c>
       <c r="C44" s="4" t="n">
         <v>0</v>
@@ -5395,7 +5395,7 @@
         <v>0</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>-13459159</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -5405,16 +5405,16 @@
         </is>
       </c>
       <c r="B45" s="4" t="n">
+        <v>-391454796421</v>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>-259060189756</v>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>-183646638072</v>
+      </c>
+      <c r="E45" s="4" t="n">
         <v>-154528078451</v>
-      </c>
-      <c r="C45" s="4" t="n">
-        <v>-183646638072</v>
-      </c>
-      <c r="D45" s="4" t="n">
-        <v>-259060189756</v>
-      </c>
-      <c r="E45" s="4" t="n">
-        <v>-391454796421</v>
       </c>
     </row>
     <row r="46">
@@ -5424,16 +5424,16 @@
         </is>
       </c>
       <c r="B46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>-208000</v>
+      </c>
+      <c r="E46" s="4" t="n">
         <v>-274074074</v>
-      </c>
-      <c r="C46" s="4" t="n">
-        <v>-208000</v>
-      </c>
-      <c r="D46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -5481,16 +5481,16 @@
         </is>
       </c>
       <c r="B49" s="4" t="n">
+        <v>-101719576574</v>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>-44478890519</v>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>-43185736098</v>
+      </c>
+      <c r="E49" s="4" t="n">
         <v>-48078060820</v>
-      </c>
-      <c r="C49" s="4" t="n">
-        <v>-43185736098</v>
-      </c>
-      <c r="D49" s="4" t="n">
-        <v>-44478890519</v>
-      </c>
-      <c r="E49" s="4" t="n">
-        <v>-101719576574</v>
       </c>
     </row>
     <row r="50">
@@ -5519,16 +5519,16 @@
         </is>
       </c>
       <c r="B51" s="4" t="n">
+        <v>-286774899108</v>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>-181492695748</v>
+      </c>
+      <c r="D51" s="4" t="n">
+        <v>-253462529034</v>
+      </c>
+      <c r="E51" s="4" t="n">
         <v>-588947224663</v>
-      </c>
-      <c r="C51" s="4" t="n">
-        <v>-253462529034</v>
-      </c>
-      <c r="D51" s="4" t="n">
-        <v>-181492695748</v>
-      </c>
-      <c r="E51" s="4" t="n">
-        <v>-286774899108</v>
       </c>
     </row>
     <row r="52">
@@ -5557,16 +5557,16 @@
         </is>
       </c>
       <c r="B53" s="4" t="n">
+        <v>46094785235</v>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>26516220809</v>
+      </c>
+      <c r="D53" s="4" t="n">
+        <v>18812470414</v>
+      </c>
+      <c r="E53" s="4" t="n">
         <v>24523594439</v>
-      </c>
-      <c r="C53" s="4" t="n">
-        <v>18812470414</v>
-      </c>
-      <c r="D53" s="4" t="n">
-        <v>26516220809</v>
-      </c>
-      <c r="E53" s="4" t="n">
-        <v>46094785235</v>
       </c>
     </row>
     <row r="54">
@@ -5576,16 +5576,16 @@
         </is>
       </c>
       <c r="B54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="4" t="n">
         <v>14002400000</v>
-      </c>
-      <c r="C54" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -5595,16 +5595,16 @@
         </is>
       </c>
       <c r="B55" s="4" t="n">
+        <v>45376233569</v>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>17491002103</v>
+      </c>
+      <c r="D55" s="4" t="n">
+        <v>12870125334</v>
+      </c>
+      <c r="E55" s="4" t="n">
         <v>10521194439</v>
-      </c>
-      <c r="C55" s="4" t="n">
-        <v>12870125334</v>
-      </c>
-      <c r="D55" s="4" t="n">
-        <v>17491002103</v>
-      </c>
-      <c r="E55" s="4" t="n">
-        <v>45376233569</v>
       </c>
     </row>
     <row r="56">
@@ -5633,16 +5633,16 @@
         </is>
       </c>
       <c r="B57" s="4" t="n">
-        <v>0</v>
+        <v>718551666</v>
       </c>
       <c r="C57" s="4" t="n">
+        <v>9025218706</v>
+      </c>
+      <c r="D57" s="4" t="n">
         <v>5942345080</v>
       </c>
-      <c r="D57" s="4" t="n">
-        <v>9025218706</v>
-      </c>
       <c r="E57" s="4" t="n">
-        <v>718551666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -5652,16 +5652,16 @@
         </is>
       </c>
       <c r="B58" s="4" t="n">
+        <v>-2281867196506</v>
+      </c>
+      <c r="C58" s="4" t="n">
+        <v>-1577064007900</v>
+      </c>
+      <c r="D58" s="4" t="n">
+        <v>-1081643946873</v>
+      </c>
+      <c r="E58" s="4" t="n">
         <v>-738410016313</v>
-      </c>
-      <c r="C58" s="4" t="n">
-        <v>-1081643946873</v>
-      </c>
-      <c r="D58" s="4" t="n">
-        <v>-1577064007900</v>
-      </c>
-      <c r="E58" s="4" t="n">
-        <v>-2281867196506</v>
       </c>
     </row>
     <row r="59">
@@ -5671,16 +5671,16 @@
         </is>
       </c>
       <c r="B59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="4" t="n">
         <v>-1400000000</v>
-      </c>
-      <c r="C59" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D59" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -5690,16 +5690,16 @@
         </is>
       </c>
       <c r="B60" s="4" t="n">
+        <v>-2055011378498</v>
+      </c>
+      <c r="C60" s="4" t="n">
+        <v>-1471244444534</v>
+      </c>
+      <c r="D60" s="4" t="n">
+        <v>-893985755421</v>
+      </c>
+      <c r="E60" s="4" t="n">
         <v>-609169047616</v>
-      </c>
-      <c r="C60" s="4" t="n">
-        <v>-893985755421</v>
-      </c>
-      <c r="D60" s="4" t="n">
-        <v>-1471244444534</v>
-      </c>
-      <c r="E60" s="4" t="n">
-        <v>-2055011378498</v>
       </c>
     </row>
     <row r="61">
@@ -5747,16 +5747,16 @@
         </is>
       </c>
       <c r="B63" s="4" t="n">
+        <v>-226855818008</v>
+      </c>
+      <c r="C63" s="4" t="n">
+        <v>-105819563366</v>
+      </c>
+      <c r="D63" s="4" t="n">
+        <v>-187658191452</v>
+      </c>
+      <c r="E63" s="4" t="n">
         <v>-127840968697</v>
-      </c>
-      <c r="C63" s="4" t="n">
-        <v>-187658191452</v>
-      </c>
-      <c r="D63" s="4" t="n">
-        <v>-105819563366</v>
-      </c>
-      <c r="E63" s="4" t="n">
-        <v>-226855818008</v>
       </c>
     </row>
     <row r="64">
@@ -5785,16 +5785,16 @@
         </is>
       </c>
       <c r="B65" s="4" t="n">
+        <v>7105472327512</v>
+      </c>
+      <c r="C65" s="4" t="n">
+        <v>4801673046224</v>
+      </c>
+      <c r="D65" s="4" t="n">
+        <v>3028297410899</v>
+      </c>
+      <c r="E65" s="4" t="n">
         <v>3057657087640</v>
-      </c>
-      <c r="C65" s="4" t="n">
-        <v>3028297410899</v>
-      </c>
-      <c r="D65" s="4" t="n">
-        <v>4801673046224</v>
-      </c>
-      <c r="E65" s="4" t="n">
-        <v>7105472327512</v>
       </c>
     </row>
     <row r="66">
@@ -5804,16 +5804,16 @@
         </is>
       </c>
       <c r="B66" s="4" t="n">
-        <v>0</v>
+        <v>3228414097</v>
       </c>
       <c r="C66" s="4" t="n">
-        <v>0</v>
+        <v>432821962</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>432821962</v>
+        <v>0</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>3228414097</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -5861,16 +5861,16 @@
         </is>
       </c>
       <c r="B69" s="4" t="n">
+        <v>12436623071</v>
+      </c>
+      <c r="C69" s="4" t="n">
+        <v>11558779299</v>
+      </c>
+      <c r="D69" s="4" t="n">
+        <v>-5958088241</v>
+      </c>
+      <c r="E69" s="4" t="n">
         <v>-8596795059</v>
-      </c>
-      <c r="C69" s="4" t="n">
-        <v>-5958088241</v>
-      </c>
-      <c r="D69" s="4" t="n">
-        <v>11558779299</v>
-      </c>
-      <c r="E69" s="4" t="n">
-        <v>12436623071</v>
       </c>
     </row>
     <row r="70">
@@ -5994,16 +5994,16 @@
         </is>
       </c>
       <c r="B76" s="4" t="n">
+        <v>5695765478179</v>
+      </c>
+      <c r="C76" s="4" t="n">
+        <v>3861253702870</v>
+      </c>
+      <c r="D76" s="4" t="n">
+        <v>2397484879388</v>
+      </c>
+      <c r="E76" s="4" t="n">
         <v>2418067296824</v>
-      </c>
-      <c r="C76" s="4" t="n">
-        <v>2397484879388</v>
-      </c>
-      <c r="D76" s="4" t="n">
-        <v>3861253702870</v>
-      </c>
-      <c r="E76" s="4" t="n">
-        <v>5695765478179</v>
       </c>
     </row>
     <row r="77">
@@ -6013,16 +6013,16 @@
         </is>
       </c>
       <c r="B77" s="4" t="n">
+        <v>5695765478179</v>
+      </c>
+      <c r="C77" s="4" t="n">
+        <v>3861253702870</v>
+      </c>
+      <c r="D77" s="4" t="n">
+        <v>2397484879388</v>
+      </c>
+      <c r="E77" s="4" t="n">
         <v>2418067296824</v>
-      </c>
-      <c r="C77" s="4" t="n">
-        <v>2397484879388</v>
-      </c>
-      <c r="D77" s="4" t="n">
-        <v>3861253702870</v>
-      </c>
-      <c r="E77" s="4" t="n">
-        <v>5695765478179</v>
       </c>
     </row>
     <row r="78">
@@ -6070,16 +6070,16 @@
         </is>
       </c>
       <c r="B80" s="4" t="n">
+        <v>12436623071</v>
+      </c>
+      <c r="C80" s="4" t="n">
+        <v>11558779299</v>
+      </c>
+      <c r="D80" s="4" t="n">
+        <v>-5958088241</v>
+      </c>
+      <c r="E80" s="4" t="n">
         <v>-8596795059</v>
-      </c>
-      <c r="C80" s="4" t="n">
-        <v>-5958088241</v>
-      </c>
-      <c r="D80" s="4" t="n">
-        <v>11558779299</v>
-      </c>
-      <c r="E80" s="4" t="n">
-        <v>12436623071</v>
       </c>
     </row>
   </sheetData>
@@ -6096,11 +6096,11 @@
   <dimension ref="A1:E149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="113" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6111,22 +6111,22 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>2022</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
         </is>
       </c>
     </row>
@@ -6137,16 +6137,16 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
+        <v>7108703741609</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>4802105868186</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>3028297410899</v>
+      </c>
+      <c r="E2" s="4" t="n">
         <v>3057657087640</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>3028297410899</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>4802105868186</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>7108703741609</v>
       </c>
     </row>
     <row r="3">
@@ -6156,16 +6156,16 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
+        <v>24873836043</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>23565200377</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>22954477706</v>
+      </c>
+      <c r="E3" s="4" t="n">
         <v>22646115484</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>22954477706</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>23565200377</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>24873836043</v>
       </c>
     </row>
     <row r="4">
@@ -6175,16 +6175,16 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
+        <v>26400000</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>6071068910</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>4636253744</v>
+      </c>
+      <c r="E4" s="4" t="n">
         <v>270349620</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>4636253744</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>6071068910</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>26400000</v>
       </c>
     </row>
     <row r="5">
@@ -6216,10 +6216,10 @@
         <v>0</v>
       </c>
       <c r="C6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4" t="n">
         <v>-11180667</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>0</v>
@@ -6232,16 +6232,16 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
+        <v>2055011378498</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>1471244444534</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>893985755421</v>
+      </c>
+      <c r="E7" s="4" t="n">
         <v>609169047616</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>893985755421</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>1471244444534</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>2055011378498</v>
       </c>
     </row>
     <row r="8">
@@ -6251,16 +6251,16 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
+        <v>-686651363984</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>-539111776066</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>-335159132981</v>
+      </c>
+      <c r="E8" s="4" t="n">
         <v>-156303191939</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>-335159132981</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>-539111776066</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>-686651363984</v>
       </c>
     </row>
     <row r="9">
@@ -6270,16 +6270,16 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
+        <v>-29065070402164</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>-9943684470023</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>-12963130531875</v>
+      </c>
+      <c r="E9" s="4" t="n">
         <v>1551393773235</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>-12963130531875</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>-9943684470023</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>-29065070402164</v>
       </c>
     </row>
     <row r="10">
@@ -6289,16 +6289,16 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
+        <v>16025337394</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>2686954618085</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>740836667695</v>
+      </c>
+      <c r="E10" s="4" t="n">
         <v>-3450109025019</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>740836667695</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>2686954618085</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>16025337394</v>
       </c>
     </row>
     <row r="11">
@@ -6327,16 +6327,16 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
+        <v>85568505507</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>2516743124189</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>-3478363005107</v>
+      </c>
+      <c r="E12" s="4" t="n">
         <v>2519094220855</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>-3478363005107</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>2516743124189</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>85568505507</v>
       </c>
     </row>
     <row r="13">
@@ -6346,16 +6346,16 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
+        <v>31220548802</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>-18967765286</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>-21009726316</v>
+      </c>
+      <c r="E13" s="4" t="n">
         <v>-5620395497</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>-21009726316</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>-18967765286</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>31220548802</v>
       </c>
     </row>
     <row r="14">
@@ -6365,16 +6365,16 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
+        <v>-2033252688434</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>-1342453255799</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>-901950985028</v>
+      </c>
+      <c r="E14" s="4" t="n">
         <v>-551285122912</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>-901950985028</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>-1342453255799</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>-2033252688434</v>
       </c>
     </row>
     <row r="15">
@@ -6384,16 +6384,16 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
+        <v>-969623062726</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>-583532014718</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>-440729850165</v>
+      </c>
+      <c r="E15" s="4" t="n">
         <v>-539650865595</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>-440729850165</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>-583532014718</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>-969623062726</v>
       </c>
     </row>
     <row r="16">
@@ -6403,16 +6403,16 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="4" t="n">
         <v>524989326844</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -6422,16 +6422,16 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>-60000000</v>
+      </c>
+      <c r="E17" s="4" t="n">
         <v>-524989326844</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>-60000000</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -6441,16 +6441,16 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
+        <v>-20564385947691</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>-4179809664082</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>-9348426947753</v>
+      </c>
+      <c r="E18" s="4" t="n">
         <v>5084833181656</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>-9348426947753</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>-4179809664082</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>-20564385947691</v>
       </c>
     </row>
     <row r="19">
@@ -6460,16 +6460,16 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
+        <v>-126608197153</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>-15530023681</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>-5938748551</v>
+      </c>
+      <c r="E19" s="4" t="n">
         <v>-18887284000</v>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>-5938748551</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>-15530023681</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>-126608197153</v>
       </c>
     </row>
     <row r="20">
@@ -6482,10 +6482,10 @@
         <v>0</v>
       </c>
       <c r="C20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="4" t="n">
         <v>475000000</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="E20" s="4" t="n">
         <v>0</v>
@@ -6536,16 +6536,16 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>0</v>
+        <v>-175249480890</v>
       </c>
       <c r="C23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="4" t="n">
         <v>-3033431775000</v>
       </c>
-      <c r="D23" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E23" s="4" t="n">
-        <v>-175249480890</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -6555,7 +6555,7 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>0</v>
+        <v>8412824066</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>0</v>
@@ -6564,7 +6564,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>8412824066</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -6593,16 +6593,16 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
+        <v>-293444853977</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>-15530023681</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>-3038895523551</v>
+      </c>
+      <c r="E26" s="4" t="n">
         <v>-18887284000</v>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>-3038895523551</v>
-      </c>
-      <c r="D26" s="4" t="n">
-        <v>-15530023681</v>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>-293444853977</v>
       </c>
     </row>
     <row r="27">
@@ -6612,16 +6612,16 @@
         </is>
       </c>
       <c r="B27" s="4" t="n">
+        <v>12106839428518</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>2252600000</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>10242763500000</v>
+      </c>
+      <c r="E27" s="4" t="n">
         <v>1893900000</v>
-      </c>
-      <c r="C27" s="4" t="n">
-        <v>10242763500000</v>
-      </c>
-      <c r="D27" s="4" t="n">
-        <v>2252600000</v>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>12106839428518</v>
       </c>
     </row>
     <row r="28">
@@ -6650,16 +6650,16 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
+        <v>95576293979754</v>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>81148615568719</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>82761482790113</v>
+      </c>
+      <c r="E29" s="4" t="n">
         <v>16481400000000</v>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>82761482790113</v>
-      </c>
-      <c r="D29" s="4" t="n">
-        <v>81148615568719</v>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>95576293979754</v>
       </c>
     </row>
     <row r="30">
@@ -6669,16 +6669,16 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
+        <v>-86581825426523</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>-77477067820028</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>-78439556027027</v>
+      </c>
+      <c r="E30" s="4" t="n">
         <v>-19594182377039</v>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>-78439556027027</v>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>-77477067820028</v>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>-86581825426523</v>
       </c>
     </row>
     <row r="31">
@@ -6707,16 +6707,16 @@
         </is>
       </c>
       <c r="B32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>-1196040613480</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="4" t="n">
         <v>-675447477440</v>
-      </c>
-      <c r="C32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="4" t="n">
-        <v>-1196040613480</v>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -6726,16 +6726,16 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
+        <v>21101307981749</v>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>2477759735211</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>14564690263086</v>
+      </c>
+      <c r="E33" s="4" t="n">
         <v>-3786335954479</v>
-      </c>
-      <c r="C33" s="4" t="n">
-        <v>14564690263086</v>
-      </c>
-      <c r="D33" s="4" t="n">
-        <v>2477759735211</v>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>21101307981749</v>
       </c>
     </row>
     <row r="34">
@@ -6745,16 +6745,16 @@
         </is>
       </c>
       <c r="B34" s="4" t="n">
+        <v>243477180081</v>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>-1717579952552</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>2177367791782</v>
+      </c>
+      <c r="E34" s="4" t="n">
         <v>1279609943177</v>
-      </c>
-      <c r="C34" s="4" t="n">
-        <v>2177367791782</v>
-      </c>
-      <c r="D34" s="4" t="n">
-        <v>-1717579952552</v>
-      </c>
-      <c r="E34" s="4" t="n">
-        <v>243477180081</v>
       </c>
     </row>
     <row r="35">
@@ -6764,16 +6764,16 @@
         </is>
       </c>
       <c r="B35" s="4" t="n">
+        <v>2864601041636</v>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>4582180994188</v>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>2404813202406</v>
+      </c>
+      <c r="E35" s="4" t="n">
         <v>1125203259229</v>
-      </c>
-      <c r="C35" s="4" t="n">
-        <v>2404813202406</v>
-      </c>
-      <c r="D35" s="4" t="n">
-        <v>4582180994188</v>
-      </c>
-      <c r="E35" s="4" t="n">
-        <v>2864601041636</v>
       </c>
     </row>
     <row r="36">
@@ -6802,16 +6802,16 @@
         </is>
       </c>
       <c r="B37" s="4" t="n">
+        <v>3108078221717</v>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>2864601041636</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>4582180994188</v>
+      </c>
+      <c r="E37" s="4" t="n">
         <v>2404813202406</v>
-      </c>
-      <c r="C37" s="4" t="n">
-        <v>4582180994188</v>
-      </c>
-      <c r="D37" s="4" t="n">
-        <v>2864601041636</v>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>3108078221717</v>
       </c>
     </row>
     <row r="38">
@@ -6897,16 +6897,16 @@
         </is>
       </c>
       <c r="B42" s="4" t="n">
+        <v>95576293979754</v>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>81148615568719</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>82761482790113</v>
+      </c>
+      <c r="E42" s="4" t="n">
         <v>16481400000000</v>
-      </c>
-      <c r="C42" s="4" t="n">
-        <v>82761482790113</v>
-      </c>
-      <c r="D42" s="4" t="n">
-        <v>81148615568719</v>
-      </c>
-      <c r="E42" s="4" t="n">
-        <v>95576293979754</v>
       </c>
     </row>
     <row r="43">
@@ -6954,16 +6954,16 @@
         </is>
       </c>
       <c r="B45" s="4" t="n">
+        <v>-86581825426523</v>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>-77477067820028</v>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>-78439556027027</v>
+      </c>
+      <c r="E45" s="4" t="n">
         <v>-19594182377039</v>
-      </c>
-      <c r="C45" s="4" t="n">
-        <v>-78439556027027</v>
-      </c>
-      <c r="D45" s="4" t="n">
-        <v>-77477067820028</v>
-      </c>
-      <c r="E45" s="4" t="n">
-        <v>-86581825426523</v>
       </c>
     </row>
     <row r="46">
@@ -6973,16 +6973,16 @@
         </is>
       </c>
       <c r="B46" s="4" t="n">
+        <v>2864601041636</v>
+      </c>
+      <c r="C46" s="4" t="n">
+        <v>4547180994188</v>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>2404813202406</v>
+      </c>
+      <c r="E46" s="4" t="n">
         <v>1125203259229</v>
-      </c>
-      <c r="C46" s="4" t="n">
-        <v>2404813202406</v>
-      </c>
-      <c r="D46" s="4" t="n">
-        <v>4547180994188</v>
-      </c>
-      <c r="E46" s="4" t="n">
-        <v>2864601041636</v>
       </c>
     </row>
     <row r="47">
@@ -7030,16 +7030,16 @@
         </is>
       </c>
       <c r="B49" s="4" t="n">
+        <v>3108078221717</v>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>2864601041636</v>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>4547180994188</v>
+      </c>
+      <c r="E49" s="4" t="n">
         <v>2404813202406</v>
-      </c>
-      <c r="C49" s="4" t="n">
-        <v>4547180994188</v>
-      </c>
-      <c r="D49" s="4" t="n">
-        <v>2864601041636</v>
-      </c>
-      <c r="E49" s="4" t="n">
-        <v>3108078221717</v>
       </c>
     </row>
     <row r="50">
@@ -7071,10 +7071,10 @@
         <v>0</v>
       </c>
       <c r="C51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="4" t="n">
         <v>35000000000</v>
-      </c>
-      <c r="D51" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="E51" s="4" t="n">
         <v>0</v>
@@ -7106,16 +7106,16 @@
         </is>
       </c>
       <c r="B53" s="4" t="n">
+        <v>738046448339303</v>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>499928912941086</v>
+      </c>
+      <c r="D53" s="4" t="n">
+        <v>341251631768076</v>
+      </c>
+      <c r="E53" s="4" t="n">
         <v>276521066989343</v>
-      </c>
-      <c r="C53" s="4" t="n">
-        <v>341251631768076</v>
-      </c>
-      <c r="D53" s="4" t="n">
-        <v>499928912941086</v>
-      </c>
-      <c r="E53" s="4" t="n">
-        <v>738046448339303</v>
       </c>
     </row>
     <row r="54">
@@ -7125,16 +7125,16 @@
         </is>
       </c>
       <c r="B54" s="4" t="n">
+        <v>-843973115884084</v>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>-575279337471679</v>
+      </c>
+      <c r="D54" s="4" t="n">
+        <v>-356333054468634</v>
+      </c>
+      <c r="E54" s="4" t="n">
         <v>-284951627339958</v>
-      </c>
-      <c r="C54" s="4" t="n">
-        <v>-356333054468634</v>
-      </c>
-      <c r="D54" s="4" t="n">
-        <v>-575279337471679</v>
-      </c>
-      <c r="E54" s="4" t="n">
-        <v>-843973115884084</v>
       </c>
     </row>
     <row r="55">
@@ -7258,16 +7258,16 @@
         </is>
       </c>
       <c r="B61" s="4" t="n">
+        <v>1198232900374700</v>
+      </c>
+      <c r="C61" s="4" t="n">
+        <v>786635095183819</v>
+      </c>
+      <c r="D61" s="4" t="n">
+        <v>526772783372466</v>
+      </c>
+      <c r="E61" s="4" t="n">
         <v>305615543755483</v>
-      </c>
-      <c r="C61" s="4" t="n">
-        <v>526772783372466</v>
-      </c>
-      <c r="D61" s="4" t="n">
-        <v>786635095183819</v>
-      </c>
-      <c r="E61" s="4" t="n">
-        <v>1198232900374700</v>
       </c>
     </row>
     <row r="62">
@@ -7277,16 +7277,16 @@
         </is>
       </c>
       <c r="B62" s="4" t="n">
-        <v>0</v>
+        <v>25613581008</v>
       </c>
       <c r="C62" s="4" t="n">
-        <v>0</v>
+        <v>43719133278</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>43719133278</v>
+        <v>0</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>25613581008</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -7296,16 +7296,16 @@
         </is>
       </c>
       <c r="B63" s="4" t="n">
+        <v>-60816680131</v>
+      </c>
+      <c r="C63" s="4" t="n">
+        <v>-47576177569</v>
+      </c>
+      <c r="D63" s="4" t="n">
+        <v>-52070652886</v>
+      </c>
+      <c r="E63" s="4" t="n">
         <v>-57278984467</v>
-      </c>
-      <c r="C63" s="4" t="n">
-        <v>-52070652886</v>
-      </c>
-      <c r="D63" s="4" t="n">
-        <v>-47576177569</v>
-      </c>
-      <c r="E63" s="4" t="n">
-        <v>-60816680131</v>
       </c>
     </row>
     <row r="64">
@@ -7353,16 +7353,16 @@
         </is>
       </c>
       <c r="B66" s="4" t="n">
+        <v>139355134797811</v>
+      </c>
+      <c r="C66" s="4" t="n">
+        <v>190416150569365</v>
+      </c>
+      <c r="D66" s="4" t="n">
+        <v>121040499898739</v>
+      </c>
+      <c r="E66" s="4" t="n">
         <v>84249052539715</v>
-      </c>
-      <c r="C66" s="4" t="n">
-        <v>121040499898739</v>
-      </c>
-      <c r="D66" s="4" t="n">
-        <v>190416150569365</v>
-      </c>
-      <c r="E66" s="4" t="n">
-        <v>139355134797811</v>
       </c>
     </row>
     <row r="67">
@@ -7372,16 +7372,16 @@
         </is>
       </c>
       <c r="B67" s="4" t="n">
+        <v>-139350374509823</v>
+      </c>
+      <c r="C67" s="4" t="n">
+        <v>-191403026217302</v>
+      </c>
+      <c r="D67" s="4" t="n">
+        <v>-120060929738920</v>
+      </c>
+      <c r="E67" s="4" t="n">
         <v>-84197133352967</v>
-      </c>
-      <c r="C67" s="4" t="n">
-        <v>-120060929738920</v>
-      </c>
-      <c r="D67" s="4" t="n">
-        <v>-191403026217302</v>
-      </c>
-      <c r="E67" s="4" t="n">
-        <v>-139350374509823</v>
       </c>
     </row>
     <row r="68">
@@ -7391,16 +7391,16 @@
         </is>
       </c>
       <c r="B68" s="4" t="n">
+        <v>678346947204</v>
+      </c>
+      <c r="C68" s="4" t="n">
+        <v>4249521552509</v>
+      </c>
+      <c r="D68" s="4" t="n">
+        <v>3444679727080</v>
+      </c>
+      <c r="E68" s="4" t="n">
         <v>-2247052204419</v>
-      </c>
-      <c r="C68" s="4" t="n">
-        <v>3444679727080</v>
-      </c>
-      <c r="D68" s="4" t="n">
-        <v>4249521552509</v>
-      </c>
-      <c r="E68" s="4" t="n">
-        <v>678346947204</v>
       </c>
     </row>
     <row r="69">
@@ -7410,16 +7410,16 @@
         </is>
       </c>
       <c r="B69" s="4" t="n">
+        <v>10024246349048</v>
+      </c>
+      <c r="C69" s="4" t="n">
+        <v>5774724796539</v>
+      </c>
+      <c r="D69" s="4" t="n">
+        <v>2330045069459</v>
+      </c>
+      <c r="E69" s="4" t="n">
         <v>4577097273878</v>
-      </c>
-      <c r="C69" s="4" t="n">
-        <v>2330045069459</v>
-      </c>
-      <c r="D69" s="4" t="n">
-        <v>5774724796539</v>
-      </c>
-      <c r="E69" s="4" t="n">
-        <v>10024246349048</v>
       </c>
     </row>
     <row r="70">
@@ -7429,16 +7429,16 @@
         </is>
       </c>
       <c r="B70" s="4" t="n">
+        <v>10024246349048</v>
+      </c>
+      <c r="C70" s="4" t="n">
+        <v>5774724796539</v>
+      </c>
+      <c r="D70" s="4" t="n">
+        <v>2330045069459</v>
+      </c>
+      <c r="E70" s="4" t="n">
         <v>4577097273878</v>
-      </c>
-      <c r="C70" s="4" t="n">
-        <v>2330045069459</v>
-      </c>
-      <c r="D70" s="4" t="n">
-        <v>5774724796539</v>
-      </c>
-      <c r="E70" s="4" t="n">
-        <v>10024246349048</v>
       </c>
     </row>
     <row r="71">
@@ -7448,16 +7448,16 @@
         </is>
       </c>
       <c r="B71" s="4" t="n">
+        <v>6447211380125</v>
+      </c>
+      <c r="C71" s="4" t="n">
+        <v>8245482244688</v>
+      </c>
+      <c r="D71" s="4" t="n">
+        <v>2945784273957</v>
+      </c>
+      <c r="E71" s="4" t="n">
         <v>2278125882711</v>
-      </c>
-      <c r="C71" s="4" t="n">
-        <v>2945784273957</v>
-      </c>
-      <c r="D71" s="4" t="n">
-        <v>8245482244688</v>
-      </c>
-      <c r="E71" s="4" t="n">
-        <v>6447211380125</v>
       </c>
     </row>
     <row r="72">
@@ -7505,16 +7505,16 @@
         </is>
       </c>
       <c r="B74" s="4" t="n">
-        <v>0</v>
+        <v>4206007929509</v>
       </c>
       <c r="C74" s="4" t="n">
+        <v>1734150405730</v>
+      </c>
+      <c r="D74" s="4" t="n">
         <v>1797451176015</v>
       </c>
-      <c r="D74" s="4" t="n">
-        <v>1734150405730</v>
-      </c>
       <c r="E74" s="4" t="n">
-        <v>4206007929509</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -7524,16 +7524,16 @@
         </is>
       </c>
       <c r="B75" s="4" t="n">
+        <v>49373986618</v>
+      </c>
+      <c r="C75" s="4" t="n">
+        <v>44613698630</v>
+      </c>
+      <c r="D75" s="4" t="n">
+        <v>1031489346567</v>
+      </c>
+      <c r="E75" s="4" t="n">
         <v>51919186748</v>
-      </c>
-      <c r="C75" s="4" t="n">
-        <v>1031489346567</v>
-      </c>
-      <c r="D75" s="4" t="n">
-        <v>44613698630</v>
-      </c>
-      <c r="E75" s="4" t="n">
-        <v>49373986618</v>
       </c>
     </row>
     <row r="76">
@@ -7638,16 +7638,16 @@
         </is>
       </c>
       <c r="B81" s="4" t="n">
+        <v>10702593296252</v>
+      </c>
+      <c r="C81" s="4" t="n">
+        <v>10024246349048</v>
+      </c>
+      <c r="D81" s="4" t="n">
+        <v>5774724796539</v>
+      </c>
+      <c r="E81" s="4" t="n">
         <v>2330045069459</v>
-      </c>
-      <c r="C81" s="4" t="n">
-        <v>5774724796539</v>
-      </c>
-      <c r="D81" s="4" t="n">
-        <v>10024246349048</v>
-      </c>
-      <c r="E81" s="4" t="n">
-        <v>10702593296252</v>
       </c>
     </row>
     <row r="82">
@@ -7657,16 +7657,16 @@
         </is>
       </c>
       <c r="B82" s="4" t="n">
+        <v>10702593296252</v>
+      </c>
+      <c r="C82" s="4" t="n">
+        <v>10024246349048</v>
+      </c>
+      <c r="D82" s="4" t="n">
+        <v>5774724796539</v>
+      </c>
+      <c r="E82" s="4" t="n">
         <v>2330045069459</v>
-      </c>
-      <c r="C82" s="4" t="n">
-        <v>5774724796539</v>
-      </c>
-      <c r="D82" s="4" t="n">
-        <v>10024246349048</v>
-      </c>
-      <c r="E82" s="4" t="n">
-        <v>10702593296252</v>
       </c>
     </row>
     <row r="83">
@@ -7676,16 +7676,16 @@
         </is>
       </c>
       <c r="B83" s="4" t="n">
+        <v>6447211380125</v>
+      </c>
+      <c r="C83" s="4" t="n">
+        <v>8245482244688</v>
+      </c>
+      <c r="D83" s="4" t="n">
+        <v>2945784273957</v>
+      </c>
+      <c r="E83" s="4" t="n">
         <v>2278125882711</v>
-      </c>
-      <c r="C83" s="4" t="n">
-        <v>2945784273957</v>
-      </c>
-      <c r="D83" s="4" t="n">
-        <v>8245482244688</v>
-      </c>
-      <c r="E83" s="4" t="n">
-        <v>6447211380125</v>
       </c>
     </row>
     <row r="84">
@@ -7771,16 +7771,16 @@
         </is>
       </c>
       <c r="B88" s="4" t="n">
-        <v>0</v>
+        <v>4206007929509</v>
       </c>
       <c r="C88" s="4" t="n">
+        <v>1734150405730</v>
+      </c>
+      <c r="D88" s="4" t="n">
         <v>1797451176015</v>
       </c>
-      <c r="D88" s="4" t="n">
-        <v>1734150405730</v>
-      </c>
       <c r="E88" s="4" t="n">
-        <v>4206007929509</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -7790,16 +7790,16 @@
         </is>
       </c>
       <c r="B89" s="4" t="n">
+        <v>49373986618</v>
+      </c>
+      <c r="C89" s="4" t="n">
+        <v>44613698630</v>
+      </c>
+      <c r="D89" s="4" t="n">
+        <v>1031489346567</v>
+      </c>
+      <c r="E89" s="4" t="n">
         <v>51919186748</v>
-      </c>
-      <c r="C89" s="4" t="n">
-        <v>1031489346567</v>
-      </c>
-      <c r="D89" s="4" t="n">
-        <v>44613698630</v>
-      </c>
-      <c r="E89" s="4" t="n">
-        <v>49373986618</v>
       </c>
     </row>
     <row r="90">
@@ -7866,16 +7866,16 @@
         </is>
       </c>
       <c r="B93" s="4" t="n">
+        <v>1393260250557</v>
+      </c>
+      <c r="C93" s="4" t="n">
+        <v>961768937755</v>
+      </c>
+      <c r="D93" s="4" t="n">
+        <v>586406173223</v>
+      </c>
+      <c r="E93" s="4" t="n">
         <v>475782320781</v>
-      </c>
-      <c r="C93" s="4" t="n">
-        <v>586406173223</v>
-      </c>
-      <c r="D93" s="4" t="n">
-        <v>961768937755</v>
-      </c>
-      <c r="E93" s="4" t="n">
-        <v>1393260250557</v>
       </c>
     </row>
     <row r="94">
@@ -7904,7 +7904,7 @@
         </is>
       </c>
       <c r="B95" s="4" t="n">
-        <v>0</v>
+        <v>5631437562</v>
       </c>
       <c r="C95" s="4" t="n">
         <v>0</v>
@@ -7913,7 +7913,7 @@
         <v>0</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>5631437562</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -7923,7 +7923,7 @@
         </is>
       </c>
       <c r="B96" s="4" t="n">
-        <v>0</v>
+        <v>3679561158</v>
       </c>
       <c r="C96" s="4" t="n">
         <v>0</v>
@@ -7932,7 +7932,7 @@
         <v>0</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>3679561158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="B102" s="4" t="n">
-        <v>0</v>
+        <v>1951876404</v>
       </c>
       <c r="C102" s="4" t="n">
         <v>0</v>
@@ -8046,7 +8046,7 @@
         <v>0</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>1951876404</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -8189,7 +8189,7 @@
         </is>
       </c>
       <c r="B110" s="4" t="n">
-        <v>0</v>
+        <v>-6910975255</v>
       </c>
       <c r="C110" s="4" t="n">
         <v>0</v>
@@ -8198,7 +8198,7 @@
         <v>0</v>
       </c>
       <c r="E110" s="4" t="n">
-        <v>-6910975255</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -8208,7 +8208,7 @@
         </is>
       </c>
       <c r="B111" s="4" t="n">
-        <v>0</v>
+        <v>-6910975255</v>
       </c>
       <c r="C111" s="4" t="n">
         <v>0</v>
@@ -8217,7 +8217,7 @@
         <v>0</v>
       </c>
       <c r="E111" s="4" t="n">
-        <v>-6910975255</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -8417,16 +8417,16 @@
         </is>
       </c>
       <c r="B122" s="4" t="n">
+        <v>-26825430350091</v>
+      </c>
+      <c r="C122" s="4" t="n">
+        <v>-13561407750219</v>
+      </c>
+      <c r="D122" s="4" t="n">
+        <v>-8839931663375</v>
+      </c>
+      <c r="E122" s="4" t="n">
         <v>3054260481126</v>
-      </c>
-      <c r="C122" s="4" t="n">
-        <v>-8839931663375</v>
-      </c>
-      <c r="D122" s="4" t="n">
-        <v>-13561407750219</v>
-      </c>
-      <c r="E122" s="4" t="n">
-        <v>-26825430350091</v>
       </c>
     </row>
     <row r="123">
@@ -8436,16 +8436,16 @@
         </is>
       </c>
       <c r="B123" s="4" t="n">
-        <v>0</v>
+        <v>-18413443303</v>
       </c>
       <c r="C123" s="4" t="n">
-        <v>0</v>
+        <v>-17278163500</v>
       </c>
       <c r="D123" s="4" t="n">
-        <v>-17278163500</v>
+        <v>0</v>
       </c>
       <c r="E123" s="4" t="n">
-        <v>-18413443303</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -8455,16 +8455,16 @@
         </is>
       </c>
       <c r="B124" s="4" t="n">
+        <v>-1335312954271</v>
+      </c>
+      <c r="C124" s="4" t="n">
+        <v>-1440059785348</v>
+      </c>
+      <c r="D124" s="4" t="n">
+        <v>-1291046000000</v>
+      </c>
+      <c r="E124" s="4" t="n">
         <v>511166300000</v>
-      </c>
-      <c r="C124" s="4" t="n">
-        <v>-1291046000000</v>
-      </c>
-      <c r="D124" s="4" t="n">
-        <v>-1440059785348</v>
-      </c>
-      <c r="E124" s="4" t="n">
-        <v>-1335312954271</v>
       </c>
     </row>
     <row r="125">
@@ -8474,16 +8474,16 @@
         </is>
       </c>
       <c r="B125" s="4" t="n">
+        <v>-17948486475954</v>
+      </c>
+      <c r="C125" s="4" t="n">
+        <v>-9292078962942</v>
+      </c>
+      <c r="D125" s="4" t="n">
+        <v>-7264561551658</v>
+      </c>
+      <c r="E125" s="4" t="n">
         <v>6497424202012</v>
-      </c>
-      <c r="C125" s="4" t="n">
-        <v>-7264561551658</v>
-      </c>
-      <c r="D125" s="4" t="n">
-        <v>-9292078962942</v>
-      </c>
-      <c r="E125" s="4" t="n">
-        <v>-17948486475954</v>
       </c>
     </row>
     <row r="126">
@@ -8493,16 +8493,16 @@
         </is>
       </c>
       <c r="B126" s="4" t="n">
+        <v>-7531928504136</v>
+      </c>
+      <c r="C126" s="4" t="n">
+        <v>-2614293738429</v>
+      </c>
+      <c r="D126" s="4" t="n">
+        <v>-292097988743</v>
+      </c>
+      <c r="E126" s="4" t="n">
         <v>-3947364654478</v>
-      </c>
-      <c r="C126" s="4" t="n">
-        <v>-292097988743</v>
-      </c>
-      <c r="D126" s="4" t="n">
-        <v>-2614293738429</v>
-      </c>
-      <c r="E126" s="4" t="n">
-        <v>-7531928504136</v>
       </c>
     </row>
     <row r="127">
@@ -8512,16 +8512,16 @@
         </is>
       </c>
       <c r="B127" s="4" t="n">
+        <v>8906516573</v>
+      </c>
+      <c r="C127" s="4" t="n">
+        <v>-197697100000</v>
+      </c>
+      <c r="D127" s="4" t="n">
+        <v>7773877026</v>
+      </c>
+      <c r="E127" s="4" t="n">
         <v>-6965366408</v>
-      </c>
-      <c r="C127" s="4" t="n">
-        <v>7773877026</v>
-      </c>
-      <c r="D127" s="4" t="n">
-        <v>-197697100000</v>
-      </c>
-      <c r="E127" s="4" t="n">
-        <v>8906516573</v>
       </c>
     </row>
     <row r="128">
@@ -8531,7 +8531,7 @@
         </is>
       </c>
       <c r="B128" s="4" t="n">
-        <v>0</v>
+        <v>-195489000</v>
       </c>
       <c r="C128" s="4" t="n">
         <v>0</v>
@@ -8540,7 +8540,7 @@
         <v>0</v>
       </c>
       <c r="E128" s="4" t="n">
-        <v>-195489000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -8664,16 +8664,16 @@
         </is>
       </c>
       <c r="B135" s="4" t="n">
+        <v>539115328852</v>
+      </c>
+      <c r="C135" s="4" t="n">
+        <v>337847776224</v>
+      </c>
+      <c r="D135" s="4" t="n">
+        <v>180391762558</v>
+      </c>
+      <c r="E135" s="4" t="n">
         <v>165790274167</v>
-      </c>
-      <c r="C135" s="4" t="n">
-        <v>180391762558</v>
-      </c>
-      <c r="D135" s="4" t="n">
-        <v>337847776224</v>
-      </c>
-      <c r="E135" s="4" t="n">
-        <v>539115328852</v>
       </c>
     </row>
     <row r="136">
@@ -8683,16 +8683,16 @@
         </is>
       </c>
       <c r="B136" s="4" t="n">
+        <v>-65178982099</v>
+      </c>
+      <c r="C136" s="4" t="n">
+        <v>-77566821611</v>
+      </c>
+      <c r="D136" s="4" t="n">
+        <v>7818314374</v>
+      </c>
+      <c r="E136" s="4" t="n">
         <v>115365106128</v>
-      </c>
-      <c r="C136" s="4" t="n">
-        <v>7818314374</v>
-      </c>
-      <c r="D136" s="4" t="n">
-        <v>-77566821611</v>
-      </c>
-      <c r="E136" s="4" t="n">
-        <v>-65178982099</v>
       </c>
     </row>
     <row r="137">
@@ -8721,16 +8721,16 @@
         </is>
       </c>
       <c r="B138" s="4" t="n">
+        <v>1933921663</v>
+      </c>
+      <c r="C138" s="4" t="n">
+        <v>125459716520</v>
+      </c>
+      <c r="D138" s="4" t="n">
+        <v>-239841359017</v>
+      </c>
+      <c r="E138" s="4" t="n">
         <v>240252940500</v>
-      </c>
-      <c r="C138" s="4" t="n">
-        <v>-239841359017</v>
-      </c>
-      <c r="D138" s="4" t="n">
-        <v>125459716520</v>
-      </c>
-      <c r="E138" s="4" t="n">
-        <v>1933921663</v>
       </c>
     </row>
     <row r="139">
@@ -8759,16 +8759,16 @@
         </is>
       </c>
       <c r="B140" s="4" t="n">
+        <v>702511645</v>
+      </c>
+      <c r="C140" s="4" t="n">
+        <v>-63376177</v>
+      </c>
+      <c r="D140" s="4" t="n">
+        <v>819874627</v>
+      </c>
+      <c r="E140" s="4" t="n">
         <v>-150000000</v>
-      </c>
-      <c r="C140" s="4" t="n">
-        <v>819874627</v>
-      </c>
-      <c r="D140" s="4" t="n">
-        <v>-63376177</v>
-      </c>
-      <c r="E140" s="4" t="n">
-        <v>702511645</v>
       </c>
     </row>
     <row r="141">
@@ -8778,16 +8778,16 @@
         </is>
       </c>
       <c r="B141" s="4" t="n">
+        <v>53057413631</v>
+      </c>
+      <c r="C141" s="4" t="n">
+        <v>9629489049</v>
+      </c>
+      <c r="D141" s="4" t="n">
+        <v>-5692616512</v>
+      </c>
+      <c r="E141" s="4" t="n">
         <v>-16576646902</v>
-      </c>
-      <c r="C141" s="4" t="n">
-        <v>-5692616512</v>
-      </c>
-      <c r="D141" s="4" t="n">
-        <v>9629489049</v>
-      </c>
-      <c r="E141" s="4" t="n">
-        <v>53057413631</v>
       </c>
     </row>
     <row r="142">
@@ -8797,16 +8797,16 @@
         </is>
       </c>
       <c r="B142" s="4" t="n">
+        <v>47843286609</v>
+      </c>
+      <c r="C142" s="4" t="n">
+        <v>38272728216</v>
+      </c>
+      <c r="D142" s="4" t="n">
+        <v>21990350285</v>
+      </c>
+      <c r="E142" s="4" t="n">
         <v>20022806384</v>
-      </c>
-      <c r="C142" s="4" t="n">
-        <v>21990350285</v>
-      </c>
-      <c r="D142" s="4" t="n">
-        <v>38272728216</v>
-      </c>
-      <c r="E142" s="4" t="n">
-        <v>47843286609</v>
       </c>
     </row>
     <row r="143">
@@ -8854,16 +8854,16 @@
         </is>
       </c>
       <c r="B145" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C145" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D145" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E145" s="4" t="n">
         <v>524989326844</v>
-      </c>
-      <c r="C145" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D145" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E145" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -8873,16 +8873,16 @@
         </is>
       </c>
       <c r="B146" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C146" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D146" s="4" t="n">
+        <v>-60000000</v>
+      </c>
+      <c r="E146" s="4" t="n">
         <v>-524989326844</v>
-      </c>
-      <c r="C146" s="4" t="n">
-        <v>-60000000</v>
-      </c>
-      <c r="D146" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E146" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -8892,16 +8892,16 @@
         </is>
       </c>
       <c r="B147" s="4" t="n">
-        <v>0</v>
+        <v>52947827083</v>
       </c>
       <c r="C147" s="4" t="n">
+        <v>-74600938496</v>
+      </c>
+      <c r="D147" s="4" t="n">
         <v>12591704106</v>
       </c>
-      <c r="D147" s="4" t="n">
-        <v>-74600938496</v>
-      </c>
       <c r="E147" s="4" t="n">
-        <v>52947827083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -8911,16 +8911,16 @@
         </is>
       </c>
       <c r="B148" s="4" t="n">
+        <v>-1091597443071580</v>
+      </c>
+      <c r="C148" s="4" t="n">
+        <v>-706044416408489</v>
+      </c>
+      <c r="D148" s="4" t="n">
+        <v>-509174180451761</v>
+      </c>
+      <c r="E148" s="4" t="n">
         <v>-299426675811568</v>
-      </c>
-      <c r="C148" s="4" t="n">
-        <v>-509174180451761</v>
-      </c>
-      <c r="D148" s="4" t="n">
-        <v>-706044416408489</v>
-      </c>
-      <c r="E148" s="4" t="n">
-        <v>-1091597443071580</v>
       </c>
     </row>
     <row r="149">
@@ -8956,11 +8956,11 @@
   <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="56" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="3" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -8971,11 +8971,19 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="6" t="n"/>
-    </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="7" t="n"/>
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Khối "CHỈ SỐ TÀI CHÍNH" tính bằng công thức từ khối "DỮ LIỆU TRÍCH XUẤT" bên dưới, không phải số nhập tay. Khối "DỮ LIỆU TRÍCH XUẤT" được dò tự động theo TÊN khoản mục (đúng theo tên gốc trong báo cáo) và theo NĂM từ 3 sheet balance_sheet / income_statement — không tham chiếu ô cố định. Có thể sửa nhãn khoản mục ở cột A khối này nếu công ty đổi tên dòng; công thức sẽ tự dò lại. Các năm được xếp tăng dần từ trái sang phải.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Lưu ý: Đây là công ty chứng khoán: "Giá vốn hàng bán" được thay bằng "Chi phí hoạt động", "Phải thu khách hàng"/"Hàng tồn kho" không có số liệu (khoản mục thời kỳ trước 2016, luôn = 0) nên Số ngày phải thu và Số ngày tồn kho hiển thị "n/a".</t>
+        </is>
+      </c>
     </row>
     <row r="4"/>
     <row r="5">
@@ -8996,19 +9004,19 @@
         </is>
       </c>
       <c r="B6" s="11">
+        <f>'balance_sheet'!E1</f>
+        <v/>
+      </c>
+      <c r="C6" s="11">
+        <f>'balance_sheet'!D1</f>
+        <v/>
+      </c>
+      <c r="D6" s="11">
+        <f>'balance_sheet'!C1</f>
+        <v/>
+      </c>
+      <c r="E6" s="11">
         <f>'balance_sheet'!B1</f>
-        <v/>
-      </c>
-      <c r="C6" s="11">
-        <f>'balance_sheet'!C1</f>
-        <v/>
-      </c>
-      <c r="D6" s="11">
-        <f>'balance_sheet'!D1</f>
-        <v/>
-      </c>
-      <c r="E6" s="11">
-        <f>'balance_sheet'!E1</f>
         <v/>
       </c>
     </row>
@@ -9522,19 +9530,19 @@
         </is>
       </c>
       <c r="B39" s="11">
+        <f>'balance_sheet'!E1</f>
+        <v/>
+      </c>
+      <c r="C39" s="11">
+        <f>'balance_sheet'!D1</f>
+        <v/>
+      </c>
+      <c r="D39" s="11">
+        <f>'balance_sheet'!C1</f>
+        <v/>
+      </c>
+      <c r="E39" s="11">
         <f>'balance_sheet'!B1</f>
-        <v/>
-      </c>
-      <c r="C39" s="11">
-        <f>'balance_sheet'!C1</f>
-        <v/>
-      </c>
-      <c r="D39" s="11">
-        <f>'balance_sheet'!D1</f>
-        <v/>
-      </c>
-      <c r="E39" s="11">
-        <f>'balance_sheet'!E1</f>
         <v/>
       </c>
     </row>

--- a/financials/TCX/TCX_financials.xlsx
+++ b/financials/TCX/TCX_financials.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="balance_sheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="income_statement" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="cash_flow" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="chi_so_tai_chinh" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="income_statement" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cash_flow" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chi_so_tai_chinh" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -157,7 +157,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -187,10 +187,28 @@
     <xf numFmtId="166" fontId="13" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="13" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6E0B4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00F8CBAD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -261,6 +279,96 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>auto</author>
+  </authors>
+  <commentList>
+    <comment ref="B48" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="C48" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="D48" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="E48" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="F48" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="G48" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="H48" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="I48" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="B50" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="C50" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="D50" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="E50" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="F50" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="G50" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="H50" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="I50" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -14101,15 +14209,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="3" customWidth="1" min="6" max="6"/>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="3" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -14119,66 +14231,191 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="42" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>Khối "CHỈ SỐ TÀI CHÍNH" tính bằng công thức từ khối "DỮ LIỆU TRÍCH XUẤT" bên dưới, không phải số nhập tay. Khối "DỮ LIỆU TRÍCH XUẤT" được dò tự động theo TÊN khoản mục (đúng theo tên gốc trong báo cáo) và theo NĂM từ 3 sheet balance_sheet / income_statement — không tham chiếu ô cố định. Có thể sửa nhãn khoản mục ở cột A khối này nếu công ty đổi tên dòng; công thức sẽ tự dò lại. Các năm được xếp tăng dần từ trái sang phải.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>Lưu ý: Đây là công ty chứng khoán: "Giá vốn hàng bán" được thay bằng "Chi phí hoạt động", "Phải thu khách hàng"/"Hàng tồn kho" không có số liệu (khoản mục thời kỳ trước 2016, luôn = 0) nên Số ngày phải thu và Số ngày tồn kho hiển thị "n/a".</t>
-        </is>
-      </c>
-    </row>
-    <row r="4"/>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>I. CHỈ SỐ TÀI CHÍNH</t>
+        </is>
+      </c>
+      <c r="B2" s="20" t="n"/>
+      <c r="C2" s="20" t="n"/>
+      <c r="D2" s="20" t="n"/>
+      <c r="E2" s="20" t="n"/>
+      <c r="F2" s="20" t="n"/>
+      <c r="G2" s="20" t="n"/>
+      <c r="H2" s="20" t="n"/>
+      <c r="I2" s="20" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Chỉ tiêu</t>
+        </is>
+      </c>
+      <c r="B3" s="11">
+        <f>'balance_sheet'!B1</f>
+        <v/>
+      </c>
+      <c r="C3" s="11">
+        <f>'balance_sheet'!C1</f>
+        <v/>
+      </c>
+      <c r="D3" s="11">
+        <f>'balance_sheet'!D1</f>
+        <v/>
+      </c>
+      <c r="E3" s="11">
+        <f>'balance_sheet'!E1</f>
+        <v/>
+      </c>
+      <c r="F3" s="11">
+        <f>'balance_sheet'!F1</f>
+        <v/>
+      </c>
+      <c r="G3" s="11">
+        <f>'balance_sheet'!G1</f>
+        <v/>
+      </c>
+      <c r="H3" s="11">
+        <f>'balance_sheet'!H1</f>
+        <v/>
+      </c>
+      <c r="I3" s="11">
+        <f>'balance_sheet'!I1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>1. Khả năng sinh lời</t>
+        </is>
+      </c>
+    </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>I. CHỈ SỐ TÀI CHÍNH</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="n"/>
-      <c r="C5" s="9" t="n"/>
-      <c r="D5" s="9" t="n"/>
-      <c r="E5" s="9" t="n"/>
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>ROE (LNST CĐ Cty mẹ / VCSH bình quân)</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C5" s="15">
+        <f>IFERROR(C$47/((C$32+B$32)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D5" s="15">
+        <f>IFERROR(D$47/((D$32+C$32)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E5" s="15">
+        <f>IFERROR(E$47/((E$32+D$32)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F5" s="15">
+        <f>IFERROR(F$47/((F$32+E$32)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G5" s="15">
+        <f>IFERROR(G$47/((G$32+F$32)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H5" s="15">
+        <f>IFERROR(H$47/((H$32+G$32)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I5" s="15">
+        <f>IFERROR(I$47/((I$32+H$32)/2),"n/a")</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>Chỉ tiêu</t>
-        </is>
-      </c>
-      <c r="B6" s="11">
-        <f>'balance_sheet'!E1</f>
-        <v/>
-      </c>
-      <c r="C6" s="11">
-        <f>'balance_sheet'!D1</f>
-        <v/>
-      </c>
-      <c r="D6" s="11">
-        <f>'balance_sheet'!C1</f>
-        <v/>
-      </c>
-      <c r="E6" s="11">
-        <f>'balance_sheet'!B1</f>
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>ROA (LNST / Tổng tài sản bình quân)</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C6" s="15">
+        <f>IFERROR(C$46/((C$33+B$33)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D6" s="15">
+        <f>IFERROR(D$46/((D$33+C$33)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E6" s="15">
+        <f>IFERROR(E$46/((E$33+D$33)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F6" s="15">
+        <f>IFERROR(F$46/((F$33+E$33)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G6" s="15">
+        <f>IFERROR(G$46/((G$33+F$33)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H6" s="15">
+        <f>IFERROR(H$46/((H$33+G$33)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I6" s="15">
+        <f>IFERROR(I$46/((I$33+H$33)/2),"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>1. Khả năng sinh lời</t>
-        </is>
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Tăng trưởng LN Cổ đông Cty mẹ</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C7" s="15">
+        <f>IFERROR((C$47-B$47)/ABS(B$47),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D7" s="15">
+        <f>IFERROR((D$47-C$47)/ABS(C$47),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E7" s="15">
+        <f>IFERROR((E$47-D$47)/ABS(D$47),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F7" s="15">
+        <f>IFERROR((F$47-E$47)/ABS(E$47),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G7" s="15">
+        <f>IFERROR((G$47-F$47)/ABS(F$47),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H7" s="15">
+        <f>IFERROR((H$47-G$47)/ABS(G$47),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I7" s="15">
+        <f>IFERROR((I$47-H$47)/ABS(H$47),"n/a")</f>
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>ROE (LNST CĐ Cty mẹ / VCSH bình quân)</t>
+          <t>Tăng trưởng Doanh thu thuần</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
@@ -14187,987 +14424,1585 @@
         </is>
       </c>
       <c r="C8" s="15">
-        <f>IFERROR(C$55/((C$40+B$40)/2),"n/a")</f>
+        <f>IFERROR((C$39-B$39)/ABS(B$39),"n/a")</f>
         <v/>
       </c>
       <c r="D8" s="15">
-        <f>IFERROR(D$55/((D$40+C$40)/2),"n/a")</f>
+        <f>IFERROR((D$39-C$39)/ABS(C$39),"n/a")</f>
         <v/>
       </c>
       <c r="E8" s="15">
-        <f>IFERROR(E$55/((E$40+D$40)/2),"n/a")</f>
+        <f>IFERROR((E$39-D$39)/ABS(D$39),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F8" s="15">
+        <f>IFERROR((F$39-E$39)/ABS(E$39),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G8" s="15">
+        <f>IFERROR((G$39-F$39)/ABS(F$39),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H8" s="15">
+        <f>IFERROR((H$39-G$39)/ABS(G$39),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I8" s="15">
+        <f>IFERROR((I$39-H$39)/ABS(H$39),"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>ROA (LNST / Tổng tài sản bình quân)</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C9" s="15">
-        <f>IFERROR(C$54/((C$41+B$41)/2),"n/a")</f>
-        <v/>
-      </c>
-      <c r="D9" s="15">
-        <f>IFERROR(D$54/((D$41+C$41)/2),"n/a")</f>
-        <v/>
-      </c>
-      <c r="E9" s="15">
-        <f>IFERROR(E$54/((E$41+D$41)/2),"n/a")</f>
-        <v/>
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>2. Biên lợi nhuận</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>Tăng trưởng LN Cổ đông Cty mẹ</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
+          <t>Biên lợi nhuận gộp</t>
+        </is>
+      </c>
+      <c r="B10" s="15">
+        <f>IFERROR(B$41/B$39,"n/a")</f>
+        <v/>
       </c>
       <c r="C10" s="15">
-        <f>IFERROR((C$55-B$55)/ABS(B$55),"n/a")</f>
+        <f>IFERROR(C$41/C$39,"n/a")</f>
         <v/>
       </c>
       <c r="D10" s="15">
-        <f>IFERROR((D$55-C$55)/ABS(C$55),"n/a")</f>
+        <f>IFERROR(D$41/D$39,"n/a")</f>
         <v/>
       </c>
       <c r="E10" s="15">
-        <f>IFERROR((E$55-D$55)/ABS(D$55),"n/a")</f>
+        <f>IFERROR(E$41/E$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F10" s="15">
+        <f>IFERROR(F$41/F$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G10" s="15">
+        <f>IFERROR(G$41/G$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H10" s="15">
+        <f>IFERROR(H$41/H$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I10" s="15">
+        <f>IFERROR(I$41/I$39,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>Tăng trưởng Doanh thu thuần</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
+          <t>Biên lợi nhuận ròng</t>
+        </is>
+      </c>
+      <c r="B11" s="15">
+        <f>IFERROR(B$46/B$39,"n/a")</f>
+        <v/>
       </c>
       <c r="C11" s="15">
-        <f>IFERROR((C$47-B$47)/ABS(B$47),"n/a")</f>
+        <f>IFERROR(C$46/C$39,"n/a")</f>
         <v/>
       </c>
       <c r="D11" s="15">
-        <f>IFERROR((D$47-C$47)/ABS(C$47),"n/a")</f>
+        <f>IFERROR(D$46/D$39,"n/a")</f>
         <v/>
       </c>
       <c r="E11" s="15">
-        <f>IFERROR((E$47-D$47)/ABS(D$47),"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12"/>
+        <f>IFERROR(E$46/E$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F11" s="15">
+        <f>IFERROR(F$46/F$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G11" s="15">
+        <f>IFERROR(G$46/G$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H11" s="15">
+        <f>IFERROR(H$46/H$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I11" s="15">
+        <f>IFERROR(I$46/I$39,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>3. Đòn bẩy tài chính</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>2. Biên lợi nhuận</t>
-        </is>
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>D/E (Nợ vay / Vốn chủ sở hữu)</t>
+        </is>
+      </c>
+      <c r="B13" s="16">
+        <f>IFERROR((B$37+B$38)/B$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C13" s="16">
+        <f>IFERROR((C$37+C$38)/C$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D13" s="16">
+        <f>IFERROR((D$37+D$38)/D$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E13" s="16">
+        <f>IFERROR((E$37+E$38)/E$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F13" s="16">
+        <f>IFERROR((F$37+F$38)/F$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G13" s="16">
+        <f>IFERROR((G$37+G$38)/G$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H13" s="16">
+        <f>IFERROR((H$37+H$38)/H$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I13" s="16">
+        <f>IFERROR((I$37+I$38)/I$32,"n/a")</f>
+        <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>Biên lợi nhuận gộp</t>
-        </is>
-      </c>
-      <c r="B14" s="15">
-        <f>IFERROR(B$49/B$47,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C14" s="15">
-        <f>IFERROR(C$49/C$47,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D14" s="15">
-        <f>IFERROR(D$49/D$47,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E14" s="15">
-        <f>IFERROR(E$49/E$47,"n/a")</f>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     - Nợ vay dài hạn/Vốn chủ sở hữu</t>
+        </is>
+      </c>
+      <c r="B14" s="16">
+        <f>IFERROR(B$38/B$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C14" s="16">
+        <f>IFERROR(C$38/C$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D14" s="16">
+        <f>IFERROR(D$38/D$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E14" s="16">
+        <f>IFERROR(E$38/E$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F14" s="16">
+        <f>IFERROR(F$38/F$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G14" s="16">
+        <f>IFERROR(G$38/G$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H14" s="16">
+        <f>IFERROR(H$38/H$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I14" s="16">
+        <f>IFERROR(I$38/I$32,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t>Biên lợi nhuận ròng</t>
-        </is>
-      </c>
-      <c r="B15" s="15">
-        <f>IFERROR(B$54/B$47,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C15" s="15">
-        <f>IFERROR(C$54/C$47,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D15" s="15">
-        <f>IFERROR(D$54/D$47,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E15" s="15">
-        <f>IFERROR(E$54/E$47,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16"/>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     - Nợ vay ngắn hạn/Vốn chủ sở hữu</t>
+        </is>
+      </c>
+      <c r="B15" s="16">
+        <f>IFERROR(B$37/B$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C15" s="16">
+        <f>IFERROR(C$37/C$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D15" s="16">
+        <f>IFERROR(D$37/D$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E15" s="16">
+        <f>IFERROR(E$37/E$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F15" s="16">
+        <f>IFERROR(F$37/F$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G15" s="16">
+        <f>IFERROR(G$37/G$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H15" s="16">
+        <f>IFERROR(H$37/H$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I15" s="16">
+        <f>IFERROR(I$37/I$32,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>Nợ phải trả/Vốn chủ sở hữu</t>
+        </is>
+      </c>
+      <c r="B16" s="16">
+        <f>IFERROR(B$34/B$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C16" s="16">
+        <f>IFERROR(C$34/C$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D16" s="16">
+        <f>IFERROR(D$34/D$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E16" s="16">
+        <f>IFERROR(E$34/E$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F16" s="16">
+        <f>IFERROR(F$34/F$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G16" s="16">
+        <f>IFERROR(G$34/G$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H16" s="16">
+        <f>IFERROR(H$34/H$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I16" s="16">
+        <f>IFERROR(I$34/I$32,"n/a")</f>
+        <v/>
+      </c>
+    </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>3. Đòn bẩy tài chính</t>
-        </is>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     - Nợ dài hạn/Vốn chủ sở hữu</t>
+        </is>
+      </c>
+      <c r="B17" s="16">
+        <f>IFERROR(B$36/B$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C17" s="16">
+        <f>IFERROR(C$36/C$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D17" s="16">
+        <f>IFERROR(D$36/D$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E17" s="16">
+        <f>IFERROR(E$36/E$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F17" s="16">
+        <f>IFERROR(F$36/F$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G17" s="16">
+        <f>IFERROR(G$36/G$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H17" s="16">
+        <f>IFERROR(H$36/H$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I17" s="16">
+        <f>IFERROR(I$36/I$32,"n/a")</f>
+        <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>D/E (Nợ vay / Vốn chủ sở hữu)</t>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     - Nợ ngắn hạn/Vốn chủ sở hữu</t>
         </is>
       </c>
       <c r="B18" s="16">
-        <f>IFERROR((B$45+B$46)/B$40,"n/a")</f>
+        <f>IFERROR(B$35/B$32,"n/a")</f>
         <v/>
       </c>
       <c r="C18" s="16">
-        <f>IFERROR((C$45+C$46)/C$40,"n/a")</f>
+        <f>IFERROR(C$35/C$32,"n/a")</f>
         <v/>
       </c>
       <c r="D18" s="16">
-        <f>IFERROR((D$45+D$46)/D$40,"n/a")</f>
+        <f>IFERROR(D$35/D$32,"n/a")</f>
         <v/>
       </c>
       <c r="E18" s="16">
-        <f>IFERROR((E$45+E$46)/E$40,"n/a")</f>
+        <f>IFERROR(E$35/E$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F18" s="16">
+        <f>IFERROR(F$35/F$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G18" s="16">
+        <f>IFERROR(G$35/G$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H18" s="16">
+        <f>IFERROR(H$35/H$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I18" s="16">
+        <f>IFERROR(I$35/I$32,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     - Nợ vay dài hạn/Vốn chủ sở hữu</t>
-        </is>
-      </c>
-      <c r="B19" s="16">
-        <f>IFERROR(B$46/B$40,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C19" s="16">
-        <f>IFERROR(C$46/C$40,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D19" s="16">
-        <f>IFERROR(D$46/D$40,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E19" s="16">
-        <f>IFERROR(E$46/E$40,"n/a")</f>
-        <v/>
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>4. Chi phí &amp; khả năng trả lãi</t>
+        </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     - Nợ vay ngắn hạn/Vốn chủ sở hữu</t>
-        </is>
-      </c>
-      <c r="B20" s="16">
-        <f>IFERROR(B$45/B$40,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C20" s="16">
-        <f>IFERROR(C$45/C$40,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D20" s="16">
-        <f>IFERROR(D$45/D$40,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E20" s="16">
-        <f>IFERROR(E$45/E$40,"n/a")</f>
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>Chi phí bán hàng, quản lý/LN gộp</t>
+        </is>
+      </c>
+      <c r="B20" s="15">
+        <f>IFERROR((ABS(B$42)+ABS(B$43))/B$41,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C20" s="15">
+        <f>IFERROR((ABS(C$42)+ABS(C$43))/C$41,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D20" s="15">
+        <f>IFERROR((ABS(D$42)+ABS(D$43))/D$41,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E20" s="15">
+        <f>IFERROR((ABS(E$42)+ABS(E$43))/E$41,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F20" s="15">
+        <f>IFERROR((ABS(F$42)+ABS(F$43))/F$41,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G20" s="15">
+        <f>IFERROR((ABS(G$42)+ABS(G$43))/G$41,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H20" s="15">
+        <f>IFERROR((ABS(H$42)+ABS(H$43))/H$41,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I20" s="15">
+        <f>IFERROR((ABS(I$42)+ABS(I$43))/I$41,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>Nợ phải trả/Vốn chủ sở hữu</t>
-        </is>
-      </c>
-      <c r="B21" s="16">
-        <f>IFERROR(B$42/B$40,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C21" s="16">
-        <f>IFERROR(C$42/C$40,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D21" s="16">
-        <f>IFERROR(D$42/D$40,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E21" s="16">
-        <f>IFERROR(E$42/E$40,"n/a")</f>
+          <t>Chi phí lãi vay/LN từ hoạt động kinh doanh</t>
+        </is>
+      </c>
+      <c r="B21" s="15">
+        <f>IFERROR(ABS(B$45)/B$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C21" s="15">
+        <f>IFERROR(ABS(C$45)/C$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D21" s="15">
+        <f>IFERROR(ABS(D$45)/D$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E21" s="15">
+        <f>IFERROR(ABS(E$45)/E$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F21" s="15">
+        <f>IFERROR(ABS(F$45)/F$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G21" s="15">
+        <f>IFERROR(ABS(G$45)/G$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H21" s="15">
+        <f>IFERROR(ABS(H$45)/H$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I21" s="15">
+        <f>IFERROR(ABS(I$45)/I$44,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     - Nợ dài hạn/Vốn chủ sở hữu</t>
-        </is>
-      </c>
-      <c r="B22" s="16">
-        <f>IFERROR(B$44/B$40,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C22" s="16">
-        <f>IFERROR(C$44/C$40,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D22" s="16">
-        <f>IFERROR(D$44/D$40,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E22" s="16">
-        <f>IFERROR(E$44/E$40,"n/a")</f>
-        <v/>
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>5. Chu kỳ hoạt động vốn lưu động</t>
+        </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     - Nợ ngắn hạn/Vốn chủ sở hữu</t>
-        </is>
-      </c>
-      <c r="B23" s="16">
-        <f>IFERROR(B$43/B$40,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C23" s="16">
-        <f>IFERROR(C$43/C$40,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D23" s="16">
-        <f>IFERROR(D$43/D$40,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E23" s="16">
-        <f>IFERROR(E$43/E$40,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24"/>
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>Số ngày phải trả (DPO)</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C23" s="17">
+        <f>IFERROR(((C$49+B$49)/2)/ABS(C$40)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D23" s="17">
+        <f>IFERROR(((D$49+C$49)/2)/ABS(D$40)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E23" s="17">
+        <f>IFERROR(((E$49+D$49)/2)/ABS(E$40)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F23" s="17">
+        <f>IFERROR(((F$49+E$49)/2)/ABS(F$40)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G23" s="17">
+        <f>IFERROR(((G$49+F$49)/2)/ABS(G$40)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H23" s="17">
+        <f>IFERROR(((H$49+G$49)/2)/ABS(H$40)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I23" s="17">
+        <f>IFERROR(((I$49+H$49)/2)/ABS(I$40)*365,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>Số ngày phải thu (DSO)</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C24" s="17">
+        <f>IFERROR(((C$48+B$48)/2)/C$39*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D24" s="17">
+        <f>IFERROR(((D$48+C$48)/2)/D$39*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E24" s="17">
+        <f>IFERROR(((E$48+D$48)/2)/E$39*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F24" s="17">
+        <f>IFERROR(((F$48+E$48)/2)/F$39*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G24" s="17">
+        <f>IFERROR(((G$48+F$48)/2)/G$39*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H24" s="17">
+        <f>IFERROR(((H$48+G$48)/2)/H$39*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I24" s="17">
+        <f>IFERROR(((I$48+H$48)/2)/I$39*365,"n/a")</f>
+        <v/>
+      </c>
+    </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>4. Chi phí &amp; khả năng trả lãi</t>
-        </is>
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>Số ngày tồn kho (DIO)</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C25" s="17">
+        <f>IFERROR(((C$50+B$50)/2)/ABS(C$40)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D25" s="17">
+        <f>IFERROR(((D$50+C$50)/2)/ABS(D$40)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E25" s="17">
+        <f>IFERROR(((E$50+D$50)/2)/ABS(E$40)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F25" s="17">
+        <f>IFERROR(((F$50+E$50)/2)/ABS(F$40)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G25" s="17">
+        <f>IFERROR(((G$50+F$50)/2)/ABS(G$40)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H25" s="17">
+        <f>IFERROR(((H$50+G$50)/2)/ABS(H$40)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I25" s="17">
+        <f>IFERROR(((I$50+H$50)/2)/ABS(I$40)*365,"n/a")</f>
+        <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="13" t="inlineStr">
-        <is>
-          <t>Chi phí bán hàng, quản lý/LN gộp</t>
-        </is>
-      </c>
-      <c r="B26" s="15">
-        <f>IFERROR((ABS(B$50)+ABS(B$51))/B$49,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C26" s="15">
-        <f>IFERROR((ABS(C$50)+ABS(C$51))/C$49,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D26" s="15">
-        <f>IFERROR((ABS(D$50)+ABS(D$51))/D$49,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E26" s="15">
-        <f>IFERROR((ABS(E$50)+ABS(E$51))/E$49,"n/a")</f>
-        <v/>
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>6. Cơ cấu tài sản</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t>Chi phí lãi vay/LN từ hoạt động kinh doanh</t>
+          <t>Tiền và tương đương tiền/Tài sản</t>
         </is>
       </c>
       <c r="B27" s="15">
-        <f>IFERROR(ABS(B$53)/B$52,"n/a")</f>
+        <f>IFERROR(B$51/B$33,"n/a")</f>
         <v/>
       </c>
       <c r="C27" s="15">
-        <f>IFERROR(ABS(C$53)/C$52,"n/a")</f>
+        <f>IFERROR(C$51/C$33,"n/a")</f>
         <v/>
       </c>
       <c r="D27" s="15">
-        <f>IFERROR(ABS(D$53)/D$52,"n/a")</f>
+        <f>IFERROR(D$51/D$33,"n/a")</f>
         <v/>
       </c>
       <c r="E27" s="15">
-        <f>IFERROR(ABS(E$53)/E$52,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>5. Chu kỳ hoạt động vốn lưu động</t>
-        </is>
-      </c>
-    </row>
+        <f>IFERROR(E$51/E$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F27" s="15">
+        <f>IFERROR(F$51/F$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G27" s="15">
+        <f>IFERROR(G$51/G$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H27" s="15">
+        <f>IFERROR(H$51/H$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I27" s="15">
+        <f>IFERROR(I$51/I$33,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>Hàng tồn kho/Tài sản</t>
+        </is>
+      </c>
+      <c r="B28" s="15">
+        <f>IFERROR(B$50/B$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C28" s="15">
+        <f>IFERROR(C$50/C$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D28" s="15">
+        <f>IFERROR(D$50/D$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E28" s="15">
+        <f>IFERROR(E$50/E$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F28" s="15">
+        <f>IFERROR(F$50/F$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G28" s="15">
+        <f>IFERROR(G$50/G$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H28" s="15">
+        <f>IFERROR(H$50/H$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I28" s="15">
+        <f>IFERROR(I$50/I$33,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29"/>
     <row r="30">
-      <c r="A30" s="13" t="inlineStr">
-        <is>
-          <t>Số ngày phải trả (DPO)</t>
-        </is>
-      </c>
-      <c r="B30" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C30" s="17">
-        <f>IFERROR(((C$57+B$57)/2)/ABS(C$48)*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D30" s="17">
-        <f>IFERROR(((D$57+C$57)/2)/ABS(D$48)*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E30" s="17">
-        <f>IFERROR(((E$57+D$57)/2)/ABS(E$48)*365,"n/a")</f>
-        <v/>
-      </c>
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>II. DỮ LIỆU TRÍCH XUẤT (tự động dò theo tên khoản mục)</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="n"/>
+      <c r="C30" s="20" t="n"/>
+      <c r="D30" s="20" t="n"/>
+      <c r="E30" s="20" t="n"/>
+      <c r="F30" s="20" t="n"/>
+      <c r="G30" s="20" t="n"/>
+      <c r="H30" s="20" t="n"/>
+      <c r="I30" s="20" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="13" t="inlineStr">
-        <is>
-          <t>Số ngày phải thu (DSO)</t>
-        </is>
-      </c>
-      <c r="B31" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C31" s="17">
-        <f>IFERROR(((C$56+B$56)/2)/C$47*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D31" s="17">
-        <f>IFERROR(((D$56+C$56)/2)/D$47*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E31" s="17">
-        <f>IFERROR(((E$56+D$56)/2)/E$47*365,"n/a")</f>
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>Khoản mục</t>
+        </is>
+      </c>
+      <c r="B31" s="11">
+        <f>'balance_sheet'!B1</f>
+        <v/>
+      </c>
+      <c r="C31" s="11">
+        <f>'balance_sheet'!C1</f>
+        <v/>
+      </c>
+      <c r="D31" s="11">
+        <f>'balance_sheet'!D1</f>
+        <v/>
+      </c>
+      <c r="E31" s="11">
+        <f>'balance_sheet'!E1</f>
+        <v/>
+      </c>
+      <c r="F31" s="11">
+        <f>'balance_sheet'!F1</f>
+        <v/>
+      </c>
+      <c r="G31" s="11">
+        <f>'balance_sheet'!G1</f>
+        <v/>
+      </c>
+      <c r="H31" s="11">
+        <f>'balance_sheet'!H1</f>
+        <v/>
+      </c>
+      <c r="I31" s="11">
+        <f>'balance_sheet'!I1</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="13" t="inlineStr">
-        <is>
-          <t>Số ngày tồn kho (DIO)</t>
-        </is>
-      </c>
-      <c r="B32" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C32" s="17">
-        <f>IFERROR(((C$58+B$58)/2)/ABS(C$48)*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D32" s="17">
-        <f>IFERROR(((D$58+C$58)/2)/ABS(D$48)*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E32" s="17">
-        <f>IFERROR(((E$58+D$58)/2)/ABS(E$48)*365,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33"/>
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Vốn chủ sở hữu</t>
+        </is>
+      </c>
+      <c r="B32" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C32" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D32" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E32" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F32" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G32" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H32" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I32" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>TỔNG CỘNG TÀI SẢN</t>
+        </is>
+      </c>
+      <c r="B33" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C33" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D33" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E33" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F33" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G33" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H33" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I33" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
     <row r="34">
-      <c r="A34" s="12" t="inlineStr">
-        <is>
-          <t>6. Cơ cấu tài sản</t>
-        </is>
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>NỢ PHẢI TRẢ</t>
+        </is>
+      </c>
+      <c r="B34" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C34" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D34" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E34" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F34" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G34" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H34" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I34" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="13" t="inlineStr">
-        <is>
-          <t>Tiền và tương đương tiền/Tài sản</t>
-        </is>
-      </c>
-      <c r="B35" s="15">
-        <f>IFERROR(B$59/B$41,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C35" s="15">
-        <f>IFERROR(C$59/C$41,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D35" s="15">
-        <f>IFERROR(D$59/D$41,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E35" s="15">
-        <f>IFERROR(E$59/E$41,"n/a")</f>
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Nợ phải trả ngắn hạn</t>
+        </is>
+      </c>
+      <c r="B35" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C35" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D35" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E35" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F35" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả ngắn hạn",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G35" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả ngắn hạn",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H35" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả ngắn hạn",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I35" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả ngắn hạn",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="13" t="inlineStr">
-        <is>
-          <t>Hàng tồn kho/Tài sản</t>
-        </is>
-      </c>
-      <c r="B36" s="15">
-        <f>IFERROR(B$58/B$41,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C36" s="15">
-        <f>IFERROR(C$58/C$41,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D36" s="15">
-        <f>IFERROR(D$58/D$41,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E36" s="15">
-        <f>IFERROR(E$58/E$41,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37"/>
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Nợ phải trả dài hạn</t>
+        </is>
+      </c>
+      <c r="B36" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả dài hạn",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C36" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả dài hạn",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D36" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả dài hạn",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E36" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả dài hạn",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F36" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả dài hạn",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G36" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả dài hạn",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H36" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả dài hạn",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I36" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả dài hạn",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Vay ngắn hạn</t>
+        </is>
+      </c>
+      <c r="B37" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C37" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D37" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E37" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F37" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G37" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H37" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I37" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
     <row r="38">
-      <c r="A38" s="8" t="inlineStr">
-        <is>
-          <t>II. DỮ LIỆU TRÍCH XUẤT (tự động dò theo tên khoản mục)</t>
-        </is>
-      </c>
-      <c r="B38" s="9" t="n"/>
-      <c r="C38" s="9" t="n"/>
-      <c r="D38" s="9" t="n"/>
-      <c r="E38" s="9" t="n"/>
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Vay dài hạn</t>
+        </is>
+      </c>
+      <c r="B38" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C38" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D38" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E38" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F38" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G38" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H38" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I38" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="inlineStr">
-        <is>
-          <t>Khoản mục</t>
-        </is>
-      </c>
-      <c r="B39" s="11">
-        <f>'balance_sheet'!E1</f>
-        <v/>
-      </c>
-      <c r="C39" s="11">
-        <f>'balance_sheet'!D1</f>
-        <v/>
-      </c>
-      <c r="D39" s="11">
-        <f>'balance_sheet'!C1</f>
-        <v/>
-      </c>
-      <c r="E39" s="11">
-        <f>'balance_sheet'!B1</f>
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Doanh thu thuần về hoạt động kinh doanh</t>
+        </is>
+      </c>
+      <c r="B39" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần về hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C39" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần về hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D39" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần về hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E39" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần về hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F39" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần về hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G39" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần về hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H39" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần về hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I39" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần về hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Vốn chủ sở hữu</t>
+          <t>CHI PHÍ HOẠT ĐỘNG</t>
         </is>
       </c>
       <c r="B40" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(B$39,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="C40" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(C$39,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="D40" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(D$39,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="E40" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(E$39,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F40" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G40" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H40" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I40" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>TỔNG CỘNG TÀI SẢN</t>
+          <t>LỢI NHUẬN GỘP</t>
         </is>
       </c>
       <c r="B41" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(B$39,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN GỘP",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="C41" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(C$39,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN GỘP",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="D41" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(D$39,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN GỘP",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="E41" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(E$39,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN GỘP",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F41" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN GỘP",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G41" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN GỘP",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H41" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN GỘP",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I41" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN GỘP",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>NỢ PHẢI TRẢ</t>
+          <t>CHI PHÍ BÁN HÀNG</t>
         </is>
       </c>
       <c r="B42" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(B$39,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ BÁN HÀNG",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="C42" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(C$39,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ BÁN HÀNG",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="D42" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(D$39,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ BÁN HÀNG",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="E42" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(E$39,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ BÁN HÀNG",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F42" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ BÁN HÀNG",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G42" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ BÁN HÀNG",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H42" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ BÁN HÀNG",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I42" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ BÁN HÀNG",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Nợ phải trả ngắn hạn</t>
+          <t>CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN</t>
         </is>
       </c>
       <c r="B43" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Nợ phải trả ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$39,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="C43" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Nợ phải trả ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$39,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="D43" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Nợ phải trả ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$39,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="E43" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Nợ phải trả ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$39,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F43" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G43" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H43" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I43" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Nợ phải trả dài hạn</t>
+          <t>KẾT QUẢ HOẠT ĐỘNG</t>
         </is>
       </c>
       <c r="B44" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Nợ phải trả dài hạn",balance_sheet!$A:$A,0),MATCH(B$39,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("KẾT QUẢ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="C44" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Nợ phải trả dài hạn",balance_sheet!$A:$A,0),MATCH(C$39,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("KẾT QUẢ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="D44" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Nợ phải trả dài hạn",balance_sheet!$A:$A,0),MATCH(D$39,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("KẾT QUẢ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="E44" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Nợ phải trả dài hạn",balance_sheet!$A:$A,0),MATCH(E$39,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("KẾT QUẢ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F44" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("KẾT QUẢ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G44" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("KẾT QUẢ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H44" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("KẾT QUẢ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I44" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("KẾT QUẢ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Vay ngắn hạn</t>
+          <t>Chi phí lãi vay</t>
         </is>
       </c>
       <c r="B45" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$39,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="C45" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$39,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="D45" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$39,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="E45" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$39,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F45" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G45" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H45" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I45" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>Vay dài hạn</t>
+          <t>LỢI NHUẬN KẾ TOÁN SAU THUẾ</t>
         </is>
       </c>
       <c r="B46" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(B$39,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN KẾ TOÁN SAU THUẾ",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="C46" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(C$39,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN KẾ TOÁN SAU THUẾ",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="D46" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(D$39,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN KẾ TOÁN SAU THUẾ",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="E46" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(E$39,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN KẾ TOÁN SAU THUẾ",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F46" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN KẾ TOÁN SAU THUẾ",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G46" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN KẾ TOÁN SAU THUẾ",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H46" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN KẾ TOÁN SAU THUẾ",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I46" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN KẾ TOÁN SAU THUẾ",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>Doanh thu thuần về hoạt động kinh doanh</t>
+          <t>Lợi nhuận sau thuế phân bổ cho chủ sở hữu</t>
         </is>
       </c>
       <c r="B47" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Doanh thu thuần về hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(B$39,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế phân bổ cho chủ sở hữu",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="C47" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Doanh thu thuần về hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(C$39,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế phân bổ cho chủ sở hữu",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="D47" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Doanh thu thuần về hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(D$39,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế phân bổ cho chủ sở hữu",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="E47" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Doanh thu thuần về hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(E$39,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế phân bổ cho chủ sở hữu",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F47" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế phân bổ cho chủ sở hữu",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G47" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế phân bổ cho chủ sở hữu",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H47" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế phân bổ cho chủ sở hữu",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I47" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế phân bổ cho chủ sở hữu",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>CHI PHÍ HOẠT ĐỘNG</t>
-        </is>
-      </c>
-      <c r="B48" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("CHI PHÍ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(B$39,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C48" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("CHI PHÍ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(C$39,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D48" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("CHI PHÍ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(D$39,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E48" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("CHI PHÍ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(E$39,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
+          <t>Phải thu khách hàng</t>
+        </is>
+      </c>
+      <c r="B48" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C48" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D48" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E48" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F48" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G48" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H48" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I48" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>LỢI NHUẬN GỘP</t>
+          <t>Phải trả người bán ngắn hạn</t>
         </is>
       </c>
       <c r="B49" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("LỢI NHUẬN GỘP",income_statement!$A:$A,0),MATCH(B$39,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="C49" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("LỢI NHUẬN GỘP",income_statement!$A:$A,0),MATCH(C$39,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="D49" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("LỢI NHUẬN GỘP",income_statement!$A:$A,0),MATCH(D$39,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="E49" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("LỢI NHUẬN GỘP",income_statement!$A:$A,0),MATCH(E$39,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F49" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán ngắn hạn",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G49" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán ngắn hạn",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H49" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán ngắn hạn",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I49" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán ngắn hạn",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>CHI PHÍ BÁN HÀNG</t>
-        </is>
-      </c>
-      <c r="B50" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("CHI PHÍ BÁN HÀNG",income_statement!$A:$A,0),MATCH(B$39,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C50" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("CHI PHÍ BÁN HÀNG",income_statement!$A:$A,0),MATCH(C$39,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D50" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("CHI PHÍ BÁN HÀNG",income_statement!$A:$A,0),MATCH(D$39,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E50" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("CHI PHÍ BÁN HÀNG",income_statement!$A:$A,0),MATCH(E$39,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
+          <t>Hàng tồn kho, ròng</t>
+        </is>
+      </c>
+      <c r="B50" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C50" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D50" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E50" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F50" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G50" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H50" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I50" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN</t>
+          <t>Tiền và tương đương tiền</t>
         </is>
       </c>
       <c r="B51" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN",income_statement!$A:$A,0),MATCH(B$39,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="C51" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN",income_statement!$A:$A,0),MATCH(C$39,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="D51" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN",income_statement!$A:$A,0),MATCH(D$39,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="E51" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN",income_statement!$A:$A,0),MATCH(E$39,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>KẾT QUẢ HOẠT ĐỘNG</t>
-        </is>
-      </c>
-      <c r="B52" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("KẾT QUẢ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(B$39,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C52" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("KẾT QUẢ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(C$39,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D52" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("KẾT QUẢ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(D$39,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E52" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("KẾT QUẢ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(E$39,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>Chi phí lãi vay</t>
-        </is>
-      </c>
-      <c r="B53" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(B$39,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C53" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(C$39,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D53" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(D$39,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E53" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(E$39,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>LỢI NHUẬN KẾ TOÁN SAU THUẾ</t>
-        </is>
-      </c>
-      <c r="B54" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("LỢI NHUẬN KẾ TOÁN SAU THUẾ",income_statement!$A:$A,0),MATCH(B$39,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C54" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("LỢI NHUẬN KẾ TOÁN SAU THUẾ",income_statement!$A:$A,0),MATCH(C$39,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D54" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("LỢI NHUẬN KẾ TOÁN SAU THUẾ",income_statement!$A:$A,0),MATCH(D$39,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E54" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("LỢI NHUẬN KẾ TOÁN SAU THUẾ",income_statement!$A:$A,0),MATCH(E$39,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>Lợi nhuận sau thuế phân bổ cho chủ sở hữu</t>
-        </is>
-      </c>
-      <c r="B55" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lợi nhuận sau thuế phân bổ cho chủ sở hữu",income_statement!$A:$A,0),MATCH(B$39,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C55" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lợi nhuận sau thuế phân bổ cho chủ sở hữu",income_statement!$A:$A,0),MATCH(C$39,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D55" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lợi nhuận sau thuế phân bổ cho chủ sở hữu",income_statement!$A:$A,0),MATCH(D$39,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E55" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lợi nhuận sau thuế phân bổ cho chủ sở hữu",income_statement!$A:$A,0),MATCH(E$39,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>Phải thu khách hàng</t>
-        </is>
-      </c>
-      <c r="B56" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C56" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D56" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="E56" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>Phải trả người bán ngắn hạn</t>
-        </is>
-      </c>
-      <c r="B57" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Phải trả người bán ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$39,balance_sheet!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C57" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Phải trả người bán ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$39,balance_sheet!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D57" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Phải trả người bán ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$39,balance_sheet!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E57" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Phải trả người bán ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$39,balance_sheet!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>Hàng tồn kho, ròng</t>
-        </is>
-      </c>
-      <c r="B58" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C58" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D58" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="E58" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>Tiền và tương đương tiền</t>
-        </is>
-      </c>
-      <c r="B59" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(B$39,balance_sheet!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C59" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(C$39,balance_sheet!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D59" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(D$39,balance_sheet!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E59" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(E$39,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F51" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G51" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H51" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I51" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A3:E3"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
+  <conditionalFormatting sqref="B5:I5">
+    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B6:I6">
+    <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B7:I7">
+    <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B8:I8">
+    <cfRule type="cellIs" priority="7" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="8" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B10:I10">
+    <cfRule type="cellIs" priority="9" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="10" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11:I11">
+    <cfRule type="cellIs" priority="11" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="12" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13:I13">
+    <cfRule type="cellIs" priority="13" operator="greaterThan" dxfId="1">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="14" operator="lessThan" dxfId="0">
+      <formula>0.3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B16:I16">
+    <cfRule type="cellIs" priority="15" operator="greaterThan" dxfId="1">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="16" operator="lessThan" dxfId="0">
+      <formula>0.3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B21:I21">
+    <cfRule type="cellIs" priority="17" operator="greaterThan" dxfId="1">
+      <formula>0.5</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="18" operator="lessThan" dxfId="0">
+      <formula>0.15</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/financials/TCX/TCX_financials.xlsx
+++ b/financials/TCX/TCX_financials.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_sheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="income_statement" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cash_flow" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chi_so_tai_chinh" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="balance_sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="income_statement" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="cash_flow" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="chi_so_tai_chinh" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +25,7 @@
     <numFmt numFmtId="166" formatCode="0.00&quot;x&quot;"/>
     <numFmt numFmtId="167" formatCode="#,##0 &quot;ngày&quot;"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,26 +53,7 @@
     </font>
     <font>
       <name val="Tahoma"/>
-      <i val="1"/>
-      <color rgb="00808080"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Tahoma"/>
-      <i val="1"/>
-      <color rgb="00C00000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Tahoma"/>
       <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="1"/>
-      <family val="2"/>
-      <color theme="1"/>
       <sz val="11"/>
     </font>
     <font>
@@ -157,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -168,47 +149,23 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00C6E0B4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00F8CBAD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -279,96 +236,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>auto</author>
-  </authors>
-  <commentList>
-    <comment ref="B48" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="C48" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="D48" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="E48" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="F48" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="G48" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="H48" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="I48" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="B50" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="C50" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="D50" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="E50" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="F50" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="G50" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="H50" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="I50" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -14232,353 +14099,353 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>I. CHỈ SỐ TÀI CHÍNH</t>
         </is>
       </c>
-      <c r="B2" s="20" t="n"/>
-      <c r="C2" s="20" t="n"/>
-      <c r="D2" s="20" t="n"/>
-      <c r="E2" s="20" t="n"/>
-      <c r="F2" s="20" t="n"/>
-      <c r="G2" s="20" t="n"/>
-      <c r="H2" s="20" t="n"/>
-      <c r="I2" s="20" t="n"/>
+      <c r="B2" s="7" t="n"/>
+      <c r="C2" s="7" t="n"/>
+      <c r="D2" s="7" t="n"/>
+      <c r="E2" s="7" t="n"/>
+      <c r="F2" s="7" t="n"/>
+      <c r="G2" s="7" t="n"/>
+      <c r="H2" s="7" t="n"/>
+      <c r="I2" s="7" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Chỉ tiêu</t>
         </is>
       </c>
-      <c r="B3" s="11">
+      <c r="B3" s="9">
         <f>'balance_sheet'!B1</f>
         <v/>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="9">
         <f>'balance_sheet'!C1</f>
         <v/>
       </c>
-      <c r="D3" s="11">
+      <c r="D3" s="9">
         <f>'balance_sheet'!D1</f>
         <v/>
       </c>
-      <c r="E3" s="11">
+      <c r="E3" s="9">
         <f>'balance_sheet'!E1</f>
         <v/>
       </c>
-      <c r="F3" s="11">
+      <c r="F3" s="9">
         <f>'balance_sheet'!F1</f>
         <v/>
       </c>
-      <c r="G3" s="11">
+      <c r="G3" s="9">
         <f>'balance_sheet'!G1</f>
         <v/>
       </c>
-      <c r="H3" s="11">
+      <c r="H3" s="9">
         <f>'balance_sheet'!H1</f>
         <v/>
       </c>
-      <c r="I3" s="11">
+      <c r="I3" s="9">
         <f>'balance_sheet'!I1</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>1. Khả năng sinh lời</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>ROE (LNST CĐ Cty mẹ / VCSH bình quân)</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C5" s="15">
+      <c r="C5" s="13">
         <f>IFERROR(C$47/((C$32+B$32)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="13">
         <f>IFERROR(D$47/((D$32+C$32)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="13">
         <f>IFERROR(E$47/((E$32+D$32)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="F5" s="15">
+      <c r="F5" s="13">
         <f>IFERROR(F$47/((F$32+E$32)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="G5" s="15">
+      <c r="G5" s="13">
         <f>IFERROR(G$47/((G$32+F$32)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="H5" s="15">
+      <c r="H5" s="13">
         <f>IFERROR(H$47/((H$32+G$32)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="I5" s="15">
+      <c r="I5" s="13">
         <f>IFERROR(I$47/((I$32+H$32)/2),"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>ROA (LNST / Tổng tài sản bình quân)</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="13">
         <f>IFERROR(C$46/((C$33+B$33)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="13">
         <f>IFERROR(D$46/((D$33+C$33)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="13">
         <f>IFERROR(E$46/((E$33+D$33)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="F6" s="15">
+      <c r="F6" s="13">
         <f>IFERROR(F$46/((F$33+E$33)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="G6" s="15">
+      <c r="G6" s="13">
         <f>IFERROR(G$46/((G$33+F$33)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="H6" s="15">
+      <c r="H6" s="13">
         <f>IFERROR(H$46/((H$33+G$33)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="I6" s="15">
+      <c r="I6" s="13">
         <f>IFERROR(I$46/((I$33+H$33)/2),"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Tăng trưởng LN Cổ đông Cty mẹ</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C7" s="15">
+      <c r="C7" s="13">
         <f>IFERROR((C$47-B$47)/ABS(B$47),"n/a")</f>
         <v/>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="13">
         <f>IFERROR((D$47-C$47)/ABS(C$47),"n/a")</f>
         <v/>
       </c>
-      <c r="E7" s="15">
+      <c r="E7" s="13">
         <f>IFERROR((E$47-D$47)/ABS(D$47),"n/a")</f>
         <v/>
       </c>
-      <c r="F7" s="15">
+      <c r="F7" s="13">
         <f>IFERROR((F$47-E$47)/ABS(E$47),"n/a")</f>
         <v/>
       </c>
-      <c r="G7" s="15">
+      <c r="G7" s="13">
         <f>IFERROR((G$47-F$47)/ABS(F$47),"n/a")</f>
         <v/>
       </c>
-      <c r="H7" s="15">
+      <c r="H7" s="13">
         <f>IFERROR((H$47-G$47)/ABS(G$47),"n/a")</f>
         <v/>
       </c>
-      <c r="I7" s="15">
+      <c r="I7" s="13">
         <f>IFERROR((I$47-H$47)/ABS(H$47),"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Tăng trưởng Doanh thu thuần</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="13">
         <f>IFERROR((C$39-B$39)/ABS(B$39),"n/a")</f>
         <v/>
       </c>
-      <c r="D8" s="15">
+      <c r="D8" s="13">
         <f>IFERROR((D$39-C$39)/ABS(C$39),"n/a")</f>
         <v/>
       </c>
-      <c r="E8" s="15">
+      <c r="E8" s="13">
         <f>IFERROR((E$39-D$39)/ABS(D$39),"n/a")</f>
         <v/>
       </c>
-      <c r="F8" s="15">
+      <c r="F8" s="13">
         <f>IFERROR((F$39-E$39)/ABS(E$39),"n/a")</f>
         <v/>
       </c>
-      <c r="G8" s="15">
+      <c r="G8" s="13">
         <f>IFERROR((G$39-F$39)/ABS(F$39),"n/a")</f>
         <v/>
       </c>
-      <c r="H8" s="15">
+      <c r="H8" s="13">
         <f>IFERROR((H$39-G$39)/ABS(G$39),"n/a")</f>
         <v/>
       </c>
-      <c r="I8" s="15">
+      <c r="I8" s="13">
         <f>IFERROR((I$39-H$39)/ABS(H$39),"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>2. Biên lợi nhuận</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Biên lợi nhuận gộp</t>
         </is>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="13">
         <f>IFERROR(B$41/B$39,"n/a")</f>
         <v/>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="13">
         <f>IFERROR(C$41/C$39,"n/a")</f>
         <v/>
       </c>
-      <c r="D10" s="15">
+      <c r="D10" s="13">
         <f>IFERROR(D$41/D$39,"n/a")</f>
         <v/>
       </c>
-      <c r="E10" s="15">
+      <c r="E10" s="13">
         <f>IFERROR(E$41/E$39,"n/a")</f>
         <v/>
       </c>
-      <c r="F10" s="15">
+      <c r="F10" s="13">
         <f>IFERROR(F$41/F$39,"n/a")</f>
         <v/>
       </c>
-      <c r="G10" s="15">
+      <c r="G10" s="13">
         <f>IFERROR(G$41/G$39,"n/a")</f>
         <v/>
       </c>
-      <c r="H10" s="15">
+      <c r="H10" s="13">
         <f>IFERROR(H$41/H$39,"n/a")</f>
         <v/>
       </c>
-      <c r="I10" s="15">
+      <c r="I10" s="13">
         <f>IFERROR(I$41/I$39,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Biên lợi nhuận ròng</t>
         </is>
       </c>
-      <c r="B11" s="15">
+      <c r="B11" s="13">
         <f>IFERROR(B$46/B$39,"n/a")</f>
         <v/>
       </c>
-      <c r="C11" s="15">
+      <c r="C11" s="13">
         <f>IFERROR(C$46/C$39,"n/a")</f>
         <v/>
       </c>
-      <c r="D11" s="15">
+      <c r="D11" s="13">
         <f>IFERROR(D$46/D$39,"n/a")</f>
         <v/>
       </c>
-      <c r="E11" s="15">
+      <c r="E11" s="13">
         <f>IFERROR(E$46/E$39,"n/a")</f>
         <v/>
       </c>
-      <c r="F11" s="15">
+      <c r="F11" s="13">
         <f>IFERROR(F$46/F$39,"n/a")</f>
         <v/>
       </c>
-      <c r="G11" s="15">
+      <c r="G11" s="13">
         <f>IFERROR(G$46/G$39,"n/a")</f>
         <v/>
       </c>
-      <c r="H11" s="15">
+      <c r="H11" s="13">
         <f>IFERROR(H$46/H$39,"n/a")</f>
         <v/>
       </c>
-      <c r="I11" s="15">
+      <c r="I11" s="13">
         <f>IFERROR(I$46/I$39,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>3. Đòn bẩy tài chính</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>D/E (Nợ vay / Vốn chủ sở hữu)</t>
         </is>
       </c>
-      <c r="B13" s="16">
+      <c r="B13" s="14">
         <f>IFERROR((B$37+B$38)/B$32,"n/a")</f>
         <v/>
       </c>
-      <c r="C13" s="16">
+      <c r="C13" s="14">
         <f>IFERROR((C$37+C$38)/C$32,"n/a")</f>
         <v/>
       </c>
-      <c r="D13" s="16">
+      <c r="D13" s="14">
         <f>IFERROR((D$37+D$38)/D$32,"n/a")</f>
         <v/>
       </c>
-      <c r="E13" s="16">
+      <c r="E13" s="14">
         <f>IFERROR((E$37+E$38)/E$32,"n/a")</f>
         <v/>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="14">
         <f>IFERROR((F$37+F$38)/F$32,"n/a")</f>
         <v/>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="14">
         <f>IFERROR((G$37+G$38)/G$32,"n/a")</f>
         <v/>
       </c>
-      <c r="H13" s="16">
+      <c r="H13" s="14">
         <f>IFERROR((H$37+H$38)/H$32,"n/a")</f>
         <v/>
       </c>
-      <c r="I13" s="16">
+      <c r="I13" s="14">
         <f>IFERROR((I$37+I$38)/I$32,"n/a")</f>
         <v/>
       </c>
@@ -14589,35 +14456,35 @@
           <t xml:space="preserve">     - Nợ vay dài hạn/Vốn chủ sở hữu</t>
         </is>
       </c>
-      <c r="B14" s="16">
+      <c r="B14" s="14">
         <f>IFERROR(B$38/B$32,"n/a")</f>
         <v/>
       </c>
-      <c r="C14" s="16">
+      <c r="C14" s="14">
         <f>IFERROR(C$38/C$32,"n/a")</f>
         <v/>
       </c>
-      <c r="D14" s="16">
+      <c r="D14" s="14">
         <f>IFERROR(D$38/D$32,"n/a")</f>
         <v/>
       </c>
-      <c r="E14" s="16">
+      <c r="E14" s="14">
         <f>IFERROR(E$38/E$32,"n/a")</f>
         <v/>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="14">
         <f>IFERROR(F$38/F$32,"n/a")</f>
         <v/>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="14">
         <f>IFERROR(G$38/G$32,"n/a")</f>
         <v/>
       </c>
-      <c r="H14" s="16">
+      <c r="H14" s="14">
         <f>IFERROR(H$38/H$32,"n/a")</f>
         <v/>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="14">
         <f>IFERROR(I$38/I$32,"n/a")</f>
         <v/>
       </c>
@@ -14628,74 +14495,74 @@
           <t xml:space="preserve">     - Nợ vay ngắn hạn/Vốn chủ sở hữu</t>
         </is>
       </c>
-      <c r="B15" s="16">
+      <c r="B15" s="14">
         <f>IFERROR(B$37/B$32,"n/a")</f>
         <v/>
       </c>
-      <c r="C15" s="16">
+      <c r="C15" s="14">
         <f>IFERROR(C$37/C$32,"n/a")</f>
         <v/>
       </c>
-      <c r="D15" s="16">
+      <c r="D15" s="14">
         <f>IFERROR(D$37/D$32,"n/a")</f>
         <v/>
       </c>
-      <c r="E15" s="16">
+      <c r="E15" s="14">
         <f>IFERROR(E$37/E$32,"n/a")</f>
         <v/>
       </c>
-      <c r="F15" s="16">
+      <c r="F15" s="14">
         <f>IFERROR(F$37/F$32,"n/a")</f>
         <v/>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="14">
         <f>IFERROR(G$37/G$32,"n/a")</f>
         <v/>
       </c>
-      <c r="H15" s="16">
+      <c r="H15" s="14">
         <f>IFERROR(H$37/H$32,"n/a")</f>
         <v/>
       </c>
-      <c r="I15" s="16">
+      <c r="I15" s="14">
         <f>IFERROR(I$37/I$32,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>Nợ phải trả/Vốn chủ sở hữu</t>
         </is>
       </c>
-      <c r="B16" s="16">
+      <c r="B16" s="14">
         <f>IFERROR(B$34/B$32,"n/a")</f>
         <v/>
       </c>
-      <c r="C16" s="16">
+      <c r="C16" s="14">
         <f>IFERROR(C$34/C$32,"n/a")</f>
         <v/>
       </c>
-      <c r="D16" s="16">
+      <c r="D16" s="14">
         <f>IFERROR(D$34/D$32,"n/a")</f>
         <v/>
       </c>
-      <c r="E16" s="16">
+      <c r="E16" s="14">
         <f>IFERROR(E$34/E$32,"n/a")</f>
         <v/>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="14">
         <f>IFERROR(F$34/F$32,"n/a")</f>
         <v/>
       </c>
-      <c r="G16" s="16">
+      <c r="G16" s="14">
         <f>IFERROR(G$34/G$32,"n/a")</f>
         <v/>
       </c>
-      <c r="H16" s="16">
+      <c r="H16" s="14">
         <f>IFERROR(H$34/H$32,"n/a")</f>
         <v/>
       </c>
-      <c r="I16" s="16">
+      <c r="I16" s="14">
         <f>IFERROR(I$34/I$32,"n/a")</f>
         <v/>
       </c>
@@ -14706,35 +14573,35 @@
           <t xml:space="preserve">     - Nợ dài hạn/Vốn chủ sở hữu</t>
         </is>
       </c>
-      <c r="B17" s="16">
+      <c r="B17" s="14">
         <f>IFERROR(B$36/B$32,"n/a")</f>
         <v/>
       </c>
-      <c r="C17" s="16">
+      <c r="C17" s="14">
         <f>IFERROR(C$36/C$32,"n/a")</f>
         <v/>
       </c>
-      <c r="D17" s="16">
+      <c r="D17" s="14">
         <f>IFERROR(D$36/D$32,"n/a")</f>
         <v/>
       </c>
-      <c r="E17" s="16">
+      <c r="E17" s="14">
         <f>IFERROR(E$36/E$32,"n/a")</f>
         <v/>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="14">
         <f>IFERROR(F$36/F$32,"n/a")</f>
         <v/>
       </c>
-      <c r="G17" s="16">
+      <c r="G17" s="14">
         <f>IFERROR(G$36/G$32,"n/a")</f>
         <v/>
       </c>
-      <c r="H17" s="16">
+      <c r="H17" s="14">
         <f>IFERROR(H$36/H$32,"n/a")</f>
         <v/>
       </c>
-      <c r="I17" s="16">
+      <c r="I17" s="14">
         <f>IFERROR(I$36/I$32,"n/a")</f>
         <v/>
       </c>
@@ -14745,387 +14612,387 @@
           <t xml:space="preserve">     - Nợ ngắn hạn/Vốn chủ sở hữu</t>
         </is>
       </c>
-      <c r="B18" s="16">
+      <c r="B18" s="14">
         <f>IFERROR(B$35/B$32,"n/a")</f>
         <v/>
       </c>
-      <c r="C18" s="16">
+      <c r="C18" s="14">
         <f>IFERROR(C$35/C$32,"n/a")</f>
         <v/>
       </c>
-      <c r="D18" s="16">
+      <c r="D18" s="14">
         <f>IFERROR(D$35/D$32,"n/a")</f>
         <v/>
       </c>
-      <c r="E18" s="16">
+      <c r="E18" s="14">
         <f>IFERROR(E$35/E$32,"n/a")</f>
         <v/>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="14">
         <f>IFERROR(F$35/F$32,"n/a")</f>
         <v/>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="14">
         <f>IFERROR(G$35/G$32,"n/a")</f>
         <v/>
       </c>
-      <c r="H18" s="16">
+      <c r="H18" s="14">
         <f>IFERROR(H$35/H$32,"n/a")</f>
         <v/>
       </c>
-      <c r="I18" s="16">
+      <c r="I18" s="14">
         <f>IFERROR(I$35/I$32,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>4. Chi phí &amp; khả năng trả lãi</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Chi phí bán hàng, quản lý/LN gộp</t>
         </is>
       </c>
-      <c r="B20" s="15">
+      <c r="B20" s="13">
         <f>IFERROR((ABS(B$42)+ABS(B$43))/B$41,"n/a")</f>
         <v/>
       </c>
-      <c r="C20" s="15">
+      <c r="C20" s="13">
         <f>IFERROR((ABS(C$42)+ABS(C$43))/C$41,"n/a")</f>
         <v/>
       </c>
-      <c r="D20" s="15">
+      <c r="D20" s="13">
         <f>IFERROR((ABS(D$42)+ABS(D$43))/D$41,"n/a")</f>
         <v/>
       </c>
-      <c r="E20" s="15">
+      <c r="E20" s="13">
         <f>IFERROR((ABS(E$42)+ABS(E$43))/E$41,"n/a")</f>
         <v/>
       </c>
-      <c r="F20" s="15">
+      <c r="F20" s="13">
         <f>IFERROR((ABS(F$42)+ABS(F$43))/F$41,"n/a")</f>
         <v/>
       </c>
-      <c r="G20" s="15">
+      <c r="G20" s="13">
         <f>IFERROR((ABS(G$42)+ABS(G$43))/G$41,"n/a")</f>
         <v/>
       </c>
-      <c r="H20" s="15">
+      <c r="H20" s="13">
         <f>IFERROR((ABS(H$42)+ABS(H$43))/H$41,"n/a")</f>
         <v/>
       </c>
-      <c r="I20" s="15">
+      <c r="I20" s="13">
         <f>IFERROR((ABS(I$42)+ABS(I$43))/I$41,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>Chi phí lãi vay/LN từ hoạt động kinh doanh</t>
         </is>
       </c>
-      <c r="B21" s="15">
+      <c r="B21" s="13">
         <f>IFERROR(ABS(B$45)/B$44,"n/a")</f>
         <v/>
       </c>
-      <c r="C21" s="15">
+      <c r="C21" s="13">
         <f>IFERROR(ABS(C$45)/C$44,"n/a")</f>
         <v/>
       </c>
-      <c r="D21" s="15">
+      <c r="D21" s="13">
         <f>IFERROR(ABS(D$45)/D$44,"n/a")</f>
         <v/>
       </c>
-      <c r="E21" s="15">
+      <c r="E21" s="13">
         <f>IFERROR(ABS(E$45)/E$44,"n/a")</f>
         <v/>
       </c>
-      <c r="F21" s="15">
+      <c r="F21" s="13">
         <f>IFERROR(ABS(F$45)/F$44,"n/a")</f>
         <v/>
       </c>
-      <c r="G21" s="15">
+      <c r="G21" s="13">
         <f>IFERROR(ABS(G$45)/G$44,"n/a")</f>
         <v/>
       </c>
-      <c r="H21" s="15">
+      <c r="H21" s="13">
         <f>IFERROR(ABS(H$45)/H$44,"n/a")</f>
         <v/>
       </c>
-      <c r="I21" s="15">
+      <c r="I21" s="13">
         <f>IFERROR(ABS(I$45)/I$44,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>5. Chu kỳ hoạt động vốn lưu động</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>Số ngày phải trả (DPO)</t>
         </is>
       </c>
-      <c r="B23" s="14" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C23" s="17">
+      <c r="C23" s="15">
         <f>IFERROR(((C$49+B$49)/2)/ABS(C$40)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="D23" s="17">
+      <c r="D23" s="15">
         <f>IFERROR(((D$49+C$49)/2)/ABS(D$40)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="E23" s="17">
+      <c r="E23" s="15">
         <f>IFERROR(((E$49+D$49)/2)/ABS(E$40)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="F23" s="17">
+      <c r="F23" s="15">
         <f>IFERROR(((F$49+E$49)/2)/ABS(F$40)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="G23" s="17">
+      <c r="G23" s="15">
         <f>IFERROR(((G$49+F$49)/2)/ABS(G$40)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="H23" s="17">
+      <c r="H23" s="15">
         <f>IFERROR(((H$49+G$49)/2)/ABS(H$40)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="I23" s="17">
+      <c r="I23" s="15">
         <f>IFERROR(((I$49+H$49)/2)/ABS(I$40)*365,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>Số ngày phải thu (DSO)</t>
         </is>
       </c>
-      <c r="B24" s="14" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C24" s="17">
+      <c r="C24" s="15">
         <f>IFERROR(((C$48+B$48)/2)/C$39*365,"n/a")</f>
         <v/>
       </c>
-      <c r="D24" s="17">
+      <c r="D24" s="15">
         <f>IFERROR(((D$48+C$48)/2)/D$39*365,"n/a")</f>
         <v/>
       </c>
-      <c r="E24" s="17">
+      <c r="E24" s="15">
         <f>IFERROR(((E$48+D$48)/2)/E$39*365,"n/a")</f>
         <v/>
       </c>
-      <c r="F24" s="17">
+      <c r="F24" s="15">
         <f>IFERROR(((F$48+E$48)/2)/F$39*365,"n/a")</f>
         <v/>
       </c>
-      <c r="G24" s="17">
+      <c r="G24" s="15">
         <f>IFERROR(((G$48+F$48)/2)/G$39*365,"n/a")</f>
         <v/>
       </c>
-      <c r="H24" s="17">
+      <c r="H24" s="15">
         <f>IFERROR(((H$48+G$48)/2)/H$39*365,"n/a")</f>
         <v/>
       </c>
-      <c r="I24" s="17">
+      <c r="I24" s="15">
         <f>IFERROR(((I$48+H$48)/2)/I$39*365,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>Số ngày tồn kho (DIO)</t>
         </is>
       </c>
-      <c r="B25" s="14" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C25" s="17">
+      <c r="C25" s="15">
         <f>IFERROR(((C$50+B$50)/2)/ABS(C$40)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="D25" s="17">
+      <c r="D25" s="15">
         <f>IFERROR(((D$50+C$50)/2)/ABS(D$40)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="E25" s="17">
+      <c r="E25" s="15">
         <f>IFERROR(((E$50+D$50)/2)/ABS(E$40)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="F25" s="17">
+      <c r="F25" s="15">
         <f>IFERROR(((F$50+E$50)/2)/ABS(F$40)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="G25" s="17">
+      <c r="G25" s="15">
         <f>IFERROR(((G$50+F$50)/2)/ABS(G$40)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="H25" s="17">
+      <c r="H25" s="15">
         <f>IFERROR(((H$50+G$50)/2)/ABS(H$40)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="I25" s="17">
+      <c r="I25" s="15">
         <f>IFERROR(((I$50+H$50)/2)/ABS(I$40)*365,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="inlineStr">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>6. Cơ cấu tài sản</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>Tiền và tương đương tiền/Tài sản</t>
         </is>
       </c>
-      <c r="B27" s="15">
+      <c r="B27" s="13">
         <f>IFERROR(B$51/B$33,"n/a")</f>
         <v/>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="13">
         <f>IFERROR(C$51/C$33,"n/a")</f>
         <v/>
       </c>
-      <c r="D27" s="15">
+      <c r="D27" s="13">
         <f>IFERROR(D$51/D$33,"n/a")</f>
         <v/>
       </c>
-      <c r="E27" s="15">
+      <c r="E27" s="13">
         <f>IFERROR(E$51/E$33,"n/a")</f>
         <v/>
       </c>
-      <c r="F27" s="15">
+      <c r="F27" s="13">
         <f>IFERROR(F$51/F$33,"n/a")</f>
         <v/>
       </c>
-      <c r="G27" s="15">
+      <c r="G27" s="13">
         <f>IFERROR(G$51/G$33,"n/a")</f>
         <v/>
       </c>
-      <c r="H27" s="15">
+      <c r="H27" s="13">
         <f>IFERROR(H$51/H$33,"n/a")</f>
         <v/>
       </c>
-      <c r="I27" s="15">
+      <c r="I27" s="13">
         <f>IFERROR(I$51/I$33,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="13" t="inlineStr">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>Hàng tồn kho/Tài sản</t>
         </is>
       </c>
-      <c r="B28" s="15">
+      <c r="B28" s="13">
         <f>IFERROR(B$50/B$33,"n/a")</f>
         <v/>
       </c>
-      <c r="C28" s="15">
+      <c r="C28" s="13">
         <f>IFERROR(C$50/C$33,"n/a")</f>
         <v/>
       </c>
-      <c r="D28" s="15">
+      <c r="D28" s="13">
         <f>IFERROR(D$50/D$33,"n/a")</f>
         <v/>
       </c>
-      <c r="E28" s="15">
+      <c r="E28" s="13">
         <f>IFERROR(E$50/E$33,"n/a")</f>
         <v/>
       </c>
-      <c r="F28" s="15">
+      <c r="F28" s="13">
         <f>IFERROR(F$50/F$33,"n/a")</f>
         <v/>
       </c>
-      <c r="G28" s="15">
+      <c r="G28" s="13">
         <f>IFERROR(G$50/G$33,"n/a")</f>
         <v/>
       </c>
-      <c r="H28" s="15">
+      <c r="H28" s="13">
         <f>IFERROR(H$50/H$33,"n/a")</f>
         <v/>
       </c>
-      <c r="I28" s="15">
+      <c r="I28" s="13">
         <f>IFERROR(I$50/I$33,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="29"/>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>II. DỮ LIỆU TRÍCH XUẤT (tự động dò theo tên khoản mục)</t>
         </is>
       </c>
-      <c r="B30" s="20" t="n"/>
-      <c r="C30" s="20" t="n"/>
-      <c r="D30" s="20" t="n"/>
-      <c r="E30" s="20" t="n"/>
-      <c r="F30" s="20" t="n"/>
-      <c r="G30" s="20" t="n"/>
-      <c r="H30" s="20" t="n"/>
-      <c r="I30" s="20" t="n"/>
+      <c r="B30" s="7" t="n"/>
+      <c r="C30" s="7" t="n"/>
+      <c r="D30" s="7" t="n"/>
+      <c r="E30" s="7" t="n"/>
+      <c r="F30" s="7" t="n"/>
+      <c r="G30" s="7" t="n"/>
+      <c r="H30" s="7" t="n"/>
+      <c r="I30" s="7" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="inlineStr">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>Khoản mục</t>
         </is>
       </c>
-      <c r="B31" s="11">
+      <c r="B31" s="9">
         <f>'balance_sheet'!B1</f>
         <v/>
       </c>
-      <c r="C31" s="11">
+      <c r="C31" s="9">
         <f>'balance_sheet'!C1</f>
         <v/>
       </c>
-      <c r="D31" s="11">
+      <c r="D31" s="9">
         <f>'balance_sheet'!D1</f>
         <v/>
       </c>
-      <c r="E31" s="11">
+      <c r="E31" s="9">
         <f>'balance_sheet'!E1</f>
         <v/>
       </c>
-      <c r="F31" s="11">
+      <c r="F31" s="9">
         <f>'balance_sheet'!F1</f>
         <v/>
       </c>
-      <c r="G31" s="11">
+      <c r="G31" s="9">
         <f>'balance_sheet'!G1</f>
         <v/>
       </c>
-      <c r="H31" s="11">
+      <c r="H31" s="9">
         <f>'balance_sheet'!H1</f>
         <v/>
       </c>
-      <c r="I31" s="11">
+      <c r="I31" s="9">
         <f>'balance_sheet'!I1</f>
         <v/>
       </c>
@@ -15136,35 +15003,35 @@
           <t>Vốn chủ sở hữu</t>
         </is>
       </c>
-      <c r="B32" s="18">
+      <c r="B32" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C32" s="18">
+      <c r="C32" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D32" s="18">
+      <c r="D32" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E32" s="18">
+      <c r="E32" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F32" s="18">
+      <c r="F32" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G32" s="18">
+      <c r="G32" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H32" s="18">
+      <c r="H32" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I32" s="18">
+      <c r="I32" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -15175,35 +15042,35 @@
           <t>TỔNG CỘNG TÀI SẢN</t>
         </is>
       </c>
-      <c r="B33" s="18">
+      <c r="B33" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C33" s="18">
+      <c r="C33" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D33" s="18">
+      <c r="D33" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E33" s="18">
+      <c r="E33" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F33" s="18">
+      <c r="F33" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G33" s="18">
+      <c r="G33" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H33" s="18">
+      <c r="H33" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I33" s="18">
+      <c r="I33" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -15214,35 +15081,35 @@
           <t>NỢ PHẢI TRẢ</t>
         </is>
       </c>
-      <c r="B34" s="18">
+      <c r="B34" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C34" s="18">
+      <c r="C34" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D34" s="18">
+      <c r="D34" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E34" s="18">
+      <c r="E34" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F34" s="18">
+      <c r="F34" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G34" s="18">
+      <c r="G34" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H34" s="18">
+      <c r="H34" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I34" s="18">
+      <c r="I34" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -15253,35 +15120,35 @@
           <t>Nợ phải trả ngắn hạn</t>
         </is>
       </c>
-      <c r="B35" s="18">
+      <c r="B35" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C35" s="18">
+      <c r="C35" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D35" s="18">
+      <c r="D35" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E35" s="18">
+      <c r="E35" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F35" s="18">
+      <c r="F35" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả ngắn hạn",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G35" s="18">
+      <c r="G35" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả ngắn hạn",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H35" s="18">
+      <c r="H35" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả ngắn hạn",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I35" s="18">
+      <c r="I35" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả ngắn hạn",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -15292,35 +15159,35 @@
           <t>Nợ phải trả dài hạn</t>
         </is>
       </c>
-      <c r="B36" s="18">
+      <c r="B36" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả dài hạn",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C36" s="18">
+      <c r="C36" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả dài hạn",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D36" s="18">
+      <c r="D36" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả dài hạn",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E36" s="18">
+      <c r="E36" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả dài hạn",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F36" s="18">
+      <c r="F36" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả dài hạn",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G36" s="18">
+      <c r="G36" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả dài hạn",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H36" s="18">
+      <c r="H36" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả dài hạn",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I36" s="18">
+      <c r="I36" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ phải trả dài hạn",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -15331,35 +15198,35 @@
           <t>Vay ngắn hạn</t>
         </is>
       </c>
-      <c r="B37" s="18">
+      <c r="B37" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C37" s="18">
+      <c r="C37" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D37" s="18">
+      <c r="D37" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E37" s="18">
+      <c r="E37" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F37" s="18">
+      <c r="F37" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G37" s="18">
+      <c r="G37" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H37" s="18">
+      <c r="H37" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I37" s="18">
+      <c r="I37" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -15370,35 +15237,35 @@
           <t>Vay dài hạn</t>
         </is>
       </c>
-      <c r="B38" s="18">
+      <c r="B38" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C38" s="18">
+      <c r="C38" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D38" s="18">
+      <c r="D38" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E38" s="18">
+      <c r="E38" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F38" s="18">
+      <c r="F38" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G38" s="18">
+      <c r="G38" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H38" s="18">
+      <c r="H38" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I38" s="18">
+      <c r="I38" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -15409,35 +15276,35 @@
           <t>Doanh thu thuần về hoạt động kinh doanh</t>
         </is>
       </c>
-      <c r="B39" s="18">
+      <c r="B39" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần về hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C39" s="18">
+      <c r="C39" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần về hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D39" s="18">
+      <c r="D39" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần về hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E39" s="18">
+      <c r="E39" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần về hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F39" s="18">
+      <c r="F39" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần về hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G39" s="18">
+      <c r="G39" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần về hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H39" s="18">
+      <c r="H39" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần về hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I39" s="18">
+      <c r="I39" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần về hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -15448,35 +15315,35 @@
           <t>CHI PHÍ HOẠT ĐỘNG</t>
         </is>
       </c>
-      <c r="B40" s="18">
+      <c r="B40" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C40" s="18">
+      <c r="C40" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D40" s="18">
+      <c r="D40" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E40" s="18">
+      <c r="E40" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F40" s="18">
+      <c r="F40" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G40" s="18">
+      <c r="G40" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H40" s="18">
+      <c r="H40" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I40" s="18">
+      <c r="I40" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -15487,35 +15354,35 @@
           <t>LỢI NHUẬN GỘP</t>
         </is>
       </c>
-      <c r="B41" s="18">
+      <c r="B41" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN GỘP",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C41" s="18">
+      <c r="C41" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN GỘP",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D41" s="18">
+      <c r="D41" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN GỘP",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E41" s="18">
+      <c r="E41" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN GỘP",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F41" s="18">
+      <c r="F41" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN GỘP",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G41" s="18">
+      <c r="G41" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN GỘP",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H41" s="18">
+      <c r="H41" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN GỘP",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I41" s="18">
+      <c r="I41" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN GỘP",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -15526,35 +15393,35 @@
           <t>CHI PHÍ BÁN HÀNG</t>
         </is>
       </c>
-      <c r="B42" s="18">
+      <c r="B42" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ BÁN HÀNG",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C42" s="18">
+      <c r="C42" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ BÁN HÀNG",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D42" s="18">
+      <c r="D42" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ BÁN HÀNG",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E42" s="18">
+      <c r="E42" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ BÁN HÀNG",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F42" s="18">
+      <c r="F42" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ BÁN HÀNG",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G42" s="18">
+      <c r="G42" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ BÁN HÀNG",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H42" s="18">
+      <c r="H42" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ BÁN HÀNG",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I42" s="18">
+      <c r="I42" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ BÁN HÀNG",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -15565,35 +15432,35 @@
           <t>CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN</t>
         </is>
       </c>
-      <c r="B43" s="18">
+      <c r="B43" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C43" s="18">
+      <c r="C43" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D43" s="18">
+      <c r="D43" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E43" s="18">
+      <c r="E43" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F43" s="18">
+      <c r="F43" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G43" s="18">
+      <c r="G43" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H43" s="18">
+      <c r="H43" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I43" s="18">
+      <c r="I43" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("CHI PHÍ QUẢN LÝ CÔNG TY CHỨNG KHOÁN",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -15604,35 +15471,35 @@
           <t>KẾT QUẢ HOẠT ĐỘNG</t>
         </is>
       </c>
-      <c r="B44" s="18">
+      <c r="B44" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("KẾT QUẢ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C44" s="18">
+      <c r="C44" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("KẾT QUẢ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D44" s="18">
+      <c r="D44" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("KẾT QUẢ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E44" s="18">
+      <c r="E44" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("KẾT QUẢ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F44" s="18">
+      <c r="F44" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("KẾT QUẢ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G44" s="18">
+      <c r="G44" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("KẾT QUẢ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H44" s="18">
+      <c r="H44" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("KẾT QUẢ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I44" s="18">
+      <c r="I44" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("KẾT QUẢ HOẠT ĐỘNG",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -15643,35 +15510,35 @@
           <t>Chi phí lãi vay</t>
         </is>
       </c>
-      <c r="B45" s="18">
+      <c r="B45" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C45" s="18">
+      <c r="C45" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D45" s="18">
+      <c r="D45" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E45" s="18">
+      <c r="E45" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F45" s="18">
+      <c r="F45" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G45" s="18">
+      <c r="G45" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H45" s="18">
+      <c r="H45" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I45" s="18">
+      <c r="I45" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -15682,35 +15549,35 @@
           <t>LỢI NHUẬN KẾ TOÁN SAU THUẾ</t>
         </is>
       </c>
-      <c r="B46" s="18">
+      <c r="B46" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN KẾ TOÁN SAU THUẾ",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C46" s="18">
+      <c r="C46" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN KẾ TOÁN SAU THUẾ",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D46" s="18">
+      <c r="D46" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN KẾ TOÁN SAU THUẾ",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E46" s="18">
+      <c r="E46" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN KẾ TOÁN SAU THUẾ",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F46" s="18">
+      <c r="F46" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN KẾ TOÁN SAU THUẾ",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G46" s="18">
+      <c r="G46" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN KẾ TOÁN SAU THUẾ",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H46" s="18">
+      <c r="H46" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN KẾ TOÁN SAU THUẾ",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I46" s="18">
+      <c r="I46" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("LỢI NHUẬN KẾ TOÁN SAU THUẾ",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -15721,35 +15588,35 @@
           <t>Lợi nhuận sau thuế phân bổ cho chủ sở hữu</t>
         </is>
       </c>
-      <c r="B47" s="18">
+      <c r="B47" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế phân bổ cho chủ sở hữu",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C47" s="18">
+      <c r="C47" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế phân bổ cho chủ sở hữu",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D47" s="18">
+      <c r="D47" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế phân bổ cho chủ sở hữu",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E47" s="18">
+      <c r="E47" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế phân bổ cho chủ sở hữu",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F47" s="18">
+      <c r="F47" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế phân bổ cho chủ sở hữu",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G47" s="18">
+      <c r="G47" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế phân bổ cho chủ sở hữu",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H47" s="18">
+      <c r="H47" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế phân bổ cho chủ sở hữu",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I47" s="18">
+      <c r="I47" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế phân bổ cho chủ sở hữu",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -15760,42 +15627,42 @@
           <t>Phải thu khách hàng</t>
         </is>
       </c>
-      <c r="B48" s="14" t="inlineStr">
+      <c r="B48" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C48" s="14" t="inlineStr">
+      <c r="C48" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="D48" s="14" t="inlineStr">
+      <c r="D48" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="E48" s="14" t="inlineStr">
+      <c r="E48" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="F48" s="14" t="inlineStr">
+      <c r="F48" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="G48" s="14" t="inlineStr">
+      <c r="G48" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="H48" s="14" t="inlineStr">
+      <c r="H48" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="I48" s="14" t="inlineStr">
+      <c r="I48" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
@@ -15807,35 +15674,35 @@
           <t>Phải trả người bán ngắn hạn</t>
         </is>
       </c>
-      <c r="B49" s="18">
+      <c r="B49" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C49" s="18">
+      <c r="C49" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D49" s="18">
+      <c r="D49" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E49" s="18">
+      <c r="E49" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F49" s="18">
+      <c r="F49" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán ngắn hạn",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G49" s="18">
+      <c r="G49" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán ngắn hạn",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H49" s="18">
+      <c r="H49" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán ngắn hạn",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I49" s="18">
+      <c r="I49" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán ngắn hạn",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -15846,42 +15713,42 @@
           <t>Hàng tồn kho, ròng</t>
         </is>
       </c>
-      <c r="B50" s="14" t="inlineStr">
+      <c r="B50" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C50" s="14" t="inlineStr">
+      <c r="C50" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="D50" s="14" t="inlineStr">
+      <c r="D50" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="E50" s="14" t="inlineStr">
+      <c r="E50" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="F50" s="14" t="inlineStr">
+      <c r="F50" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="G50" s="14" t="inlineStr">
+      <c r="G50" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="H50" s="14" t="inlineStr">
+      <c r="H50" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="I50" s="14" t="inlineStr">
+      <c r="I50" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
@@ -15893,35 +15760,35 @@
           <t>Tiền và tương đương tiền</t>
         </is>
       </c>
-      <c r="B51" s="18">
+      <c r="B51" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C51" s="18">
+      <c r="C51" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D51" s="18">
+      <c r="D51" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E51" s="18">
+      <c r="E51" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F51" s="18">
+      <c r="F51" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G51" s="18">
+      <c r="G51" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H51" s="18">
+      <c r="H51" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I51" s="18">
+      <c r="I51" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -15930,79 +15797,6 @@
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
-  <conditionalFormatting sqref="B5:I5">
-    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="1">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B6:I6">
-    <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="4" operator="lessThan" dxfId="1">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B7:I7">
-    <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="6" operator="lessThan" dxfId="1">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B8:I8">
-    <cfRule type="cellIs" priority="7" operator="greaterThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="8" operator="lessThan" dxfId="1">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B10:I10">
-    <cfRule type="cellIs" priority="9" operator="greaterThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="10" operator="lessThan" dxfId="1">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B11:I11">
-    <cfRule type="cellIs" priority="11" operator="greaterThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="12" operator="lessThan" dxfId="1">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B13:I13">
-    <cfRule type="cellIs" priority="13" operator="greaterThan" dxfId="1">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="14" operator="lessThan" dxfId="0">
-      <formula>0.3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B16:I16">
-    <cfRule type="cellIs" priority="15" operator="greaterThan" dxfId="1">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="16" operator="lessThan" dxfId="0">
-      <formula>0.3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B21:I21">
-    <cfRule type="cellIs" priority="17" operator="greaterThan" dxfId="1">
-      <formula>0.5</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="18" operator="lessThan" dxfId="0">
-      <formula>0.15</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>